--- a/공기산정_2026기준.xlsx
+++ b/공기산정_2026기준.xlsx
@@ -11,6 +11,9 @@
     <sheet name="별표2-비작업일수" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="기상자료" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="지점목록" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="법정공휴일" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="시설물별공기(토목)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="공기산정(1일작업량)" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="내선전공">#REF!</definedName>
@@ -38,7 +41,7 @@
     <numFmt numFmtId="174" formatCode="0&quot;월&quot;"/>
     <numFmt numFmtId="175" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -182,8 +185,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -202,8 +209,23 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="33">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -613,6 +635,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="00999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -631,7 +667,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1012,6 +1048,17 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -83940,4 +83987,6169 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="131" t="inlineStr">
+        <is>
+          <t>법정 공휴일수 (2019-2035년)  ※ 2019~2025: 기존 별표1, 2026~2035: 2026년 가이드라인 부록 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="134" t="inlineStr">
+        <is>
+          <t>연도</t>
+        </is>
+      </c>
+      <c r="B3" s="134" t="inlineStr">
+        <is>
+          <t>1월</t>
+        </is>
+      </c>
+      <c r="C3" s="134" t="inlineStr">
+        <is>
+          <t>2월</t>
+        </is>
+      </c>
+      <c r="D3" s="134" t="inlineStr">
+        <is>
+          <t>3월</t>
+        </is>
+      </c>
+      <c r="E3" s="134" t="inlineStr">
+        <is>
+          <t>4월</t>
+        </is>
+      </c>
+      <c r="F3" s="134" t="inlineStr">
+        <is>
+          <t>5월</t>
+        </is>
+      </c>
+      <c r="G3" s="134" t="inlineStr">
+        <is>
+          <t>6월</t>
+        </is>
+      </c>
+      <c r="H3" s="134" t="inlineStr">
+        <is>
+          <t>7월</t>
+        </is>
+      </c>
+      <c r="I3" s="134" t="inlineStr">
+        <is>
+          <t>8월</t>
+        </is>
+      </c>
+      <c r="J3" s="134" t="inlineStr">
+        <is>
+          <t>9월</t>
+        </is>
+      </c>
+      <c r="K3" s="134" t="inlineStr">
+        <is>
+          <t>10월</t>
+        </is>
+      </c>
+      <c r="L3" s="134" t="inlineStr">
+        <is>
+          <t>11월</t>
+        </is>
+      </c>
+      <c r="M3" s="134" t="inlineStr">
+        <is>
+          <t>12월</t>
+        </is>
+      </c>
+      <c r="N3" s="134" t="inlineStr">
+        <is>
+          <t>소계</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>6</v>
+      </c>
+      <c r="N4">
+        <f>SUM(B4:M4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5</v>
+      </c>
+      <c r="N5">
+        <f>SUM(B5:M5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6">
+        <f>SUM(B6:M6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7">
+        <f>SUM(B7:M7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8">
+        <f>SUM(B8:M8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N9">
+        <f>SUM(B9:M9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10">
+        <f>SUM(B10:M10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11">
+        <f>SUM(B11:M11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M12" t="n">
+        <v>6</v>
+      </c>
+      <c r="N12">
+        <f>SUM(B12:M12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>6</v>
+      </c>
+      <c r="N13">
+        <f>SUM(B13:M13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>6</v>
+      </c>
+      <c r="N14">
+        <f>SUM(B14:M14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>8</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6</v>
+      </c>
+      <c r="N15">
+        <f>SUM(B15:M15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16">
+        <f>SUM(B16:M16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>6</v>
+      </c>
+      <c r="N17">
+        <f>SUM(B17:M17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2033</v>
+      </c>
+      <c r="B18" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="n">
+        <v>7</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>7</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7</v>
+      </c>
+      <c r="L18" t="n">
+        <v>4</v>
+      </c>
+      <c r="M18" t="n">
+        <v>5</v>
+      </c>
+      <c r="N18">
+        <f>SUM(B18:M18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2034</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>6</v>
+      </c>
+      <c r="N19">
+        <f>SUM(B19:M19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2035</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>7</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>8</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>6</v>
+      </c>
+      <c r="N20">
+        <f>SUM(B20:M20)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" style="92" min="1" max="1"/>
+    <col width="62" customWidth="1" style="92" min="2" max="2"/>
+    <col width="22" customWidth="1" style="92" min="3" max="3"/>
+    <col width="22" customWidth="1" style="92" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="135" t="inlineStr">
+        <is>
+          <t>토목 시설물 공사기간 산정 (가이드라인 부록 5 산정공식)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1" s="92">
+      <c r="A2" s="136" t="inlineStr">
+        <is>
+          <t>※ 노란 칸에 입력합니다. 산정값 Y는 비작업일수를 포함하므로, 준비기간과 정리기간만 더합니다. 적용범위를 넘으면 산정공식을 쓰지 말고 '공기산정(1일작업량)' 시트로 산정합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="131" t="inlineStr">
+        <is>
+          <t>시설물</t>
+        </is>
+      </c>
+      <c r="B4" s="137" t="inlineStr">
+        <is>
+          <t>도로포장</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="131" t="inlineStr">
+        <is>
+          <t>총공사비 C (백만원)</t>
+        </is>
+      </c>
+      <c r="B5" s="137" t="n"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>추정금액(추정가격+부가가치세+관급자재비)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="131" t="inlineStr">
+        <is>
+          <t>도로연장(m) L</t>
+        </is>
+      </c>
+      <c r="B6" s="137" t="n"/>
+      <c r="C6">
+        <f>IF(INDEX(F23:F28,MATCH($B$4,$A$23:$A$28,0))=1,"← 필요","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="131" t="inlineStr">
+        <is>
+          <t>도로폭원(m) W</t>
+        </is>
+      </c>
+      <c r="B7" s="137" t="n"/>
+      <c r="C7">
+        <f>IF(INDEX(G23:G28,MATCH($B$4,$A$23:$A$28,0))=1,"← 필요","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="131" t="inlineStr">
+        <is>
+          <t>교량연장(m) BL</t>
+        </is>
+      </c>
+      <c r="B8" s="137" t="n"/>
+      <c r="C8">
+        <f>IF(INDEX(H23:H28,MATCH($B$4,$A$23:$A$28,0))=1,"← 필요","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="131" t="inlineStr">
+        <is>
+          <t>관경(mm) D</t>
+        </is>
+      </c>
+      <c r="B9" s="137" t="n"/>
+      <c r="C9">
+        <f>IF(INDEX(I23:I28,MATCH($B$4,$A$23:$A$28,0))=1,"← 필요","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="131" t="inlineStr">
+        <is>
+          <t>양수장/배수장/가압장 개수 S</t>
+        </is>
+      </c>
+      <c r="B10" s="137" t="n"/>
+      <c r="C10">
+        <f>IF(INDEX(J23:J28,MATCH($B$4,$A$23:$A$28,0))=1,"← 필요","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="131" t="inlineStr">
+        <is>
+          <t>하수도 연장(m) SL</t>
+        </is>
+      </c>
+      <c r="B11" s="137" t="n"/>
+      <c r="C11">
+        <f>IF(INDEX(K23:K28,MATCH($B$4,$A$23:$A$28,0))=1,"← 필요","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="131" t="inlineStr">
+        <is>
+          <t>궤도연장(m) RL</t>
+        </is>
+      </c>
+      <c r="B12" s="137" t="n"/>
+      <c r="C12">
+        <f>IF(INDEX(L23:L28,MATCH($B$4,$A$23:$A$28,0))=1,"← 필요","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="131" t="inlineStr">
+        <is>
+          <t>준비기간 (일)</t>
+        </is>
+      </c>
+      <c r="B14" s="137" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="131" t="inlineStr">
+        <is>
+          <t>정리기간 (일)</t>
+        </is>
+      </c>
+      <c r="B15" s="137" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="131" t="inlineStr">
+        <is>
+          <t>적용범위 판정</t>
+        </is>
+      </c>
+      <c r="B17" s="138">
+        <f>IF(NOT(ISNUMBER(B5)),"총공사비를 입력하세요",IF(AND(B5&gt;=INDEX($C$23:$C$28,MATCH($B$4,$A$23:$A$28,0)),B5&lt;=INDEX($D$23:$D$28,MATCH($B$4,$A$23:$A$28,0))),"적용범위 이내 (산정공식 사용 가능)","적용범위 초과 → 산정공식 사용 불가. 1일 작업량 방식으로 산정하세요"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="131" t="inlineStr">
+        <is>
+          <t>산정공식 값 Y (일)</t>
+        </is>
+      </c>
+      <c r="B18" s="138">
+        <f>IF(LEFT(B17,4)="적용범위",IF(ISNUMBER(SEARCH("이내",B17)),IFERROR(ROUND(IF($B$4="도로포장",-637.009+173.198*LN(B6)+0.049*B5,IF($B$4="도로(토공+교량)",-160.855-14.288*B7+164.473*LN(B6)-1.474*B8+0.052*B5,IF($B$4="농업용수",-2251.569+415.137*LN(B5),IF($B$4="상수도",-1175.174+119.731*B10-0.273*B9+222.426*LN(B5),IF($B$4="하수도",-452.433+98.364*LN(B11)+0.083*B5,-1723.316-74.26*LN(B12)+372.266*LN(B5)))))),0),"입력 확인"),"적용불가"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="131" t="inlineStr">
+        <is>
+          <t>공사기간 (Y + 준비 + 정리, 일)</t>
+        </is>
+      </c>
+      <c r="B19" s="138">
+        <f>IF(ISNUMBER(B18),B18+B14+B15,"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="131" t="inlineStr">
+        <is>
+          <t>환산 (개월)</t>
+        </is>
+      </c>
+      <c r="B20" s="138">
+        <f>IF(ISNUMBER(B19),ROUND(B19/30,1),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>▼ 시설물별 산정공식과 적용범위 (부록 5)  Y=공사기간(일), 금액 단위는 백만원(농업용수·상수도 등 범위는 억원을 백만원으로 환산)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="134" t="inlineStr">
+        <is>
+          <t>시설물</t>
+        </is>
+      </c>
+      <c r="B22" s="134" t="inlineStr">
+        <is>
+          <t>산정공식</t>
+        </is>
+      </c>
+      <c r="C22" s="134" t="inlineStr">
+        <is>
+          <t>총공사비 하한(백만원)</t>
+        </is>
+      </c>
+      <c r="D22" s="134" t="inlineStr">
+        <is>
+          <t>총공사비 상한(백만원)</t>
+        </is>
+      </c>
+      <c r="E22" s="134" t="inlineStr"/>
+      <c r="F22" s="134" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G22" s="134" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="H22" s="134" t="inlineStr">
+        <is>
+          <t>BL</t>
+        </is>
+      </c>
+      <c r="I22" s="134" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J22" s="134" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K22" s="134" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="L22" s="134" t="inlineStr">
+        <is>
+          <t>RL</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="139" t="inlineStr">
+        <is>
+          <t>도로포장</t>
+        </is>
+      </c>
+      <c r="B23" s="139" t="inlineStr">
+        <is>
+          <t>Y = -637.009 + 173.198×ln(L) + 0.049×C</t>
+        </is>
+      </c>
+      <c r="C23" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="139" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E23" s="139" t="n"/>
+      <c r="F23" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="139" t="inlineStr">
+        <is>
+          <t>도로(토공+교량)</t>
+        </is>
+      </c>
+      <c r="B24" s="139" t="inlineStr">
+        <is>
+          <t>Y = -160.855 - 14.288×W + 164.473×ln(L) - 1.474×BL + 0.052×C</t>
+        </is>
+      </c>
+      <c r="C24" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="139" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E24" s="139" t="n"/>
+      <c r="F24" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="139" t="inlineStr">
+        <is>
+          <t>농업용수</t>
+        </is>
+      </c>
+      <c r="B25" s="139" t="inlineStr">
+        <is>
+          <t>Y = -2251.569 + 415.137×ln(C)</t>
+        </is>
+      </c>
+      <c r="C25" s="139" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D25" s="139" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E25" s="139" t="n"/>
+      <c r="F25" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="139" t="inlineStr">
+        <is>
+          <t>상수도</t>
+        </is>
+      </c>
+      <c r="B26" s="139" t="inlineStr">
+        <is>
+          <t>Y = -1175.174 + 119.731×S - 0.273×D + 222.426×ln(C)</t>
+        </is>
+      </c>
+      <c r="C26" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="139" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E26" s="139" t="n"/>
+      <c r="F26" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="139" t="inlineStr">
+        <is>
+          <t>하수도</t>
+        </is>
+      </c>
+      <c r="B27" s="139" t="inlineStr">
+        <is>
+          <t>Y = -452.433 + 98.364×ln(SL) + 0.083×C</t>
+        </is>
+      </c>
+      <c r="C27" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="139" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E27" s="139" t="n"/>
+      <c r="F27" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="139" t="inlineStr">
+        <is>
+          <t>철도(궤도)</t>
+        </is>
+      </c>
+      <c r="B28" s="139" t="inlineStr">
+        <is>
+          <t>Y = -1723.316 - 74.260×ln(RL) + 372.266×ln(C)</t>
+        </is>
+      </c>
+      <c r="C28" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="139" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E28" s="139" t="n"/>
+      <c r="F28" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>※ ln은 자연로그. 상수도는 다종의 관일 때 물량이 가장 많거나 가장 큰 관경을 적용. 도로포장은 토공+교량이 함께 있으면 '도로(토공+교량)' 공식을 적용. 철도(궤도)는 설비 부분 공기 별도.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"도로포장,도로(토공+교량),농업용수,상수도,하수도,철도(궤도)"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P119"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" style="92" min="1" max="1"/>
+    <col width="34" customWidth="1" style="92" min="2" max="2"/>
+    <col width="14" customWidth="1" style="92" min="3" max="3"/>
+    <col width="14" customWidth="1" style="92" min="4" max="4"/>
+    <col width="14" customWidth="1" style="92" min="5" max="5"/>
+    <col width="14" customWidth="1" style="92" min="6" max="6"/>
+    <col width="14" customWidth="1" style="92" min="7" max="7"/>
+    <col width="14" customWidth="1" style="92" min="8" max="8"/>
+    <col width="14" customWidth="1" style="92" min="9" max="9"/>
+    <col width="14" customWidth="1" style="92" min="10" max="10"/>
+    <col width="14" customWidth="1" style="92" min="11" max="11"/>
+    <col width="14" customWidth="1" style="92" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="135" t="inlineStr">
+        <is>
+          <t>1일 작업량에 의한 공사기간 산정 (가이드라인 제2장)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1" s="92">
+      <c r="A2" s="136" t="inlineStr">
+        <is>
+          <t>공사기간 = 준비기간 + 주공정(CP) 공종별 공사기간의 합 + 정리기간,  공종별 공사기간 = 작업일수 + 비작업일수.  월별 비작업일수 = A(기후)+B(공휴일)-C(A×B÷달력일수), 월 8일(주40시간) 미만이면 8일 적용.  공종은 입력 순서대로 이어서 시공하는 것으로 계산합니다. 준비·정리기간에는 비작업일수를 넣지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="131" t="inlineStr">
+        <is>
+          <t>기상 지점</t>
+        </is>
+      </c>
+      <c r="B4" s="137" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="C4">
+        <f>IFERROR("지점코드 "&amp;INDEX(지점목록!$C$2:$C$96,MATCH(B4,지점목록!$A$2:$A$96,0)),"지점명을 확인하세요")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="131" t="inlineStr">
+        <is>
+          <t>본공사 착수 연도</t>
+        </is>
+      </c>
+      <c r="B5" s="137" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>※ 본공사 착수 월의 1일부터 계산 (준비기간은 그 이전)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="131" t="inlineStr">
+        <is>
+          <t>본공사 착수 월</t>
+        </is>
+      </c>
+      <c r="B6" s="137" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="131" t="inlineStr">
+        <is>
+          <t>준비기간 (일)</t>
+        </is>
+      </c>
+      <c r="B7" s="137">
+        <f>'시설물별공기(토목)'!B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="131" t="inlineStr">
+        <is>
+          <t>정리기간 (일)</t>
+        </is>
+      </c>
+      <c r="B8" s="137">
+        <f>'시설물별공기(토목)'!B15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="131" t="inlineStr">
+        <is>
+          <t>▼ 적용할 기상조건 선택 (O=적용, X=미적용) — 선택한 지점의 월별 비작업일수(2015~2024, 가이드라인 부록 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="134" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B11" s="134" t="inlineStr">
+        <is>
+          <t>기상조건</t>
+        </is>
+      </c>
+      <c r="C11" s="134" t="inlineStr">
+        <is>
+          <t>적용</t>
+        </is>
+      </c>
+      <c r="D11" s="134" t="inlineStr">
+        <is>
+          <t>1월</t>
+        </is>
+      </c>
+      <c r="E11" s="134" t="inlineStr">
+        <is>
+          <t>2월</t>
+        </is>
+      </c>
+      <c r="F11" s="134" t="inlineStr">
+        <is>
+          <t>3월</t>
+        </is>
+      </c>
+      <c r="G11" s="134" t="inlineStr">
+        <is>
+          <t>4월</t>
+        </is>
+      </c>
+      <c r="H11" s="134" t="inlineStr">
+        <is>
+          <t>5월</t>
+        </is>
+      </c>
+      <c r="I11" s="134" t="inlineStr">
+        <is>
+          <t>6월</t>
+        </is>
+      </c>
+      <c r="J11" s="134" t="inlineStr">
+        <is>
+          <t>7월</t>
+        </is>
+      </c>
+      <c r="K11" s="134" t="inlineStr">
+        <is>
+          <t>8월</t>
+        </is>
+      </c>
+      <c r="L11" s="134" t="inlineStr">
+        <is>
+          <t>9월</t>
+        </is>
+      </c>
+      <c r="M11" s="134" t="inlineStr">
+        <is>
+          <t>10월</t>
+        </is>
+      </c>
+      <c r="N11" s="134" t="inlineStr">
+        <is>
+          <t>11월</t>
+        </is>
+      </c>
+      <c r="O11" s="134" t="inlineStr">
+        <is>
+          <t>12월</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>소계</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="139" t="inlineStr">
+        <is>
+          <t>혹서기：체감온도 33°C 이상</t>
+        </is>
+      </c>
+      <c r="C12" s="137" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D12" s="139">
+        <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="139">
+        <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
+        <v/>
+      </c>
+      <c r="F12" s="139">
+        <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="139">
+        <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="139">
+        <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="139">
+        <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="139">
+        <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="139">
+        <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
+        <v/>
+      </c>
+      <c r="L12" s="139">
+        <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="139">
+        <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
+        <v/>
+      </c>
+      <c r="N12" s="139">
+        <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
+        <v/>
+      </c>
+      <c r="O12" s="139">
+        <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
+        <v/>
+      </c>
+      <c r="P12" s="139">
+        <f>SUM(D12:O12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="139" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="139" t="inlineStr">
+        <is>
+          <t>혹서기：체감온도 35°C 이상</t>
+        </is>
+      </c>
+      <c r="C13" s="137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D13" s="139">
+        <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="139">
+        <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="139">
+        <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
+        <v/>
+      </c>
+      <c r="G13" s="139">
+        <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="139">
+        <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="139">
+        <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="139">
+        <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="139">
+        <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
+        <v/>
+      </c>
+      <c r="L13" s="139">
+        <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="139">
+        <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
+        <v/>
+      </c>
+      <c r="N13" s="139">
+        <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
+        <v/>
+      </c>
+      <c r="O13" s="139">
+        <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
+        <v/>
+      </c>
+      <c r="P13" s="139">
+        <f>SUM(D13:O13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="139" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="139" t="inlineStr">
+        <is>
+          <t>혹서기：일최고온도 33°C 이상</t>
+        </is>
+      </c>
+      <c r="C14" s="137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D14" s="139">
+        <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="139">
+        <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
+        <v/>
+      </c>
+      <c r="F14" s="139">
+        <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
+        <v/>
+      </c>
+      <c r="G14" s="139">
+        <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="139">
+        <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="139">
+        <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="139">
+        <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
+        <v/>
+      </c>
+      <c r="K14" s="139">
+        <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
+        <v/>
+      </c>
+      <c r="L14" s="139">
+        <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="139">
+        <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
+        <v/>
+      </c>
+      <c r="N14" s="139">
+        <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
+        <v/>
+      </c>
+      <c r="O14" s="139">
+        <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
+        <v/>
+      </c>
+      <c r="P14" s="139">
+        <f>SUM(D14:O14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="139" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="139" t="inlineStr">
+        <is>
+          <t>혹서기：일최고온도 35°C 이상</t>
+        </is>
+      </c>
+      <c r="C15" s="137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D15" s="139">
+        <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="139">
+        <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
+        <v/>
+      </c>
+      <c r="F15" s="139">
+        <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="139">
+        <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="139">
+        <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="139">
+        <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="139">
+        <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
+        <v/>
+      </c>
+      <c r="K15" s="139">
+        <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
+        <v/>
+      </c>
+      <c r="L15" s="139">
+        <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
+        <v/>
+      </c>
+      <c r="M15" s="139">
+        <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
+        <v/>
+      </c>
+      <c r="N15" s="139">
+        <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
+        <v/>
+      </c>
+      <c r="O15" s="139">
+        <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
+        <v/>
+      </c>
+      <c r="P15" s="139">
+        <f>SUM(D15:O15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="139" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="139" t="inlineStr">
+        <is>
+          <t>동절기：일최고기온 0°C 이하</t>
+        </is>
+      </c>
+      <c r="C16" s="137" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D16" s="139">
+        <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="139">
+        <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
+        <v/>
+      </c>
+      <c r="F16" s="139">
+        <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
+        <v/>
+      </c>
+      <c r="G16" s="139">
+        <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="139">
+        <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="139">
+        <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="139">
+        <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
+        <v/>
+      </c>
+      <c r="K16" s="139">
+        <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
+        <v/>
+      </c>
+      <c r="L16" s="139">
+        <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
+        <v/>
+      </c>
+      <c r="M16" s="139">
+        <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
+        <v/>
+      </c>
+      <c r="N16" s="139">
+        <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
+        <v/>
+      </c>
+      <c r="O16" s="139">
+        <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
+        <v/>
+      </c>
+      <c r="P16" s="139">
+        <f>SUM(D16:O16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="139" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" s="139" t="inlineStr">
+        <is>
+          <t>동절기：일최심신적설 5㎝ 이상</t>
+        </is>
+      </c>
+      <c r="C17" s="137" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D17" s="139">
+        <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="139">
+        <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
+        <v/>
+      </c>
+      <c r="F17" s="139">
+        <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
+        <v/>
+      </c>
+      <c r="G17" s="139">
+        <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
+        <v/>
+      </c>
+      <c r="H17" s="139">
+        <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
+        <v/>
+      </c>
+      <c r="I17" s="139">
+        <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="139">
+        <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
+        <v/>
+      </c>
+      <c r="K17" s="139">
+        <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
+        <v/>
+      </c>
+      <c r="L17" s="139">
+        <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
+        <v/>
+      </c>
+      <c r="M17" s="139">
+        <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
+        <v/>
+      </c>
+      <c r="N17" s="139">
+        <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
+        <v/>
+      </c>
+      <c r="O17" s="139">
+        <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
+        <v/>
+      </c>
+      <c r="P17" s="139">
+        <f>SUM(D17:O17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="139" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" s="139" t="inlineStr">
+        <is>
+          <t>동절기：일최고기온 0°C 이하 이거나 일최심신적설 5㎝ 이상</t>
+        </is>
+      </c>
+      <c r="C18" s="137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D18" s="139">
+        <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
+        <v/>
+      </c>
+      <c r="E18" s="139">
+        <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
+        <v/>
+      </c>
+      <c r="F18" s="139">
+        <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
+        <v/>
+      </c>
+      <c r="G18" s="139">
+        <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="139">
+        <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
+        <v/>
+      </c>
+      <c r="I18" s="139">
+        <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="139">
+        <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
+        <v/>
+      </c>
+      <c r="K18" s="139">
+        <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
+        <v/>
+      </c>
+      <c r="L18" s="139">
+        <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
+        <v/>
+      </c>
+      <c r="M18" s="139">
+        <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
+        <v/>
+      </c>
+      <c r="N18" s="139">
+        <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
+        <v/>
+      </c>
+      <c r="O18" s="139">
+        <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
+        <v/>
+      </c>
+      <c r="P18" s="139">
+        <f>SUM(D18:O18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="139" t="n">
+        <v>8</v>
+      </c>
+      <c r="B19" s="139" t="inlineStr">
+        <is>
+          <t>동절기：일최저기온 -12°C 이하</t>
+        </is>
+      </c>
+      <c r="C19" s="137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D19" s="139">
+        <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
+        <v/>
+      </c>
+      <c r="E19" s="139">
+        <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
+        <v/>
+      </c>
+      <c r="F19" s="139">
+        <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
+        <v/>
+      </c>
+      <c r="G19" s="139">
+        <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
+        <v/>
+      </c>
+      <c r="H19" s="139">
+        <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
+        <v/>
+      </c>
+      <c r="I19" s="139">
+        <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="139">
+        <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
+        <v/>
+      </c>
+      <c r="K19" s="139">
+        <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
+        <v/>
+      </c>
+      <c r="L19" s="139">
+        <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
+        <v/>
+      </c>
+      <c r="M19" s="139">
+        <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
+        <v/>
+      </c>
+      <c r="N19" s="139">
+        <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
+        <v/>
+      </c>
+      <c r="O19" s="139">
+        <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
+        <v/>
+      </c>
+      <c r="P19" s="139">
+        <f>SUM(D19:O19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="139" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" s="139" t="inlineStr">
+        <is>
+          <t>일강수량：3㎜ 이상</t>
+        </is>
+      </c>
+      <c r="C20" s="137" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D20" s="139">
+        <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
+        <v/>
+      </c>
+      <c r="E20" s="139">
+        <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
+        <v/>
+      </c>
+      <c r="F20" s="139">
+        <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
+        <v/>
+      </c>
+      <c r="G20" s="139">
+        <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
+        <v/>
+      </c>
+      <c r="H20" s="139">
+        <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
+        <v/>
+      </c>
+      <c r="I20" s="139">
+        <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="139">
+        <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
+        <v/>
+      </c>
+      <c r="K20" s="139">
+        <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
+        <v/>
+      </c>
+      <c r="L20" s="139">
+        <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
+        <v/>
+      </c>
+      <c r="M20" s="139">
+        <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
+        <v/>
+      </c>
+      <c r="N20" s="139">
+        <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
+        <v/>
+      </c>
+      <c r="O20" s="139">
+        <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
+        <v/>
+      </c>
+      <c r="P20" s="139">
+        <f>SUM(D20:O20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="139" t="n">
+        <v>10</v>
+      </c>
+      <c r="B21" s="139" t="inlineStr">
+        <is>
+          <t>일강수량：5㎜ 이상</t>
+        </is>
+      </c>
+      <c r="C21" s="137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D21" s="139">
+        <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
+        <v/>
+      </c>
+      <c r="E21" s="139">
+        <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
+        <v/>
+      </c>
+      <c r="F21" s="139">
+        <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
+        <v/>
+      </c>
+      <c r="G21" s="139">
+        <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
+        <v/>
+      </c>
+      <c r="H21" s="139">
+        <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
+        <v/>
+      </c>
+      <c r="I21" s="139">
+        <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="139">
+        <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
+        <v/>
+      </c>
+      <c r="K21" s="139">
+        <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
+        <v/>
+      </c>
+      <c r="L21" s="139">
+        <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
+        <v/>
+      </c>
+      <c r="M21" s="139">
+        <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
+        <v/>
+      </c>
+      <c r="N21" s="139">
+        <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
+        <v/>
+      </c>
+      <c r="O21" s="139">
+        <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
+        <v/>
+      </c>
+      <c r="P21" s="139">
+        <f>SUM(D21:O21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="139" t="n">
+        <v>11</v>
+      </c>
+      <c r="B22" s="139" t="inlineStr">
+        <is>
+          <t>일강수량：10㎜ 이상</t>
+        </is>
+      </c>
+      <c r="C22" s="137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D22" s="139">
+        <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
+        <v/>
+      </c>
+      <c r="E22" s="139">
+        <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
+        <v/>
+      </c>
+      <c r="F22" s="139">
+        <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
+        <v/>
+      </c>
+      <c r="G22" s="139">
+        <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
+        <v/>
+      </c>
+      <c r="H22" s="139">
+        <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="139">
+        <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="139">
+        <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
+        <v/>
+      </c>
+      <c r="K22" s="139">
+        <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
+        <v/>
+      </c>
+      <c r="L22" s="139">
+        <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
+        <v/>
+      </c>
+      <c r="M22" s="139">
+        <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
+        <v/>
+      </c>
+      <c r="N22" s="139">
+        <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
+        <v/>
+      </c>
+      <c r="O22" s="139">
+        <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
+        <v/>
+      </c>
+      <c r="P22" s="139">
+        <f>SUM(D22:O22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="139" t="n">
+        <v>12</v>
+      </c>
+      <c r="B23" s="139" t="inlineStr">
+        <is>
+          <t>일강수량：20㎜ 이상</t>
+        </is>
+      </c>
+      <c r="C23" s="137" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D23" s="139">
+        <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
+        <v/>
+      </c>
+      <c r="E23" s="139">
+        <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
+        <v/>
+      </c>
+      <c r="F23" s="139">
+        <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
+        <v/>
+      </c>
+      <c r="G23" s="139">
+        <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
+        <v/>
+      </c>
+      <c r="H23" s="139">
+        <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="139">
+        <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="139">
+        <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
+        <v/>
+      </c>
+      <c r="K23" s="139">
+        <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
+        <v/>
+      </c>
+      <c r="L23" s="139">
+        <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
+        <v/>
+      </c>
+      <c r="M23" s="139">
+        <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
+        <v/>
+      </c>
+      <c r="N23" s="139">
+        <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
+        <v/>
+      </c>
+      <c r="O23" s="139">
+        <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
+        <v/>
+      </c>
+      <c r="P23" s="139">
+        <f>SUM(D23:O23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="139" t="n">
+        <v>13</v>
+      </c>
+      <c r="B24" s="139" t="inlineStr">
+        <is>
+          <t>일최대순간풍속：15m/s 이상</t>
+        </is>
+      </c>
+      <c r="C24" s="137" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D24" s="139">
+        <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
+        <v/>
+      </c>
+      <c r="E24" s="139">
+        <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
+        <v/>
+      </c>
+      <c r="F24" s="139">
+        <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
+        <v/>
+      </c>
+      <c r="G24" s="139">
+        <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
+        <v/>
+      </c>
+      <c r="H24" s="139">
+        <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
+        <v/>
+      </c>
+      <c r="I24" s="139">
+        <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="139">
+        <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
+        <v/>
+      </c>
+      <c r="K24" s="139">
+        <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
+        <v/>
+      </c>
+      <c r="L24" s="139">
+        <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
+        <v/>
+      </c>
+      <c r="M24" s="139">
+        <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
+        <v/>
+      </c>
+      <c r="N24" s="139">
+        <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
+        <v/>
+      </c>
+      <c r="O24" s="139">
+        <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
+        <v/>
+      </c>
+      <c r="P24" s="139">
+        <f>SUM(D24:O24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="131" t="inlineStr">
+        <is>
+          <t>적용 조건 합계 (A: 기후여건)</t>
+        </is>
+      </c>
+      <c r="D25" s="140">
+        <f>SUMPRODUCT(($C$12:$C$24="O")*D12:D24)</f>
+        <v/>
+      </c>
+      <c r="E25" s="140">
+        <f>SUMPRODUCT(($C$12:$C$24="O")*E12:E24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="140">
+        <f>SUMPRODUCT(($C$12:$C$24="O")*F12:F24)</f>
+        <v/>
+      </c>
+      <c r="G25" s="140">
+        <f>SUMPRODUCT(($C$12:$C$24="O")*G12:G24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="140">
+        <f>SUMPRODUCT(($C$12:$C$24="O")*H12:H24)</f>
+        <v/>
+      </c>
+      <c r="I25" s="140">
+        <f>SUMPRODUCT(($C$12:$C$24="O")*I12:I24)</f>
+        <v/>
+      </c>
+      <c r="J25" s="140">
+        <f>SUMPRODUCT(($C$12:$C$24="O")*J12:J24)</f>
+        <v/>
+      </c>
+      <c r="K25" s="140">
+        <f>SUMPRODUCT(($C$12:$C$24="O")*K12:K24)</f>
+        <v/>
+      </c>
+      <c r="L25" s="140">
+        <f>SUMPRODUCT(($C$12:$C$24="O")*L12:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="140">
+        <f>SUMPRODUCT(($C$12:$C$24="O")*M12:M24)</f>
+        <v/>
+      </c>
+      <c r="N25" s="140">
+        <f>SUMPRODUCT(($C$12:$C$24="O")*N12:N24)</f>
+        <v/>
+      </c>
+      <c r="O25" s="140">
+        <f>SUMPRODUCT(($C$12:$C$24="O")*O12:O24)</f>
+        <v/>
+      </c>
+      <c r="P25">
+        <f>SUM(D25:O25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="131" t="inlineStr">
+        <is>
+          <t>▼ 공종별 작업량 입력 (주공정=Y인 공종만 공사기간에 합산, 위에서 아래 순서로 이어서 시공)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="134" t="inlineStr">
+        <is>
+          <t>공종</t>
+        </is>
+      </c>
+      <c r="B28" s="134" t="inlineStr">
+        <is>
+          <t>작업수량</t>
+        </is>
+      </c>
+      <c r="C28" s="134" t="inlineStr">
+        <is>
+          <t>단위</t>
+        </is>
+      </c>
+      <c r="D28" s="134" t="inlineStr">
+        <is>
+          <t>1일 작업량</t>
+        </is>
+      </c>
+      <c r="E28" s="134" t="inlineStr">
+        <is>
+          <t>주공정(Y/N)</t>
+        </is>
+      </c>
+      <c r="F28" s="134" t="inlineStr">
+        <is>
+          <t>작업일수</t>
+        </is>
+      </c>
+      <c r="G28" s="134" t="inlineStr">
+        <is>
+          <t>누적 작업일수</t>
+        </is>
+      </c>
+      <c r="H28" s="134" t="inlineStr">
+        <is>
+          <t>경과일수(누적)</t>
+        </is>
+      </c>
+      <c r="I28" s="134" t="inlineStr">
+        <is>
+          <t>공종별 공사기간</t>
+        </is>
+      </c>
+      <c r="J28" s="134" t="inlineStr">
+        <is>
+          <t>비작업일수</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="137" t="inlineStr">
+        <is>
+          <t>철골세우기</t>
+        </is>
+      </c>
+      <c r="B29" s="137" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C29" s="137" t="inlineStr">
+        <is>
+          <t>톤</t>
+        </is>
+      </c>
+      <c r="D29" s="137" t="n">
+        <v>50</v>
+      </c>
+      <c r="E29" s="137" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F29" s="139">
+        <f>IF(AND(ISNUMBER(B29),ISNUMBER(D29),N(D29)&gt;0),ROUNDUP(B29/D29,0),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="139">
+        <f>IF(F29="","",N(G28)+IF(E29="Y",F29,0))</f>
+        <v/>
+      </c>
+      <c r="H29" s="139">
+        <f>IF(G29="","",IF(G29=0,0,IF(G29&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G29,$K$58:$K$117,1))+(G29-INDEX($K$58:$K$117,MATCH(G29,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G29,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G29,$K$58:$K$117,1)))))</f>
+        <v/>
+      </c>
+      <c r="I29" s="139">
+        <f>IF(F29="","",IF(E29="Y",IF(ISNUMBER(H29),ROUND(H29-N(H28),1),"기간초과"),"-"))</f>
+        <v/>
+      </c>
+      <c r="J29" s="139">
+        <f>IF(ISNUMBER(I29),ROUND(I29-F29,1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="137" t="inlineStr">
+        <is>
+          <t>데크플레이트 설치</t>
+        </is>
+      </c>
+      <c r="B30" s="137" t="n">
+        <v>33800</v>
+      </c>
+      <c r="C30" s="137" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="D30" s="137" t="n">
+        <v>440</v>
+      </c>
+      <c r="E30" s="137" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F30" s="139">
+        <f>IF(AND(ISNUMBER(B30),ISNUMBER(D30),N(D30)&gt;0),ROUNDUP(B30/D30,0),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="139">
+        <f>IF(F30="","",N(G29)+IF(E30="Y",F30,0))</f>
+        <v/>
+      </c>
+      <c r="H30" s="139">
+        <f>IF(G30="","",IF(G30=0,0,IF(G30&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G30,$K$58:$K$117,1))+(G30-INDEX($K$58:$K$117,MATCH(G30,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G30,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G30,$K$58:$K$117,1)))))</f>
+        <v/>
+      </c>
+      <c r="I30" s="139">
+        <f>IF(F30="","",IF(E30="Y",IF(ISNUMBER(H30),ROUND(H30-N(H29),1),"기간초과"),"-"))</f>
+        <v/>
+      </c>
+      <c r="J30" s="139">
+        <f>IF(ISNUMBER(I30),ROUND(I30-F30,1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="137" t="inlineStr">
+        <is>
+          <t>철근 가공/조립</t>
+        </is>
+      </c>
+      <c r="B31" s="137" t="n">
+        <v>940</v>
+      </c>
+      <c r="C31" s="137" t="inlineStr">
+        <is>
+          <t>톤</t>
+        </is>
+      </c>
+      <c r="D31" s="137" t="n">
+        <v>12</v>
+      </c>
+      <c r="E31" s="137" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F31" s="139">
+        <f>IF(AND(ISNUMBER(B31),ISNUMBER(D31),N(D31)&gt;0),ROUNDUP(B31/D31,0),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="139">
+        <f>IF(F31="","",N(G30)+IF(E31="Y",F31,0))</f>
+        <v/>
+      </c>
+      <c r="H31" s="139">
+        <f>IF(G31="","",IF(G31=0,0,IF(G31&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G31,$K$58:$K$117,1))+(G31-INDEX($K$58:$K$117,MATCH(G31,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G31,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G31,$K$58:$K$117,1)))))</f>
+        <v/>
+      </c>
+      <c r="I31" s="139">
+        <f>IF(F31="","",IF(E31="Y",IF(ISNUMBER(H31),ROUND(H31-N(H30),1),"기간초과"),"-"))</f>
+        <v/>
+      </c>
+      <c r="J31" s="139">
+        <f>IF(ISNUMBER(I31),ROUND(I31-F31,1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="137" t="inlineStr">
+        <is>
+          <t>형틀 조립</t>
+        </is>
+      </c>
+      <c r="B32" s="137" t="n">
+        <v>24500</v>
+      </c>
+      <c r="C32" s="137" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="D32" s="137" t="n">
+        <v>320</v>
+      </c>
+      <c r="E32" s="137" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F32" s="139">
+        <f>IF(AND(ISNUMBER(B32),ISNUMBER(D32),N(D32)&gt;0),ROUNDUP(B32/D32,0),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="139">
+        <f>IF(F32="","",N(G31)+IF(E32="Y",F32,0))</f>
+        <v/>
+      </c>
+      <c r="H32" s="139">
+        <f>IF(G32="","",IF(G32=0,0,IF(G32&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G32,$K$58:$K$117,1))+(G32-INDEX($K$58:$K$117,MATCH(G32,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G32,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G32,$K$58:$K$117,1)))))</f>
+        <v/>
+      </c>
+      <c r="I32" s="139">
+        <f>IF(F32="","",IF(E32="Y",IF(ISNUMBER(H32),ROUND(H32-N(H31),1),"기간초과"),"-"))</f>
+        <v/>
+      </c>
+      <c r="J32" s="139">
+        <f>IF(ISNUMBER(I32),ROUND(I32-F32,1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="137" t="inlineStr">
+        <is>
+          <t>콘크리트 타설</t>
+        </is>
+      </c>
+      <c r="B33" s="137" t="n">
+        <v>10300</v>
+      </c>
+      <c r="C33" s="137" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="D33" s="137" t="n">
+        <v>930</v>
+      </c>
+      <c r="E33" s="137" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F33" s="139">
+        <f>IF(AND(ISNUMBER(B33),ISNUMBER(D33),N(D33)&gt;0),ROUNDUP(B33/D33,0),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="139">
+        <f>IF(F33="","",N(G32)+IF(E33="Y",F33,0))</f>
+        <v/>
+      </c>
+      <c r="H33" s="139">
+        <f>IF(G33="","",IF(G33=0,0,IF(G33&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G33,$K$58:$K$117,1))+(G33-INDEX($K$58:$K$117,MATCH(G33,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G33,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G33,$K$58:$K$117,1)))))</f>
+        <v/>
+      </c>
+      <c r="I33" s="139">
+        <f>IF(F33="","",IF(E33="Y",IF(ISNUMBER(H33),ROUND(H33-N(H32),1),"기간초과"),"-"))</f>
+        <v/>
+      </c>
+      <c r="J33" s="139">
+        <f>IF(ISNUMBER(I33),ROUND(I33-F33,1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="137" t="n"/>
+      <c r="B34" s="137" t="n"/>
+      <c r="C34" s="137" t="n"/>
+      <c r="D34" s="137" t="n"/>
+      <c r="E34" s="137" t="n"/>
+      <c r="F34" s="139">
+        <f>IF(AND(ISNUMBER(B34),ISNUMBER(D34),N(D34)&gt;0),ROUNDUP(B34/D34,0),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="139">
+        <f>IF(F34="","",N(G33)+IF(E34="Y",F34,0))</f>
+        <v/>
+      </c>
+      <c r="H34" s="139">
+        <f>IF(G34="","",IF(G34=0,0,IF(G34&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G34,$K$58:$K$117,1))+(G34-INDEX($K$58:$K$117,MATCH(G34,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G34,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G34,$K$58:$K$117,1)))))</f>
+        <v/>
+      </c>
+      <c r="I34" s="139">
+        <f>IF(F34="","",IF(E34="Y",IF(ISNUMBER(H34),ROUND(H34-N(H33),1),"기간초과"),"-"))</f>
+        <v/>
+      </c>
+      <c r="J34" s="139">
+        <f>IF(ISNUMBER(I34),ROUND(I34-F34,1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="137" t="n"/>
+      <c r="B35" s="137" t="n"/>
+      <c r="C35" s="137" t="n"/>
+      <c r="D35" s="137" t="n"/>
+      <c r="E35" s="137" t="n"/>
+      <c r="F35" s="139">
+        <f>IF(AND(ISNUMBER(B35),ISNUMBER(D35),N(D35)&gt;0),ROUNDUP(B35/D35,0),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="139">
+        <f>IF(F35="","",N(G34)+IF(E35="Y",F35,0))</f>
+        <v/>
+      </c>
+      <c r="H35" s="139">
+        <f>IF(G35="","",IF(G35=0,0,IF(G35&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G35,$K$58:$K$117,1))+(G35-INDEX($K$58:$K$117,MATCH(G35,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G35,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G35,$K$58:$K$117,1)))))</f>
+        <v/>
+      </c>
+      <c r="I35" s="139">
+        <f>IF(F35="","",IF(E35="Y",IF(ISNUMBER(H35),ROUND(H35-N(H34),1),"기간초과"),"-"))</f>
+        <v/>
+      </c>
+      <c r="J35" s="139">
+        <f>IF(ISNUMBER(I35),ROUND(I35-F35,1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="137" t="n"/>
+      <c r="B36" s="137" t="n"/>
+      <c r="C36" s="137" t="n"/>
+      <c r="D36" s="137" t="n"/>
+      <c r="E36" s="137" t="n"/>
+      <c r="F36" s="139">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(D36),N(D36)&gt;0),ROUNDUP(B36/D36,0),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="139">
+        <f>IF(F36="","",N(G35)+IF(E36="Y",F36,0))</f>
+        <v/>
+      </c>
+      <c r="H36" s="139">
+        <f>IF(G36="","",IF(G36=0,0,IF(G36&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G36,$K$58:$K$117,1))+(G36-INDEX($K$58:$K$117,MATCH(G36,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G36,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G36,$K$58:$K$117,1)))))</f>
+        <v/>
+      </c>
+      <c r="I36" s="139">
+        <f>IF(F36="","",IF(E36="Y",IF(ISNUMBER(H36),ROUND(H36-N(H35),1),"기간초과"),"-"))</f>
+        <v/>
+      </c>
+      <c r="J36" s="139">
+        <f>IF(ISNUMBER(I36),ROUND(I36-F36,1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="137" t="n"/>
+      <c r="B37" s="137" t="n"/>
+      <c r="C37" s="137" t="n"/>
+      <c r="D37" s="137" t="n"/>
+      <c r="E37" s="137" t="n"/>
+      <c r="F37" s="139">
+        <f>IF(AND(ISNUMBER(B37),ISNUMBER(D37),N(D37)&gt;0),ROUNDUP(B37/D37,0),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="139">
+        <f>IF(F37="","",N(G36)+IF(E37="Y",F37,0))</f>
+        <v/>
+      </c>
+      <c r="H37" s="139">
+        <f>IF(G37="","",IF(G37=0,0,IF(G37&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G37,$K$58:$K$117,1))+(G37-INDEX($K$58:$K$117,MATCH(G37,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G37,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G37,$K$58:$K$117,1)))))</f>
+        <v/>
+      </c>
+      <c r="I37" s="139">
+        <f>IF(F37="","",IF(E37="Y",IF(ISNUMBER(H37),ROUND(H37-N(H36),1),"기간초과"),"-"))</f>
+        <v/>
+      </c>
+      <c r="J37" s="139">
+        <f>IF(ISNUMBER(I37),ROUND(I37-F37,1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="137" t="n"/>
+      <c r="B38" s="137" t="n"/>
+      <c r="C38" s="137" t="n"/>
+      <c r="D38" s="137" t="n"/>
+      <c r="E38" s="137" t="n"/>
+      <c r="F38" s="139">
+        <f>IF(AND(ISNUMBER(B38),ISNUMBER(D38),N(D38)&gt;0),ROUNDUP(B38/D38,0),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="139">
+        <f>IF(F38="","",N(G37)+IF(E38="Y",F38,0))</f>
+        <v/>
+      </c>
+      <c r="H38" s="139">
+        <f>IF(G38="","",IF(G38=0,0,IF(G38&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G38,$K$58:$K$117,1))+(G38-INDEX($K$58:$K$117,MATCH(G38,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G38,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G38,$K$58:$K$117,1)))))</f>
+        <v/>
+      </c>
+      <c r="I38" s="139">
+        <f>IF(F38="","",IF(E38="Y",IF(ISNUMBER(H38),ROUND(H38-N(H37),1),"기간초과"),"-"))</f>
+        <v/>
+      </c>
+      <c r="J38" s="139">
+        <f>IF(ISNUMBER(I38),ROUND(I38-F38,1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="137" t="n"/>
+      <c r="B39" s="137" t="n"/>
+      <c r="C39" s="137" t="n"/>
+      <c r="D39" s="137" t="n"/>
+      <c r="E39" s="137" t="n"/>
+      <c r="F39" s="139">
+        <f>IF(AND(ISNUMBER(B39),ISNUMBER(D39),N(D39)&gt;0),ROUNDUP(B39/D39,0),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="139">
+        <f>IF(F39="","",N(G38)+IF(E39="Y",F39,0))</f>
+        <v/>
+      </c>
+      <c r="H39" s="139">
+        <f>IF(G39="","",IF(G39=0,0,IF(G39&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G39,$K$58:$K$117,1))+(G39-INDEX($K$58:$K$117,MATCH(G39,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G39,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G39,$K$58:$K$117,1)))))</f>
+        <v/>
+      </c>
+      <c r="I39" s="139">
+        <f>IF(F39="","",IF(E39="Y",IF(ISNUMBER(H39),ROUND(H39-N(H38),1),"기간초과"),"-"))</f>
+        <v/>
+      </c>
+      <c r="J39" s="139">
+        <f>IF(ISNUMBER(I39),ROUND(I39-F39,1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="137" t="n"/>
+      <c r="B40" s="137" t="n"/>
+      <c r="C40" s="137" t="n"/>
+      <c r="D40" s="137" t="n"/>
+      <c r="E40" s="137" t="n"/>
+      <c r="F40" s="139">
+        <f>IF(AND(ISNUMBER(B40),ISNUMBER(D40),N(D40)&gt;0),ROUNDUP(B40/D40,0),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="139">
+        <f>IF(F40="","",N(G39)+IF(E40="Y",F40,0))</f>
+        <v/>
+      </c>
+      <c r="H40" s="139">
+        <f>IF(G40="","",IF(G40=0,0,IF(G40&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G40,$K$58:$K$117,1))+(G40-INDEX($K$58:$K$117,MATCH(G40,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G40,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G40,$K$58:$K$117,1)))))</f>
+        <v/>
+      </c>
+      <c r="I40" s="139">
+        <f>IF(F40="","",IF(E40="Y",IF(ISNUMBER(H40),ROUND(H40-N(H39),1),"기간초과"),"-"))</f>
+        <v/>
+      </c>
+      <c r="J40" s="139">
+        <f>IF(ISNUMBER(I40),ROUND(I40-F40,1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="137" t="n"/>
+      <c r="B41" s="137" t="n"/>
+      <c r="C41" s="137" t="n"/>
+      <c r="D41" s="137" t="n"/>
+      <c r="E41" s="137" t="n"/>
+      <c r="F41" s="139">
+        <f>IF(AND(ISNUMBER(B41),ISNUMBER(D41),N(D41)&gt;0),ROUNDUP(B41/D41,0),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="139">
+        <f>IF(F41="","",N(G40)+IF(E41="Y",F41,0))</f>
+        <v/>
+      </c>
+      <c r="H41" s="139">
+        <f>IF(G41="","",IF(G41=0,0,IF(G41&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G41,$K$58:$K$117,1))+(G41-INDEX($K$58:$K$117,MATCH(G41,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G41,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G41,$K$58:$K$117,1)))))</f>
+        <v/>
+      </c>
+      <c r="I41" s="139">
+        <f>IF(F41="","",IF(E41="Y",IF(ISNUMBER(H41),ROUND(H41-N(H40),1),"기간초과"),"-"))</f>
+        <v/>
+      </c>
+      <c r="J41" s="139">
+        <f>IF(ISNUMBER(I41),ROUND(I41-F41,1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="137" t="n"/>
+      <c r="B42" s="137" t="n"/>
+      <c r="C42" s="137" t="n"/>
+      <c r="D42" s="137" t="n"/>
+      <c r="E42" s="137" t="n"/>
+      <c r="F42" s="139">
+        <f>IF(AND(ISNUMBER(B42),ISNUMBER(D42),N(D42)&gt;0),ROUNDUP(B42/D42,0),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="139">
+        <f>IF(F42="","",N(G41)+IF(E42="Y",F42,0))</f>
+        <v/>
+      </c>
+      <c r="H42" s="139">
+        <f>IF(G42="","",IF(G42=0,0,IF(G42&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G42,$K$58:$K$117,1))+(G42-INDEX($K$58:$K$117,MATCH(G42,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G42,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G42,$K$58:$K$117,1)))))</f>
+        <v/>
+      </c>
+      <c r="I42" s="139">
+        <f>IF(F42="","",IF(E42="Y",IF(ISNUMBER(H42),ROUND(H42-N(H41),1),"기간초과"),"-"))</f>
+        <v/>
+      </c>
+      <c r="J42" s="139">
+        <f>IF(ISNUMBER(I42),ROUND(I42-F42,1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="137" t="n"/>
+      <c r="B43" s="137" t="n"/>
+      <c r="C43" s="137" t="n"/>
+      <c r="D43" s="137" t="n"/>
+      <c r="E43" s="137" t="n"/>
+      <c r="F43" s="139">
+        <f>IF(AND(ISNUMBER(B43),ISNUMBER(D43),N(D43)&gt;0),ROUNDUP(B43/D43,0),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="139">
+        <f>IF(F43="","",N(G42)+IF(E43="Y",F43,0))</f>
+        <v/>
+      </c>
+      <c r="H43" s="139">
+        <f>IF(G43="","",IF(G43=0,0,IF(G43&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G43,$K$58:$K$117,1))+(G43-INDEX($K$58:$K$117,MATCH(G43,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G43,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G43,$K$58:$K$117,1)))))</f>
+        <v/>
+      </c>
+      <c r="I43" s="139">
+        <f>IF(F43="","",IF(E43="Y",IF(ISNUMBER(H43),ROUND(H43-N(H42),1),"기간초과"),"-"))</f>
+        <v/>
+      </c>
+      <c r="J43" s="139">
+        <f>IF(ISNUMBER(I43),ROUND(I43-F43,1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="131" t="inlineStr">
+        <is>
+          <t>▼ 결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="131" t="inlineStr">
+        <is>
+          <t>준비기간 (일)</t>
+        </is>
+      </c>
+      <c r="B46" s="138">
+        <f>B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="131" t="inlineStr">
+        <is>
+          <t>주공정 공종별 공사기간의 합 (일)</t>
+        </is>
+      </c>
+      <c r="B47" s="138">
+        <f>IFERROR(ROUNDUP(MAX(H29:H43),0),"기간초과")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="131" t="inlineStr">
+        <is>
+          <t>정리기간 (일)</t>
+        </is>
+      </c>
+      <c r="B48" s="138">
+        <f>B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="131" t="inlineStr">
+        <is>
+          <t>공사기간 A (일)</t>
+        </is>
+      </c>
+      <c r="B49" s="138">
+        <f>IF(ISNUMBER(B47),B46+B47+B48,"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="131" t="inlineStr">
+        <is>
+          <t>환산 (개월)</t>
+        </is>
+      </c>
+      <c r="B50" s="138">
+        <f>IF(ISNUMBER(B49),ROUND(B49/30,1),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="131" t="inlineStr">
+        <is>
+          <t>산정공식 공사기간 B (일) — 시설물별공기(토목)</t>
+        </is>
+      </c>
+      <c r="B51" s="138">
+        <f>'시설물별공기(토목)'!B19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="131" t="inlineStr">
+        <is>
+          <t>적정성 검토 (A가 B의 ±20% 이내인지)</t>
+        </is>
+      </c>
+      <c r="B52" s="138">
+        <f>IF(AND(ISNUMBER(B49),ISNUMBER(B51)),IF(ABS(B49/B51-1)&lt;=0.2,"±20% 이내 (적정)","±20% 초과 → 산정 과정 재검토 (편차 "&amp;TEXT(B49/B51-1,"0.0%")&amp;")"),"산정공식 적용범위 밖이거나 미입력 → 비교 생략")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="131" t="inlineStr">
+        <is>
+          <t>▼ 월별 비작업일수 계산 (착수 월부터 60개월)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="48" customHeight="1" s="92">
+      <c r="A57" s="134" t="inlineStr">
+        <is>
+          <t>순번</t>
+        </is>
+      </c>
+      <c r="B57" s="134" t="inlineStr">
+        <is>
+          <t>연도</t>
+        </is>
+      </c>
+      <c r="C57" s="134" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="D57" s="134" t="inlineStr">
+        <is>
+          <t>달력일수</t>
+        </is>
+      </c>
+      <c r="E57" s="134" t="inlineStr">
+        <is>
+          <t>법정공휴일 B</t>
+        </is>
+      </c>
+      <c r="F57" s="134" t="inlineStr">
+        <is>
+          <t>기후여건 A</t>
+        </is>
+      </c>
+      <c r="G57" s="134" t="inlineStr">
+        <is>
+          <t>중복일수 C=A×B÷달력일수</t>
+        </is>
+      </c>
+      <c r="H57" s="134" t="inlineStr">
+        <is>
+          <t>A+B-C</t>
+        </is>
+      </c>
+      <c r="I57" s="134" t="inlineStr">
+        <is>
+          <t>적용 비작업일수(월8일 이상, 정수)</t>
+        </is>
+      </c>
+      <c r="J57" s="134" t="inlineStr">
+        <is>
+          <t>작업가능일수</t>
+        </is>
+      </c>
+      <c r="K57" s="134" t="inlineStr">
+        <is>
+          <t>누적 작업가능(전월까지)</t>
+        </is>
+      </c>
+      <c r="L57" s="134" t="inlineStr">
+        <is>
+          <t>누적 달력일수(전월까지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="139" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A58-1))</f>
+        <v/>
+      </c>
+      <c r="C58" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A58-1))</f>
+        <v/>
+      </c>
+      <c r="D58" s="139">
+        <f>DAY(EOMONTH(DATE(B58,C58,1),0))</f>
+        <v/>
+      </c>
+      <c r="E58" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B58,법정공휴일!$A$4:$A$20,0),C58),0)</f>
+        <v/>
+      </c>
+      <c r="F58" s="139">
+        <f>INDEX($D$25:$O$25,C58)</f>
+        <v/>
+      </c>
+      <c r="G58" s="139">
+        <f>ROUND(F58*E58/D58,1)</f>
+        <v/>
+      </c>
+      <c r="H58" s="139">
+        <f>F58+E58-G58</f>
+        <v/>
+      </c>
+      <c r="I58" s="139">
+        <f>ROUND(MAX(H58,8),0)</f>
+        <v/>
+      </c>
+      <c r="J58" s="139">
+        <f>D58-I58</f>
+        <v/>
+      </c>
+      <c r="K58" s="139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="139" t="n">
+        <v>2</v>
+      </c>
+      <c r="B59" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A59-1))</f>
+        <v/>
+      </c>
+      <c r="C59" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A59-1))</f>
+        <v/>
+      </c>
+      <c r="D59" s="139">
+        <f>DAY(EOMONTH(DATE(B59,C59,1),0))</f>
+        <v/>
+      </c>
+      <c r="E59" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B59,법정공휴일!$A$4:$A$20,0),C59),0)</f>
+        <v/>
+      </c>
+      <c r="F59" s="139">
+        <f>INDEX($D$25:$O$25,C59)</f>
+        <v/>
+      </c>
+      <c r="G59" s="139">
+        <f>ROUND(F59*E59/D59,1)</f>
+        <v/>
+      </c>
+      <c r="H59" s="139">
+        <f>F59+E59-G59</f>
+        <v/>
+      </c>
+      <c r="I59" s="139">
+        <f>ROUND(MAX(H59,8),0)</f>
+        <v/>
+      </c>
+      <c r="J59" s="139">
+        <f>D59-I59</f>
+        <v/>
+      </c>
+      <c r="K59" s="139">
+        <f>K58+J58</f>
+        <v/>
+      </c>
+      <c r="L59" s="139">
+        <f>L58+D58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="139" t="n">
+        <v>3</v>
+      </c>
+      <c r="B60" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A60-1))</f>
+        <v/>
+      </c>
+      <c r="C60" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A60-1))</f>
+        <v/>
+      </c>
+      <c r="D60" s="139">
+        <f>DAY(EOMONTH(DATE(B60,C60,1),0))</f>
+        <v/>
+      </c>
+      <c r="E60" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B60,법정공휴일!$A$4:$A$20,0),C60),0)</f>
+        <v/>
+      </c>
+      <c r="F60" s="139">
+        <f>INDEX($D$25:$O$25,C60)</f>
+        <v/>
+      </c>
+      <c r="G60" s="139">
+        <f>ROUND(F60*E60/D60,1)</f>
+        <v/>
+      </c>
+      <c r="H60" s="139">
+        <f>F60+E60-G60</f>
+        <v/>
+      </c>
+      <c r="I60" s="139">
+        <f>ROUND(MAX(H60,8),0)</f>
+        <v/>
+      </c>
+      <c r="J60" s="139">
+        <f>D60-I60</f>
+        <v/>
+      </c>
+      <c r="K60" s="139">
+        <f>K59+J59</f>
+        <v/>
+      </c>
+      <c r="L60" s="139">
+        <f>L59+D59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="139" t="n">
+        <v>4</v>
+      </c>
+      <c r="B61" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A61-1))</f>
+        <v/>
+      </c>
+      <c r="C61" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A61-1))</f>
+        <v/>
+      </c>
+      <c r="D61" s="139">
+        <f>DAY(EOMONTH(DATE(B61,C61,1),0))</f>
+        <v/>
+      </c>
+      <c r="E61" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B61,법정공휴일!$A$4:$A$20,0),C61),0)</f>
+        <v/>
+      </c>
+      <c r="F61" s="139">
+        <f>INDEX($D$25:$O$25,C61)</f>
+        <v/>
+      </c>
+      <c r="G61" s="139">
+        <f>ROUND(F61*E61/D61,1)</f>
+        <v/>
+      </c>
+      <c r="H61" s="139">
+        <f>F61+E61-G61</f>
+        <v/>
+      </c>
+      <c r="I61" s="139">
+        <f>ROUND(MAX(H61,8),0)</f>
+        <v/>
+      </c>
+      <c r="J61" s="139">
+        <f>D61-I61</f>
+        <v/>
+      </c>
+      <c r="K61" s="139">
+        <f>K60+J60</f>
+        <v/>
+      </c>
+      <c r="L61" s="139">
+        <f>L60+D60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="139" t="n">
+        <v>5</v>
+      </c>
+      <c r="B62" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A62-1))</f>
+        <v/>
+      </c>
+      <c r="C62" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A62-1))</f>
+        <v/>
+      </c>
+      <c r="D62" s="139">
+        <f>DAY(EOMONTH(DATE(B62,C62,1),0))</f>
+        <v/>
+      </c>
+      <c r="E62" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B62,법정공휴일!$A$4:$A$20,0),C62),0)</f>
+        <v/>
+      </c>
+      <c r="F62" s="139">
+        <f>INDEX($D$25:$O$25,C62)</f>
+        <v/>
+      </c>
+      <c r="G62" s="139">
+        <f>ROUND(F62*E62/D62,1)</f>
+        <v/>
+      </c>
+      <c r="H62" s="139">
+        <f>F62+E62-G62</f>
+        <v/>
+      </c>
+      <c r="I62" s="139">
+        <f>ROUND(MAX(H62,8),0)</f>
+        <v/>
+      </c>
+      <c r="J62" s="139">
+        <f>D62-I62</f>
+        <v/>
+      </c>
+      <c r="K62" s="139">
+        <f>K61+J61</f>
+        <v/>
+      </c>
+      <c r="L62" s="139">
+        <f>L61+D61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="139" t="n">
+        <v>6</v>
+      </c>
+      <c r="B63" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A63-1))</f>
+        <v/>
+      </c>
+      <c r="C63" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A63-1))</f>
+        <v/>
+      </c>
+      <c r="D63" s="139">
+        <f>DAY(EOMONTH(DATE(B63,C63,1),0))</f>
+        <v/>
+      </c>
+      <c r="E63" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B63,법정공휴일!$A$4:$A$20,0),C63),0)</f>
+        <v/>
+      </c>
+      <c r="F63" s="139">
+        <f>INDEX($D$25:$O$25,C63)</f>
+        <v/>
+      </c>
+      <c r="G63" s="139">
+        <f>ROUND(F63*E63/D63,1)</f>
+        <v/>
+      </c>
+      <c r="H63" s="139">
+        <f>F63+E63-G63</f>
+        <v/>
+      </c>
+      <c r="I63" s="139">
+        <f>ROUND(MAX(H63,8),0)</f>
+        <v/>
+      </c>
+      <c r="J63" s="139">
+        <f>D63-I63</f>
+        <v/>
+      </c>
+      <c r="K63" s="139">
+        <f>K62+J62</f>
+        <v/>
+      </c>
+      <c r="L63" s="139">
+        <f>L62+D62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="139" t="n">
+        <v>7</v>
+      </c>
+      <c r="B64" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A64-1))</f>
+        <v/>
+      </c>
+      <c r="C64" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A64-1))</f>
+        <v/>
+      </c>
+      <c r="D64" s="139">
+        <f>DAY(EOMONTH(DATE(B64,C64,1),0))</f>
+        <v/>
+      </c>
+      <c r="E64" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B64,법정공휴일!$A$4:$A$20,0),C64),0)</f>
+        <v/>
+      </c>
+      <c r="F64" s="139">
+        <f>INDEX($D$25:$O$25,C64)</f>
+        <v/>
+      </c>
+      <c r="G64" s="139">
+        <f>ROUND(F64*E64/D64,1)</f>
+        <v/>
+      </c>
+      <c r="H64" s="139">
+        <f>F64+E64-G64</f>
+        <v/>
+      </c>
+      <c r="I64" s="139">
+        <f>ROUND(MAX(H64,8),0)</f>
+        <v/>
+      </c>
+      <c r="J64" s="139">
+        <f>D64-I64</f>
+        <v/>
+      </c>
+      <c r="K64" s="139">
+        <f>K63+J63</f>
+        <v/>
+      </c>
+      <c r="L64" s="139">
+        <f>L63+D63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="139" t="n">
+        <v>8</v>
+      </c>
+      <c r="B65" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A65-1))</f>
+        <v/>
+      </c>
+      <c r="C65" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A65-1))</f>
+        <v/>
+      </c>
+      <c r="D65" s="139">
+        <f>DAY(EOMONTH(DATE(B65,C65,1),0))</f>
+        <v/>
+      </c>
+      <c r="E65" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B65,법정공휴일!$A$4:$A$20,0),C65),0)</f>
+        <v/>
+      </c>
+      <c r="F65" s="139">
+        <f>INDEX($D$25:$O$25,C65)</f>
+        <v/>
+      </c>
+      <c r="G65" s="139">
+        <f>ROUND(F65*E65/D65,1)</f>
+        <v/>
+      </c>
+      <c r="H65" s="139">
+        <f>F65+E65-G65</f>
+        <v/>
+      </c>
+      <c r="I65" s="139">
+        <f>ROUND(MAX(H65,8),0)</f>
+        <v/>
+      </c>
+      <c r="J65" s="139">
+        <f>D65-I65</f>
+        <v/>
+      </c>
+      <c r="K65" s="139">
+        <f>K64+J64</f>
+        <v/>
+      </c>
+      <c r="L65" s="139">
+        <f>L64+D64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="139" t="n">
+        <v>9</v>
+      </c>
+      <c r="B66" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A66-1))</f>
+        <v/>
+      </c>
+      <c r="C66" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A66-1))</f>
+        <v/>
+      </c>
+      <c r="D66" s="139">
+        <f>DAY(EOMONTH(DATE(B66,C66,1),0))</f>
+        <v/>
+      </c>
+      <c r="E66" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B66,법정공휴일!$A$4:$A$20,0),C66),0)</f>
+        <v/>
+      </c>
+      <c r="F66" s="139">
+        <f>INDEX($D$25:$O$25,C66)</f>
+        <v/>
+      </c>
+      <c r="G66" s="139">
+        <f>ROUND(F66*E66/D66,1)</f>
+        <v/>
+      </c>
+      <c r="H66" s="139">
+        <f>F66+E66-G66</f>
+        <v/>
+      </c>
+      <c r="I66" s="139">
+        <f>ROUND(MAX(H66,8),0)</f>
+        <v/>
+      </c>
+      <c r="J66" s="139">
+        <f>D66-I66</f>
+        <v/>
+      </c>
+      <c r="K66" s="139">
+        <f>K65+J65</f>
+        <v/>
+      </c>
+      <c r="L66" s="139">
+        <f>L65+D65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="139" t="n">
+        <v>10</v>
+      </c>
+      <c r="B67" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A67-1))</f>
+        <v/>
+      </c>
+      <c r="C67" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A67-1))</f>
+        <v/>
+      </c>
+      <c r="D67" s="139">
+        <f>DAY(EOMONTH(DATE(B67,C67,1),0))</f>
+        <v/>
+      </c>
+      <c r="E67" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B67,법정공휴일!$A$4:$A$20,0),C67),0)</f>
+        <v/>
+      </c>
+      <c r="F67" s="139">
+        <f>INDEX($D$25:$O$25,C67)</f>
+        <v/>
+      </c>
+      <c r="G67" s="139">
+        <f>ROUND(F67*E67/D67,1)</f>
+        <v/>
+      </c>
+      <c r="H67" s="139">
+        <f>F67+E67-G67</f>
+        <v/>
+      </c>
+      <c r="I67" s="139">
+        <f>ROUND(MAX(H67,8),0)</f>
+        <v/>
+      </c>
+      <c r="J67" s="139">
+        <f>D67-I67</f>
+        <v/>
+      </c>
+      <c r="K67" s="139">
+        <f>K66+J66</f>
+        <v/>
+      </c>
+      <c r="L67" s="139">
+        <f>L66+D66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="139" t="n">
+        <v>11</v>
+      </c>
+      <c r="B68" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A68-1))</f>
+        <v/>
+      </c>
+      <c r="C68" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A68-1))</f>
+        <v/>
+      </c>
+      <c r="D68" s="139">
+        <f>DAY(EOMONTH(DATE(B68,C68,1),0))</f>
+        <v/>
+      </c>
+      <c r="E68" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B68,법정공휴일!$A$4:$A$20,0),C68),0)</f>
+        <v/>
+      </c>
+      <c r="F68" s="139">
+        <f>INDEX($D$25:$O$25,C68)</f>
+        <v/>
+      </c>
+      <c r="G68" s="139">
+        <f>ROUND(F68*E68/D68,1)</f>
+        <v/>
+      </c>
+      <c r="H68" s="139">
+        <f>F68+E68-G68</f>
+        <v/>
+      </c>
+      <c r="I68" s="139">
+        <f>ROUND(MAX(H68,8),0)</f>
+        <v/>
+      </c>
+      <c r="J68" s="139">
+        <f>D68-I68</f>
+        <v/>
+      </c>
+      <c r="K68" s="139">
+        <f>K67+J67</f>
+        <v/>
+      </c>
+      <c r="L68" s="139">
+        <f>L67+D67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="139" t="n">
+        <v>12</v>
+      </c>
+      <c r="B69" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A69-1))</f>
+        <v/>
+      </c>
+      <c r="C69" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A69-1))</f>
+        <v/>
+      </c>
+      <c r="D69" s="139">
+        <f>DAY(EOMONTH(DATE(B69,C69,1),0))</f>
+        <v/>
+      </c>
+      <c r="E69" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B69,법정공휴일!$A$4:$A$20,0),C69),0)</f>
+        <v/>
+      </c>
+      <c r="F69" s="139">
+        <f>INDEX($D$25:$O$25,C69)</f>
+        <v/>
+      </c>
+      <c r="G69" s="139">
+        <f>ROUND(F69*E69/D69,1)</f>
+        <v/>
+      </c>
+      <c r="H69" s="139">
+        <f>F69+E69-G69</f>
+        <v/>
+      </c>
+      <c r="I69" s="139">
+        <f>ROUND(MAX(H69,8),0)</f>
+        <v/>
+      </c>
+      <c r="J69" s="139">
+        <f>D69-I69</f>
+        <v/>
+      </c>
+      <c r="K69" s="139">
+        <f>K68+J68</f>
+        <v/>
+      </c>
+      <c r="L69" s="139">
+        <f>L68+D68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="139" t="n">
+        <v>13</v>
+      </c>
+      <c r="B70" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A70-1))</f>
+        <v/>
+      </c>
+      <c r="C70" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A70-1))</f>
+        <v/>
+      </c>
+      <c r="D70" s="139">
+        <f>DAY(EOMONTH(DATE(B70,C70,1),0))</f>
+        <v/>
+      </c>
+      <c r="E70" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B70,법정공휴일!$A$4:$A$20,0),C70),0)</f>
+        <v/>
+      </c>
+      <c r="F70" s="139">
+        <f>INDEX($D$25:$O$25,C70)</f>
+        <v/>
+      </c>
+      <c r="G70" s="139">
+        <f>ROUND(F70*E70/D70,1)</f>
+        <v/>
+      </c>
+      <c r="H70" s="139">
+        <f>F70+E70-G70</f>
+        <v/>
+      </c>
+      <c r="I70" s="139">
+        <f>ROUND(MAX(H70,8),0)</f>
+        <v/>
+      </c>
+      <c r="J70" s="139">
+        <f>D70-I70</f>
+        <v/>
+      </c>
+      <c r="K70" s="139">
+        <f>K69+J69</f>
+        <v/>
+      </c>
+      <c r="L70" s="139">
+        <f>L69+D69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="139" t="n">
+        <v>14</v>
+      </c>
+      <c r="B71" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A71-1))</f>
+        <v/>
+      </c>
+      <c r="C71" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A71-1))</f>
+        <v/>
+      </c>
+      <c r="D71" s="139">
+        <f>DAY(EOMONTH(DATE(B71,C71,1),0))</f>
+        <v/>
+      </c>
+      <c r="E71" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B71,법정공휴일!$A$4:$A$20,0),C71),0)</f>
+        <v/>
+      </c>
+      <c r="F71" s="139">
+        <f>INDEX($D$25:$O$25,C71)</f>
+        <v/>
+      </c>
+      <c r="G71" s="139">
+        <f>ROUND(F71*E71/D71,1)</f>
+        <v/>
+      </c>
+      <c r="H71" s="139">
+        <f>F71+E71-G71</f>
+        <v/>
+      </c>
+      <c r="I71" s="139">
+        <f>ROUND(MAX(H71,8),0)</f>
+        <v/>
+      </c>
+      <c r="J71" s="139">
+        <f>D71-I71</f>
+        <v/>
+      </c>
+      <c r="K71" s="139">
+        <f>K70+J70</f>
+        <v/>
+      </c>
+      <c r="L71" s="139">
+        <f>L70+D70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="139" t="n">
+        <v>15</v>
+      </c>
+      <c r="B72" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A72-1))</f>
+        <v/>
+      </c>
+      <c r="C72" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A72-1))</f>
+        <v/>
+      </c>
+      <c r="D72" s="139">
+        <f>DAY(EOMONTH(DATE(B72,C72,1),0))</f>
+        <v/>
+      </c>
+      <c r="E72" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B72,법정공휴일!$A$4:$A$20,0),C72),0)</f>
+        <v/>
+      </c>
+      <c r="F72" s="139">
+        <f>INDEX($D$25:$O$25,C72)</f>
+        <v/>
+      </c>
+      <c r="G72" s="139">
+        <f>ROUND(F72*E72/D72,1)</f>
+        <v/>
+      </c>
+      <c r="H72" s="139">
+        <f>F72+E72-G72</f>
+        <v/>
+      </c>
+      <c r="I72" s="139">
+        <f>ROUND(MAX(H72,8),0)</f>
+        <v/>
+      </c>
+      <c r="J72" s="139">
+        <f>D72-I72</f>
+        <v/>
+      </c>
+      <c r="K72" s="139">
+        <f>K71+J71</f>
+        <v/>
+      </c>
+      <c r="L72" s="139">
+        <f>L71+D71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="139" t="n">
+        <v>16</v>
+      </c>
+      <c r="B73" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A73-1))</f>
+        <v/>
+      </c>
+      <c r="C73" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A73-1))</f>
+        <v/>
+      </c>
+      <c r="D73" s="139">
+        <f>DAY(EOMONTH(DATE(B73,C73,1),0))</f>
+        <v/>
+      </c>
+      <c r="E73" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B73,법정공휴일!$A$4:$A$20,0),C73),0)</f>
+        <v/>
+      </c>
+      <c r="F73" s="139">
+        <f>INDEX($D$25:$O$25,C73)</f>
+        <v/>
+      </c>
+      <c r="G73" s="139">
+        <f>ROUND(F73*E73/D73,1)</f>
+        <v/>
+      </c>
+      <c r="H73" s="139">
+        <f>F73+E73-G73</f>
+        <v/>
+      </c>
+      <c r="I73" s="139">
+        <f>ROUND(MAX(H73,8),0)</f>
+        <v/>
+      </c>
+      <c r="J73" s="139">
+        <f>D73-I73</f>
+        <v/>
+      </c>
+      <c r="K73" s="139">
+        <f>K72+J72</f>
+        <v/>
+      </c>
+      <c r="L73" s="139">
+        <f>L72+D72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="139" t="n">
+        <v>17</v>
+      </c>
+      <c r="B74" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A74-1))</f>
+        <v/>
+      </c>
+      <c r="C74" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A74-1))</f>
+        <v/>
+      </c>
+      <c r="D74" s="139">
+        <f>DAY(EOMONTH(DATE(B74,C74,1),0))</f>
+        <v/>
+      </c>
+      <c r="E74" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B74,법정공휴일!$A$4:$A$20,0),C74),0)</f>
+        <v/>
+      </c>
+      <c r="F74" s="139">
+        <f>INDEX($D$25:$O$25,C74)</f>
+        <v/>
+      </c>
+      <c r="G74" s="139">
+        <f>ROUND(F74*E74/D74,1)</f>
+        <v/>
+      </c>
+      <c r="H74" s="139">
+        <f>F74+E74-G74</f>
+        <v/>
+      </c>
+      <c r="I74" s="139">
+        <f>ROUND(MAX(H74,8),0)</f>
+        <v/>
+      </c>
+      <c r="J74" s="139">
+        <f>D74-I74</f>
+        <v/>
+      </c>
+      <c r="K74" s="139">
+        <f>K73+J73</f>
+        <v/>
+      </c>
+      <c r="L74" s="139">
+        <f>L73+D73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="139" t="n">
+        <v>18</v>
+      </c>
+      <c r="B75" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A75-1))</f>
+        <v/>
+      </c>
+      <c r="C75" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A75-1))</f>
+        <v/>
+      </c>
+      <c r="D75" s="139">
+        <f>DAY(EOMONTH(DATE(B75,C75,1),0))</f>
+        <v/>
+      </c>
+      <c r="E75" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B75,법정공휴일!$A$4:$A$20,0),C75),0)</f>
+        <v/>
+      </c>
+      <c r="F75" s="139">
+        <f>INDEX($D$25:$O$25,C75)</f>
+        <v/>
+      </c>
+      <c r="G75" s="139">
+        <f>ROUND(F75*E75/D75,1)</f>
+        <v/>
+      </c>
+      <c r="H75" s="139">
+        <f>F75+E75-G75</f>
+        <v/>
+      </c>
+      <c r="I75" s="139">
+        <f>ROUND(MAX(H75,8),0)</f>
+        <v/>
+      </c>
+      <c r="J75" s="139">
+        <f>D75-I75</f>
+        <v/>
+      </c>
+      <c r="K75" s="139">
+        <f>K74+J74</f>
+        <v/>
+      </c>
+      <c r="L75" s="139">
+        <f>L74+D74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="139" t="n">
+        <v>19</v>
+      </c>
+      <c r="B76" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A76-1))</f>
+        <v/>
+      </c>
+      <c r="C76" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A76-1))</f>
+        <v/>
+      </c>
+      <c r="D76" s="139">
+        <f>DAY(EOMONTH(DATE(B76,C76,1),0))</f>
+        <v/>
+      </c>
+      <c r="E76" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B76,법정공휴일!$A$4:$A$20,0),C76),0)</f>
+        <v/>
+      </c>
+      <c r="F76" s="139">
+        <f>INDEX($D$25:$O$25,C76)</f>
+        <v/>
+      </c>
+      <c r="G76" s="139">
+        <f>ROUND(F76*E76/D76,1)</f>
+        <v/>
+      </c>
+      <c r="H76" s="139">
+        <f>F76+E76-G76</f>
+        <v/>
+      </c>
+      <c r="I76" s="139">
+        <f>ROUND(MAX(H76,8),0)</f>
+        <v/>
+      </c>
+      <c r="J76" s="139">
+        <f>D76-I76</f>
+        <v/>
+      </c>
+      <c r="K76" s="139">
+        <f>K75+J75</f>
+        <v/>
+      </c>
+      <c r="L76" s="139">
+        <f>L75+D75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="139" t="n">
+        <v>20</v>
+      </c>
+      <c r="B77" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A77-1))</f>
+        <v/>
+      </c>
+      <c r="C77" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A77-1))</f>
+        <v/>
+      </c>
+      <c r="D77" s="139">
+        <f>DAY(EOMONTH(DATE(B77,C77,1),0))</f>
+        <v/>
+      </c>
+      <c r="E77" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B77,법정공휴일!$A$4:$A$20,0),C77),0)</f>
+        <v/>
+      </c>
+      <c r="F77" s="139">
+        <f>INDEX($D$25:$O$25,C77)</f>
+        <v/>
+      </c>
+      <c r="G77" s="139">
+        <f>ROUND(F77*E77/D77,1)</f>
+        <v/>
+      </c>
+      <c r="H77" s="139">
+        <f>F77+E77-G77</f>
+        <v/>
+      </c>
+      <c r="I77" s="139">
+        <f>ROUND(MAX(H77,8),0)</f>
+        <v/>
+      </c>
+      <c r="J77" s="139">
+        <f>D77-I77</f>
+        <v/>
+      </c>
+      <c r="K77" s="139">
+        <f>K76+J76</f>
+        <v/>
+      </c>
+      <c r="L77" s="139">
+        <f>L76+D76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="139" t="n">
+        <v>21</v>
+      </c>
+      <c r="B78" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A78-1))</f>
+        <v/>
+      </c>
+      <c r="C78" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A78-1))</f>
+        <v/>
+      </c>
+      <c r="D78" s="139">
+        <f>DAY(EOMONTH(DATE(B78,C78,1),0))</f>
+        <v/>
+      </c>
+      <c r="E78" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B78,법정공휴일!$A$4:$A$20,0),C78),0)</f>
+        <v/>
+      </c>
+      <c r="F78" s="139">
+        <f>INDEX($D$25:$O$25,C78)</f>
+        <v/>
+      </c>
+      <c r="G78" s="139">
+        <f>ROUND(F78*E78/D78,1)</f>
+        <v/>
+      </c>
+      <c r="H78" s="139">
+        <f>F78+E78-G78</f>
+        <v/>
+      </c>
+      <c r="I78" s="139">
+        <f>ROUND(MAX(H78,8),0)</f>
+        <v/>
+      </c>
+      <c r="J78" s="139">
+        <f>D78-I78</f>
+        <v/>
+      </c>
+      <c r="K78" s="139">
+        <f>K77+J77</f>
+        <v/>
+      </c>
+      <c r="L78" s="139">
+        <f>L77+D77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="139" t="n">
+        <v>22</v>
+      </c>
+      <c r="B79" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A79-1))</f>
+        <v/>
+      </c>
+      <c r="C79" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A79-1))</f>
+        <v/>
+      </c>
+      <c r="D79" s="139">
+        <f>DAY(EOMONTH(DATE(B79,C79,1),0))</f>
+        <v/>
+      </c>
+      <c r="E79" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B79,법정공휴일!$A$4:$A$20,0),C79),0)</f>
+        <v/>
+      </c>
+      <c r="F79" s="139">
+        <f>INDEX($D$25:$O$25,C79)</f>
+        <v/>
+      </c>
+      <c r="G79" s="139">
+        <f>ROUND(F79*E79/D79,1)</f>
+        <v/>
+      </c>
+      <c r="H79" s="139">
+        <f>F79+E79-G79</f>
+        <v/>
+      </c>
+      <c r="I79" s="139">
+        <f>ROUND(MAX(H79,8),0)</f>
+        <v/>
+      </c>
+      <c r="J79" s="139">
+        <f>D79-I79</f>
+        <v/>
+      </c>
+      <c r="K79" s="139">
+        <f>K78+J78</f>
+        <v/>
+      </c>
+      <c r="L79" s="139">
+        <f>L78+D78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="139" t="n">
+        <v>23</v>
+      </c>
+      <c r="B80" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A80-1))</f>
+        <v/>
+      </c>
+      <c r="C80" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A80-1))</f>
+        <v/>
+      </c>
+      <c r="D80" s="139">
+        <f>DAY(EOMONTH(DATE(B80,C80,1),0))</f>
+        <v/>
+      </c>
+      <c r="E80" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B80,법정공휴일!$A$4:$A$20,0),C80),0)</f>
+        <v/>
+      </c>
+      <c r="F80" s="139">
+        <f>INDEX($D$25:$O$25,C80)</f>
+        <v/>
+      </c>
+      <c r="G80" s="139">
+        <f>ROUND(F80*E80/D80,1)</f>
+        <v/>
+      </c>
+      <c r="H80" s="139">
+        <f>F80+E80-G80</f>
+        <v/>
+      </c>
+      <c r="I80" s="139">
+        <f>ROUND(MAX(H80,8),0)</f>
+        <v/>
+      </c>
+      <c r="J80" s="139">
+        <f>D80-I80</f>
+        <v/>
+      </c>
+      <c r="K80" s="139">
+        <f>K79+J79</f>
+        <v/>
+      </c>
+      <c r="L80" s="139">
+        <f>L79+D79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="139" t="n">
+        <v>24</v>
+      </c>
+      <c r="B81" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A81-1))</f>
+        <v/>
+      </c>
+      <c r="C81" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A81-1))</f>
+        <v/>
+      </c>
+      <c r="D81" s="139">
+        <f>DAY(EOMONTH(DATE(B81,C81,1),0))</f>
+        <v/>
+      </c>
+      <c r="E81" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B81,법정공휴일!$A$4:$A$20,0),C81),0)</f>
+        <v/>
+      </c>
+      <c r="F81" s="139">
+        <f>INDEX($D$25:$O$25,C81)</f>
+        <v/>
+      </c>
+      <c r="G81" s="139">
+        <f>ROUND(F81*E81/D81,1)</f>
+        <v/>
+      </c>
+      <c r="H81" s="139">
+        <f>F81+E81-G81</f>
+        <v/>
+      </c>
+      <c r="I81" s="139">
+        <f>ROUND(MAX(H81,8),0)</f>
+        <v/>
+      </c>
+      <c r="J81" s="139">
+        <f>D81-I81</f>
+        <v/>
+      </c>
+      <c r="K81" s="139">
+        <f>K80+J80</f>
+        <v/>
+      </c>
+      <c r="L81" s="139">
+        <f>L80+D80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="139" t="n">
+        <v>25</v>
+      </c>
+      <c r="B82" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A82-1))</f>
+        <v/>
+      </c>
+      <c r="C82" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A82-1))</f>
+        <v/>
+      </c>
+      <c r="D82" s="139">
+        <f>DAY(EOMONTH(DATE(B82,C82,1),0))</f>
+        <v/>
+      </c>
+      <c r="E82" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B82,법정공휴일!$A$4:$A$20,0),C82),0)</f>
+        <v/>
+      </c>
+      <c r="F82" s="139">
+        <f>INDEX($D$25:$O$25,C82)</f>
+        <v/>
+      </c>
+      <c r="G82" s="139">
+        <f>ROUND(F82*E82/D82,1)</f>
+        <v/>
+      </c>
+      <c r="H82" s="139">
+        <f>F82+E82-G82</f>
+        <v/>
+      </c>
+      <c r="I82" s="139">
+        <f>ROUND(MAX(H82,8),0)</f>
+        <v/>
+      </c>
+      <c r="J82" s="139">
+        <f>D82-I82</f>
+        <v/>
+      </c>
+      <c r="K82" s="139">
+        <f>K81+J81</f>
+        <v/>
+      </c>
+      <c r="L82" s="139">
+        <f>L81+D81</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="139" t="n">
+        <v>26</v>
+      </c>
+      <c r="B83" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A83-1))</f>
+        <v/>
+      </c>
+      <c r="C83" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A83-1))</f>
+        <v/>
+      </c>
+      <c r="D83" s="139">
+        <f>DAY(EOMONTH(DATE(B83,C83,1),0))</f>
+        <v/>
+      </c>
+      <c r="E83" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B83,법정공휴일!$A$4:$A$20,0),C83),0)</f>
+        <v/>
+      </c>
+      <c r="F83" s="139">
+        <f>INDEX($D$25:$O$25,C83)</f>
+        <v/>
+      </c>
+      <c r="G83" s="139">
+        <f>ROUND(F83*E83/D83,1)</f>
+        <v/>
+      </c>
+      <c r="H83" s="139">
+        <f>F83+E83-G83</f>
+        <v/>
+      </c>
+      <c r="I83" s="139">
+        <f>ROUND(MAX(H83,8),0)</f>
+        <v/>
+      </c>
+      <c r="J83" s="139">
+        <f>D83-I83</f>
+        <v/>
+      </c>
+      <c r="K83" s="139">
+        <f>K82+J82</f>
+        <v/>
+      </c>
+      <c r="L83" s="139">
+        <f>L82+D82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="139" t="n">
+        <v>27</v>
+      </c>
+      <c r="B84" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A84-1))</f>
+        <v/>
+      </c>
+      <c r="C84" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A84-1))</f>
+        <v/>
+      </c>
+      <c r="D84" s="139">
+        <f>DAY(EOMONTH(DATE(B84,C84,1),0))</f>
+        <v/>
+      </c>
+      <c r="E84" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B84,법정공휴일!$A$4:$A$20,0),C84),0)</f>
+        <v/>
+      </c>
+      <c r="F84" s="139">
+        <f>INDEX($D$25:$O$25,C84)</f>
+        <v/>
+      </c>
+      <c r="G84" s="139">
+        <f>ROUND(F84*E84/D84,1)</f>
+        <v/>
+      </c>
+      <c r="H84" s="139">
+        <f>F84+E84-G84</f>
+        <v/>
+      </c>
+      <c r="I84" s="139">
+        <f>ROUND(MAX(H84,8),0)</f>
+        <v/>
+      </c>
+      <c r="J84" s="139">
+        <f>D84-I84</f>
+        <v/>
+      </c>
+      <c r="K84" s="139">
+        <f>K83+J83</f>
+        <v/>
+      </c>
+      <c r="L84" s="139">
+        <f>L83+D83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="139" t="n">
+        <v>28</v>
+      </c>
+      <c r="B85" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A85-1))</f>
+        <v/>
+      </c>
+      <c r="C85" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A85-1))</f>
+        <v/>
+      </c>
+      <c r="D85" s="139">
+        <f>DAY(EOMONTH(DATE(B85,C85,1),0))</f>
+        <v/>
+      </c>
+      <c r="E85" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B85,법정공휴일!$A$4:$A$20,0),C85),0)</f>
+        <v/>
+      </c>
+      <c r="F85" s="139">
+        <f>INDEX($D$25:$O$25,C85)</f>
+        <v/>
+      </c>
+      <c r="G85" s="139">
+        <f>ROUND(F85*E85/D85,1)</f>
+        <v/>
+      </c>
+      <c r="H85" s="139">
+        <f>F85+E85-G85</f>
+        <v/>
+      </c>
+      <c r="I85" s="139">
+        <f>ROUND(MAX(H85,8),0)</f>
+        <v/>
+      </c>
+      <c r="J85" s="139">
+        <f>D85-I85</f>
+        <v/>
+      </c>
+      <c r="K85" s="139">
+        <f>K84+J84</f>
+        <v/>
+      </c>
+      <c r="L85" s="139">
+        <f>L84+D84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="139" t="n">
+        <v>29</v>
+      </c>
+      <c r="B86" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A86-1))</f>
+        <v/>
+      </c>
+      <c r="C86" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A86-1))</f>
+        <v/>
+      </c>
+      <c r="D86" s="139">
+        <f>DAY(EOMONTH(DATE(B86,C86,1),0))</f>
+        <v/>
+      </c>
+      <c r="E86" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B86,법정공휴일!$A$4:$A$20,0),C86),0)</f>
+        <v/>
+      </c>
+      <c r="F86" s="139">
+        <f>INDEX($D$25:$O$25,C86)</f>
+        <v/>
+      </c>
+      <c r="G86" s="139">
+        <f>ROUND(F86*E86/D86,1)</f>
+        <v/>
+      </c>
+      <c r="H86" s="139">
+        <f>F86+E86-G86</f>
+        <v/>
+      </c>
+      <c r="I86" s="139">
+        <f>ROUND(MAX(H86,8),0)</f>
+        <v/>
+      </c>
+      <c r="J86" s="139">
+        <f>D86-I86</f>
+        <v/>
+      </c>
+      <c r="K86" s="139">
+        <f>K85+J85</f>
+        <v/>
+      </c>
+      <c r="L86" s="139">
+        <f>L85+D85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="139" t="n">
+        <v>30</v>
+      </c>
+      <c r="B87" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A87-1))</f>
+        <v/>
+      </c>
+      <c r="C87" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A87-1))</f>
+        <v/>
+      </c>
+      <c r="D87" s="139">
+        <f>DAY(EOMONTH(DATE(B87,C87,1),0))</f>
+        <v/>
+      </c>
+      <c r="E87" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B87,법정공휴일!$A$4:$A$20,0),C87),0)</f>
+        <v/>
+      </c>
+      <c r="F87" s="139">
+        <f>INDEX($D$25:$O$25,C87)</f>
+        <v/>
+      </c>
+      <c r="G87" s="139">
+        <f>ROUND(F87*E87/D87,1)</f>
+        <v/>
+      </c>
+      <c r="H87" s="139">
+        <f>F87+E87-G87</f>
+        <v/>
+      </c>
+      <c r="I87" s="139">
+        <f>ROUND(MAX(H87,8),0)</f>
+        <v/>
+      </c>
+      <c r="J87" s="139">
+        <f>D87-I87</f>
+        <v/>
+      </c>
+      <c r="K87" s="139">
+        <f>K86+J86</f>
+        <v/>
+      </c>
+      <c r="L87" s="139">
+        <f>L86+D86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="139" t="n">
+        <v>31</v>
+      </c>
+      <c r="B88" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A88-1))</f>
+        <v/>
+      </c>
+      <c r="C88" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A88-1))</f>
+        <v/>
+      </c>
+      <c r="D88" s="139">
+        <f>DAY(EOMONTH(DATE(B88,C88,1),0))</f>
+        <v/>
+      </c>
+      <c r="E88" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B88,법정공휴일!$A$4:$A$20,0),C88),0)</f>
+        <v/>
+      </c>
+      <c r="F88" s="139">
+        <f>INDEX($D$25:$O$25,C88)</f>
+        <v/>
+      </c>
+      <c r="G88" s="139">
+        <f>ROUND(F88*E88/D88,1)</f>
+        <v/>
+      </c>
+      <c r="H88" s="139">
+        <f>F88+E88-G88</f>
+        <v/>
+      </c>
+      <c r="I88" s="139">
+        <f>ROUND(MAX(H88,8),0)</f>
+        <v/>
+      </c>
+      <c r="J88" s="139">
+        <f>D88-I88</f>
+        <v/>
+      </c>
+      <c r="K88" s="139">
+        <f>K87+J87</f>
+        <v/>
+      </c>
+      <c r="L88" s="139">
+        <f>L87+D87</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="139" t="n">
+        <v>32</v>
+      </c>
+      <c r="B89" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A89-1))</f>
+        <v/>
+      </c>
+      <c r="C89" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A89-1))</f>
+        <v/>
+      </c>
+      <c r="D89" s="139">
+        <f>DAY(EOMONTH(DATE(B89,C89,1),0))</f>
+        <v/>
+      </c>
+      <c r="E89" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B89,법정공휴일!$A$4:$A$20,0),C89),0)</f>
+        <v/>
+      </c>
+      <c r="F89" s="139">
+        <f>INDEX($D$25:$O$25,C89)</f>
+        <v/>
+      </c>
+      <c r="G89" s="139">
+        <f>ROUND(F89*E89/D89,1)</f>
+        <v/>
+      </c>
+      <c r="H89" s="139">
+        <f>F89+E89-G89</f>
+        <v/>
+      </c>
+      <c r="I89" s="139">
+        <f>ROUND(MAX(H89,8),0)</f>
+        <v/>
+      </c>
+      <c r="J89" s="139">
+        <f>D89-I89</f>
+        <v/>
+      </c>
+      <c r="K89" s="139">
+        <f>K88+J88</f>
+        <v/>
+      </c>
+      <c r="L89" s="139">
+        <f>L88+D88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="139" t="n">
+        <v>33</v>
+      </c>
+      <c r="B90" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A90-1))</f>
+        <v/>
+      </c>
+      <c r="C90" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A90-1))</f>
+        <v/>
+      </c>
+      <c r="D90" s="139">
+        <f>DAY(EOMONTH(DATE(B90,C90,1),0))</f>
+        <v/>
+      </c>
+      <c r="E90" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B90,법정공휴일!$A$4:$A$20,0),C90),0)</f>
+        <v/>
+      </c>
+      <c r="F90" s="139">
+        <f>INDEX($D$25:$O$25,C90)</f>
+        <v/>
+      </c>
+      <c r="G90" s="139">
+        <f>ROUND(F90*E90/D90,1)</f>
+        <v/>
+      </c>
+      <c r="H90" s="139">
+        <f>F90+E90-G90</f>
+        <v/>
+      </c>
+      <c r="I90" s="139">
+        <f>ROUND(MAX(H90,8),0)</f>
+        <v/>
+      </c>
+      <c r="J90" s="139">
+        <f>D90-I90</f>
+        <v/>
+      </c>
+      <c r="K90" s="139">
+        <f>K89+J89</f>
+        <v/>
+      </c>
+      <c r="L90" s="139">
+        <f>L89+D89</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="139" t="n">
+        <v>34</v>
+      </c>
+      <c r="B91" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A91-1))</f>
+        <v/>
+      </c>
+      <c r="C91" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A91-1))</f>
+        <v/>
+      </c>
+      <c r="D91" s="139">
+        <f>DAY(EOMONTH(DATE(B91,C91,1),0))</f>
+        <v/>
+      </c>
+      <c r="E91" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B91,법정공휴일!$A$4:$A$20,0),C91),0)</f>
+        <v/>
+      </c>
+      <c r="F91" s="139">
+        <f>INDEX($D$25:$O$25,C91)</f>
+        <v/>
+      </c>
+      <c r="G91" s="139">
+        <f>ROUND(F91*E91/D91,1)</f>
+        <v/>
+      </c>
+      <c r="H91" s="139">
+        <f>F91+E91-G91</f>
+        <v/>
+      </c>
+      <c r="I91" s="139">
+        <f>ROUND(MAX(H91,8),0)</f>
+        <v/>
+      </c>
+      <c r="J91" s="139">
+        <f>D91-I91</f>
+        <v/>
+      </c>
+      <c r="K91" s="139">
+        <f>K90+J90</f>
+        <v/>
+      </c>
+      <c r="L91" s="139">
+        <f>L90+D90</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="139" t="n">
+        <v>35</v>
+      </c>
+      <c r="B92" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A92-1))</f>
+        <v/>
+      </c>
+      <c r="C92" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A92-1))</f>
+        <v/>
+      </c>
+      <c r="D92" s="139">
+        <f>DAY(EOMONTH(DATE(B92,C92,1),0))</f>
+        <v/>
+      </c>
+      <c r="E92" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B92,법정공휴일!$A$4:$A$20,0),C92),0)</f>
+        <v/>
+      </c>
+      <c r="F92" s="139">
+        <f>INDEX($D$25:$O$25,C92)</f>
+        <v/>
+      </c>
+      <c r="G92" s="139">
+        <f>ROUND(F92*E92/D92,1)</f>
+        <v/>
+      </c>
+      <c r="H92" s="139">
+        <f>F92+E92-G92</f>
+        <v/>
+      </c>
+      <c r="I92" s="139">
+        <f>ROUND(MAX(H92,8),0)</f>
+        <v/>
+      </c>
+      <c r="J92" s="139">
+        <f>D92-I92</f>
+        <v/>
+      </c>
+      <c r="K92" s="139">
+        <f>K91+J91</f>
+        <v/>
+      </c>
+      <c r="L92" s="139">
+        <f>L91+D91</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="139" t="n">
+        <v>36</v>
+      </c>
+      <c r="B93" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A93-1))</f>
+        <v/>
+      </c>
+      <c r="C93" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A93-1))</f>
+        <v/>
+      </c>
+      <c r="D93" s="139">
+        <f>DAY(EOMONTH(DATE(B93,C93,1),0))</f>
+        <v/>
+      </c>
+      <c r="E93" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B93,법정공휴일!$A$4:$A$20,0),C93),0)</f>
+        <v/>
+      </c>
+      <c r="F93" s="139">
+        <f>INDEX($D$25:$O$25,C93)</f>
+        <v/>
+      </c>
+      <c r="G93" s="139">
+        <f>ROUND(F93*E93/D93,1)</f>
+        <v/>
+      </c>
+      <c r="H93" s="139">
+        <f>F93+E93-G93</f>
+        <v/>
+      </c>
+      <c r="I93" s="139">
+        <f>ROUND(MAX(H93,8),0)</f>
+        <v/>
+      </c>
+      <c r="J93" s="139">
+        <f>D93-I93</f>
+        <v/>
+      </c>
+      <c r="K93" s="139">
+        <f>K92+J92</f>
+        <v/>
+      </c>
+      <c r="L93" s="139">
+        <f>L92+D92</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="139" t="n">
+        <v>37</v>
+      </c>
+      <c r="B94" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A94-1))</f>
+        <v/>
+      </c>
+      <c r="C94" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A94-1))</f>
+        <v/>
+      </c>
+      <c r="D94" s="139">
+        <f>DAY(EOMONTH(DATE(B94,C94,1),0))</f>
+        <v/>
+      </c>
+      <c r="E94" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B94,법정공휴일!$A$4:$A$20,0),C94),0)</f>
+        <v/>
+      </c>
+      <c r="F94" s="139">
+        <f>INDEX($D$25:$O$25,C94)</f>
+        <v/>
+      </c>
+      <c r="G94" s="139">
+        <f>ROUND(F94*E94/D94,1)</f>
+        <v/>
+      </c>
+      <c r="H94" s="139">
+        <f>F94+E94-G94</f>
+        <v/>
+      </c>
+      <c r="I94" s="139">
+        <f>ROUND(MAX(H94,8),0)</f>
+        <v/>
+      </c>
+      <c r="J94" s="139">
+        <f>D94-I94</f>
+        <v/>
+      </c>
+      <c r="K94" s="139">
+        <f>K93+J93</f>
+        <v/>
+      </c>
+      <c r="L94" s="139">
+        <f>L93+D93</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="139" t="n">
+        <v>38</v>
+      </c>
+      <c r="B95" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A95-1))</f>
+        <v/>
+      </c>
+      <c r="C95" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A95-1))</f>
+        <v/>
+      </c>
+      <c r="D95" s="139">
+        <f>DAY(EOMONTH(DATE(B95,C95,1),0))</f>
+        <v/>
+      </c>
+      <c r="E95" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B95,법정공휴일!$A$4:$A$20,0),C95),0)</f>
+        <v/>
+      </c>
+      <c r="F95" s="139">
+        <f>INDEX($D$25:$O$25,C95)</f>
+        <v/>
+      </c>
+      <c r="G95" s="139">
+        <f>ROUND(F95*E95/D95,1)</f>
+        <v/>
+      </c>
+      <c r="H95" s="139">
+        <f>F95+E95-G95</f>
+        <v/>
+      </c>
+      <c r="I95" s="139">
+        <f>ROUND(MAX(H95,8),0)</f>
+        <v/>
+      </c>
+      <c r="J95" s="139">
+        <f>D95-I95</f>
+        <v/>
+      </c>
+      <c r="K95" s="139">
+        <f>K94+J94</f>
+        <v/>
+      </c>
+      <c r="L95" s="139">
+        <f>L94+D94</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="139" t="n">
+        <v>39</v>
+      </c>
+      <c r="B96" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A96-1))</f>
+        <v/>
+      </c>
+      <c r="C96" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A96-1))</f>
+        <v/>
+      </c>
+      <c r="D96" s="139">
+        <f>DAY(EOMONTH(DATE(B96,C96,1),0))</f>
+        <v/>
+      </c>
+      <c r="E96" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B96,법정공휴일!$A$4:$A$20,0),C96),0)</f>
+        <v/>
+      </c>
+      <c r="F96" s="139">
+        <f>INDEX($D$25:$O$25,C96)</f>
+        <v/>
+      </c>
+      <c r="G96" s="139">
+        <f>ROUND(F96*E96/D96,1)</f>
+        <v/>
+      </c>
+      <c r="H96" s="139">
+        <f>F96+E96-G96</f>
+        <v/>
+      </c>
+      <c r="I96" s="139">
+        <f>ROUND(MAX(H96,8),0)</f>
+        <v/>
+      </c>
+      <c r="J96" s="139">
+        <f>D96-I96</f>
+        <v/>
+      </c>
+      <c r="K96" s="139">
+        <f>K95+J95</f>
+        <v/>
+      </c>
+      <c r="L96" s="139">
+        <f>L95+D95</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="139" t="n">
+        <v>40</v>
+      </c>
+      <c r="B97" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A97-1))</f>
+        <v/>
+      </c>
+      <c r="C97" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A97-1))</f>
+        <v/>
+      </c>
+      <c r="D97" s="139">
+        <f>DAY(EOMONTH(DATE(B97,C97,1),0))</f>
+        <v/>
+      </c>
+      <c r="E97" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B97,법정공휴일!$A$4:$A$20,0),C97),0)</f>
+        <v/>
+      </c>
+      <c r="F97" s="139">
+        <f>INDEX($D$25:$O$25,C97)</f>
+        <v/>
+      </c>
+      <c r="G97" s="139">
+        <f>ROUND(F97*E97/D97,1)</f>
+        <v/>
+      </c>
+      <c r="H97" s="139">
+        <f>F97+E97-G97</f>
+        <v/>
+      </c>
+      <c r="I97" s="139">
+        <f>ROUND(MAX(H97,8),0)</f>
+        <v/>
+      </c>
+      <c r="J97" s="139">
+        <f>D97-I97</f>
+        <v/>
+      </c>
+      <c r="K97" s="139">
+        <f>K96+J96</f>
+        <v/>
+      </c>
+      <c r="L97" s="139">
+        <f>L96+D96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="139" t="n">
+        <v>41</v>
+      </c>
+      <c r="B98" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A98-1))</f>
+        <v/>
+      </c>
+      <c r="C98" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A98-1))</f>
+        <v/>
+      </c>
+      <c r="D98" s="139">
+        <f>DAY(EOMONTH(DATE(B98,C98,1),0))</f>
+        <v/>
+      </c>
+      <c r="E98" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B98,법정공휴일!$A$4:$A$20,0),C98),0)</f>
+        <v/>
+      </c>
+      <c r="F98" s="139">
+        <f>INDEX($D$25:$O$25,C98)</f>
+        <v/>
+      </c>
+      <c r="G98" s="139">
+        <f>ROUND(F98*E98/D98,1)</f>
+        <v/>
+      </c>
+      <c r="H98" s="139">
+        <f>F98+E98-G98</f>
+        <v/>
+      </c>
+      <c r="I98" s="139">
+        <f>ROUND(MAX(H98,8),0)</f>
+        <v/>
+      </c>
+      <c r="J98" s="139">
+        <f>D98-I98</f>
+        <v/>
+      </c>
+      <c r="K98" s="139">
+        <f>K97+J97</f>
+        <v/>
+      </c>
+      <c r="L98" s="139">
+        <f>L97+D97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="139" t="n">
+        <v>42</v>
+      </c>
+      <c r="B99" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A99-1))</f>
+        <v/>
+      </c>
+      <c r="C99" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A99-1))</f>
+        <v/>
+      </c>
+      <c r="D99" s="139">
+        <f>DAY(EOMONTH(DATE(B99,C99,1),0))</f>
+        <v/>
+      </c>
+      <c r="E99" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B99,법정공휴일!$A$4:$A$20,0),C99),0)</f>
+        <v/>
+      </c>
+      <c r="F99" s="139">
+        <f>INDEX($D$25:$O$25,C99)</f>
+        <v/>
+      </c>
+      <c r="G99" s="139">
+        <f>ROUND(F99*E99/D99,1)</f>
+        <v/>
+      </c>
+      <c r="H99" s="139">
+        <f>F99+E99-G99</f>
+        <v/>
+      </c>
+      <c r="I99" s="139">
+        <f>ROUND(MAX(H99,8),0)</f>
+        <v/>
+      </c>
+      <c r="J99" s="139">
+        <f>D99-I99</f>
+        <v/>
+      </c>
+      <c r="K99" s="139">
+        <f>K98+J98</f>
+        <v/>
+      </c>
+      <c r="L99" s="139">
+        <f>L98+D98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="139" t="n">
+        <v>43</v>
+      </c>
+      <c r="B100" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A100-1))</f>
+        <v/>
+      </c>
+      <c r="C100" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A100-1))</f>
+        <v/>
+      </c>
+      <c r="D100" s="139">
+        <f>DAY(EOMONTH(DATE(B100,C100,1),0))</f>
+        <v/>
+      </c>
+      <c r="E100" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B100,법정공휴일!$A$4:$A$20,0),C100),0)</f>
+        <v/>
+      </c>
+      <c r="F100" s="139">
+        <f>INDEX($D$25:$O$25,C100)</f>
+        <v/>
+      </c>
+      <c r="G100" s="139">
+        <f>ROUND(F100*E100/D100,1)</f>
+        <v/>
+      </c>
+      <c r="H100" s="139">
+        <f>F100+E100-G100</f>
+        <v/>
+      </c>
+      <c r="I100" s="139">
+        <f>ROUND(MAX(H100,8),0)</f>
+        <v/>
+      </c>
+      <c r="J100" s="139">
+        <f>D100-I100</f>
+        <v/>
+      </c>
+      <c r="K100" s="139">
+        <f>K99+J99</f>
+        <v/>
+      </c>
+      <c r="L100" s="139">
+        <f>L99+D99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="139" t="n">
+        <v>44</v>
+      </c>
+      <c r="B101" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A101-1))</f>
+        <v/>
+      </c>
+      <c r="C101" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A101-1))</f>
+        <v/>
+      </c>
+      <c r="D101" s="139">
+        <f>DAY(EOMONTH(DATE(B101,C101,1),0))</f>
+        <v/>
+      </c>
+      <c r="E101" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B101,법정공휴일!$A$4:$A$20,0),C101),0)</f>
+        <v/>
+      </c>
+      <c r="F101" s="139">
+        <f>INDEX($D$25:$O$25,C101)</f>
+        <v/>
+      </c>
+      <c r="G101" s="139">
+        <f>ROUND(F101*E101/D101,1)</f>
+        <v/>
+      </c>
+      <c r="H101" s="139">
+        <f>F101+E101-G101</f>
+        <v/>
+      </c>
+      <c r="I101" s="139">
+        <f>ROUND(MAX(H101,8),0)</f>
+        <v/>
+      </c>
+      <c r="J101" s="139">
+        <f>D101-I101</f>
+        <v/>
+      </c>
+      <c r="K101" s="139">
+        <f>K100+J100</f>
+        <v/>
+      </c>
+      <c r="L101" s="139">
+        <f>L100+D100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="139" t="n">
+        <v>45</v>
+      </c>
+      <c r="B102" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A102-1))</f>
+        <v/>
+      </c>
+      <c r="C102" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A102-1))</f>
+        <v/>
+      </c>
+      <c r="D102" s="139">
+        <f>DAY(EOMONTH(DATE(B102,C102,1),0))</f>
+        <v/>
+      </c>
+      <c r="E102" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B102,법정공휴일!$A$4:$A$20,0),C102),0)</f>
+        <v/>
+      </c>
+      <c r="F102" s="139">
+        <f>INDEX($D$25:$O$25,C102)</f>
+        <v/>
+      </c>
+      <c r="G102" s="139">
+        <f>ROUND(F102*E102/D102,1)</f>
+        <v/>
+      </c>
+      <c r="H102" s="139">
+        <f>F102+E102-G102</f>
+        <v/>
+      </c>
+      <c r="I102" s="139">
+        <f>ROUND(MAX(H102,8),0)</f>
+        <v/>
+      </c>
+      <c r="J102" s="139">
+        <f>D102-I102</f>
+        <v/>
+      </c>
+      <c r="K102" s="139">
+        <f>K101+J101</f>
+        <v/>
+      </c>
+      <c r="L102" s="139">
+        <f>L101+D101</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="139" t="n">
+        <v>46</v>
+      </c>
+      <c r="B103" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A103-1))</f>
+        <v/>
+      </c>
+      <c r="C103" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A103-1))</f>
+        <v/>
+      </c>
+      <c r="D103" s="139">
+        <f>DAY(EOMONTH(DATE(B103,C103,1),0))</f>
+        <v/>
+      </c>
+      <c r="E103" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B103,법정공휴일!$A$4:$A$20,0),C103),0)</f>
+        <v/>
+      </c>
+      <c r="F103" s="139">
+        <f>INDEX($D$25:$O$25,C103)</f>
+        <v/>
+      </c>
+      <c r="G103" s="139">
+        <f>ROUND(F103*E103/D103,1)</f>
+        <v/>
+      </c>
+      <c r="H103" s="139">
+        <f>F103+E103-G103</f>
+        <v/>
+      </c>
+      <c r="I103" s="139">
+        <f>ROUND(MAX(H103,8),0)</f>
+        <v/>
+      </c>
+      <c r="J103" s="139">
+        <f>D103-I103</f>
+        <v/>
+      </c>
+      <c r="K103" s="139">
+        <f>K102+J102</f>
+        <v/>
+      </c>
+      <c r="L103" s="139">
+        <f>L102+D102</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="139" t="n">
+        <v>47</v>
+      </c>
+      <c r="B104" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A104-1))</f>
+        <v/>
+      </c>
+      <c r="C104" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A104-1))</f>
+        <v/>
+      </c>
+      <c r="D104" s="139">
+        <f>DAY(EOMONTH(DATE(B104,C104,1),0))</f>
+        <v/>
+      </c>
+      <c r="E104" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B104,법정공휴일!$A$4:$A$20,0),C104),0)</f>
+        <v/>
+      </c>
+      <c r="F104" s="139">
+        <f>INDEX($D$25:$O$25,C104)</f>
+        <v/>
+      </c>
+      <c r="G104" s="139">
+        <f>ROUND(F104*E104/D104,1)</f>
+        <v/>
+      </c>
+      <c r="H104" s="139">
+        <f>F104+E104-G104</f>
+        <v/>
+      </c>
+      <c r="I104" s="139">
+        <f>ROUND(MAX(H104,8),0)</f>
+        <v/>
+      </c>
+      <c r="J104" s="139">
+        <f>D104-I104</f>
+        <v/>
+      </c>
+      <c r="K104" s="139">
+        <f>K103+J103</f>
+        <v/>
+      </c>
+      <c r="L104" s="139">
+        <f>L103+D103</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="139" t="n">
+        <v>48</v>
+      </c>
+      <c r="B105" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A105-1))</f>
+        <v/>
+      </c>
+      <c r="C105" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A105-1))</f>
+        <v/>
+      </c>
+      <c r="D105" s="139">
+        <f>DAY(EOMONTH(DATE(B105,C105,1),0))</f>
+        <v/>
+      </c>
+      <c r="E105" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B105,법정공휴일!$A$4:$A$20,0),C105),0)</f>
+        <v/>
+      </c>
+      <c r="F105" s="139">
+        <f>INDEX($D$25:$O$25,C105)</f>
+        <v/>
+      </c>
+      <c r="G105" s="139">
+        <f>ROUND(F105*E105/D105,1)</f>
+        <v/>
+      </c>
+      <c r="H105" s="139">
+        <f>F105+E105-G105</f>
+        <v/>
+      </c>
+      <c r="I105" s="139">
+        <f>ROUND(MAX(H105,8),0)</f>
+        <v/>
+      </c>
+      <c r="J105" s="139">
+        <f>D105-I105</f>
+        <v/>
+      </c>
+      <c r="K105" s="139">
+        <f>K104+J104</f>
+        <v/>
+      </c>
+      <c r="L105" s="139">
+        <f>L104+D104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="139" t="n">
+        <v>49</v>
+      </c>
+      <c r="B106" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A106-1))</f>
+        <v/>
+      </c>
+      <c r="C106" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A106-1))</f>
+        <v/>
+      </c>
+      <c r="D106" s="139">
+        <f>DAY(EOMONTH(DATE(B106,C106,1),0))</f>
+        <v/>
+      </c>
+      <c r="E106" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B106,법정공휴일!$A$4:$A$20,0),C106),0)</f>
+        <v/>
+      </c>
+      <c r="F106" s="139">
+        <f>INDEX($D$25:$O$25,C106)</f>
+        <v/>
+      </c>
+      <c r="G106" s="139">
+        <f>ROUND(F106*E106/D106,1)</f>
+        <v/>
+      </c>
+      <c r="H106" s="139">
+        <f>F106+E106-G106</f>
+        <v/>
+      </c>
+      <c r="I106" s="139">
+        <f>ROUND(MAX(H106,8),0)</f>
+        <v/>
+      </c>
+      <c r="J106" s="139">
+        <f>D106-I106</f>
+        <v/>
+      </c>
+      <c r="K106" s="139">
+        <f>K105+J105</f>
+        <v/>
+      </c>
+      <c r="L106" s="139">
+        <f>L105+D105</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="139" t="n">
+        <v>50</v>
+      </c>
+      <c r="B107" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A107-1))</f>
+        <v/>
+      </c>
+      <c r="C107" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A107-1))</f>
+        <v/>
+      </c>
+      <c r="D107" s="139">
+        <f>DAY(EOMONTH(DATE(B107,C107,1),0))</f>
+        <v/>
+      </c>
+      <c r="E107" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B107,법정공휴일!$A$4:$A$20,0),C107),0)</f>
+        <v/>
+      </c>
+      <c r="F107" s="139">
+        <f>INDEX($D$25:$O$25,C107)</f>
+        <v/>
+      </c>
+      <c r="G107" s="139">
+        <f>ROUND(F107*E107/D107,1)</f>
+        <v/>
+      </c>
+      <c r="H107" s="139">
+        <f>F107+E107-G107</f>
+        <v/>
+      </c>
+      <c r="I107" s="139">
+        <f>ROUND(MAX(H107,8),0)</f>
+        <v/>
+      </c>
+      <c r="J107" s="139">
+        <f>D107-I107</f>
+        <v/>
+      </c>
+      <c r="K107" s="139">
+        <f>K106+J106</f>
+        <v/>
+      </c>
+      <c r="L107" s="139">
+        <f>L106+D106</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="139" t="n">
+        <v>51</v>
+      </c>
+      <c r="B108" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A108-1))</f>
+        <v/>
+      </c>
+      <c r="C108" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A108-1))</f>
+        <v/>
+      </c>
+      <c r="D108" s="139">
+        <f>DAY(EOMONTH(DATE(B108,C108,1),0))</f>
+        <v/>
+      </c>
+      <c r="E108" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B108,법정공휴일!$A$4:$A$20,0),C108),0)</f>
+        <v/>
+      </c>
+      <c r="F108" s="139">
+        <f>INDEX($D$25:$O$25,C108)</f>
+        <v/>
+      </c>
+      <c r="G108" s="139">
+        <f>ROUND(F108*E108/D108,1)</f>
+        <v/>
+      </c>
+      <c r="H108" s="139">
+        <f>F108+E108-G108</f>
+        <v/>
+      </c>
+      <c r="I108" s="139">
+        <f>ROUND(MAX(H108,8),0)</f>
+        <v/>
+      </c>
+      <c r="J108" s="139">
+        <f>D108-I108</f>
+        <v/>
+      </c>
+      <c r="K108" s="139">
+        <f>K107+J107</f>
+        <v/>
+      </c>
+      <c r="L108" s="139">
+        <f>L107+D107</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="139" t="n">
+        <v>52</v>
+      </c>
+      <c r="B109" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A109-1))</f>
+        <v/>
+      </c>
+      <c r="C109" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A109-1))</f>
+        <v/>
+      </c>
+      <c r="D109" s="139">
+        <f>DAY(EOMONTH(DATE(B109,C109,1),0))</f>
+        <v/>
+      </c>
+      <c r="E109" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B109,법정공휴일!$A$4:$A$20,0),C109),0)</f>
+        <v/>
+      </c>
+      <c r="F109" s="139">
+        <f>INDEX($D$25:$O$25,C109)</f>
+        <v/>
+      </c>
+      <c r="G109" s="139">
+        <f>ROUND(F109*E109/D109,1)</f>
+        <v/>
+      </c>
+      <c r="H109" s="139">
+        <f>F109+E109-G109</f>
+        <v/>
+      </c>
+      <c r="I109" s="139">
+        <f>ROUND(MAX(H109,8),0)</f>
+        <v/>
+      </c>
+      <c r="J109" s="139">
+        <f>D109-I109</f>
+        <v/>
+      </c>
+      <c r="K109" s="139">
+        <f>K108+J108</f>
+        <v/>
+      </c>
+      <c r="L109" s="139">
+        <f>L108+D108</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="139" t="n">
+        <v>53</v>
+      </c>
+      <c r="B110" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A110-1))</f>
+        <v/>
+      </c>
+      <c r="C110" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A110-1))</f>
+        <v/>
+      </c>
+      <c r="D110" s="139">
+        <f>DAY(EOMONTH(DATE(B110,C110,1),0))</f>
+        <v/>
+      </c>
+      <c r="E110" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B110,법정공휴일!$A$4:$A$20,0),C110),0)</f>
+        <v/>
+      </c>
+      <c r="F110" s="139">
+        <f>INDEX($D$25:$O$25,C110)</f>
+        <v/>
+      </c>
+      <c r="G110" s="139">
+        <f>ROUND(F110*E110/D110,1)</f>
+        <v/>
+      </c>
+      <c r="H110" s="139">
+        <f>F110+E110-G110</f>
+        <v/>
+      </c>
+      <c r="I110" s="139">
+        <f>ROUND(MAX(H110,8),0)</f>
+        <v/>
+      </c>
+      <c r="J110" s="139">
+        <f>D110-I110</f>
+        <v/>
+      </c>
+      <c r="K110" s="139">
+        <f>K109+J109</f>
+        <v/>
+      </c>
+      <c r="L110" s="139">
+        <f>L109+D109</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="139" t="n">
+        <v>54</v>
+      </c>
+      <c r="B111" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A111-1))</f>
+        <v/>
+      </c>
+      <c r="C111" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A111-1))</f>
+        <v/>
+      </c>
+      <c r="D111" s="139">
+        <f>DAY(EOMONTH(DATE(B111,C111,1),0))</f>
+        <v/>
+      </c>
+      <c r="E111" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B111,법정공휴일!$A$4:$A$20,0),C111),0)</f>
+        <v/>
+      </c>
+      <c r="F111" s="139">
+        <f>INDEX($D$25:$O$25,C111)</f>
+        <v/>
+      </c>
+      <c r="G111" s="139">
+        <f>ROUND(F111*E111/D111,1)</f>
+        <v/>
+      </c>
+      <c r="H111" s="139">
+        <f>F111+E111-G111</f>
+        <v/>
+      </c>
+      <c r="I111" s="139">
+        <f>ROUND(MAX(H111,8),0)</f>
+        <v/>
+      </c>
+      <c r="J111" s="139">
+        <f>D111-I111</f>
+        <v/>
+      </c>
+      <c r="K111" s="139">
+        <f>K110+J110</f>
+        <v/>
+      </c>
+      <c r="L111" s="139">
+        <f>L110+D110</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="139" t="n">
+        <v>55</v>
+      </c>
+      <c r="B112" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A112-1))</f>
+        <v/>
+      </c>
+      <c r="C112" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A112-1))</f>
+        <v/>
+      </c>
+      <c r="D112" s="139">
+        <f>DAY(EOMONTH(DATE(B112,C112,1),0))</f>
+        <v/>
+      </c>
+      <c r="E112" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B112,법정공휴일!$A$4:$A$20,0),C112),0)</f>
+        <v/>
+      </c>
+      <c r="F112" s="139">
+        <f>INDEX($D$25:$O$25,C112)</f>
+        <v/>
+      </c>
+      <c r="G112" s="139">
+        <f>ROUND(F112*E112/D112,1)</f>
+        <v/>
+      </c>
+      <c r="H112" s="139">
+        <f>F112+E112-G112</f>
+        <v/>
+      </c>
+      <c r="I112" s="139">
+        <f>ROUND(MAX(H112,8),0)</f>
+        <v/>
+      </c>
+      <c r="J112" s="139">
+        <f>D112-I112</f>
+        <v/>
+      </c>
+      <c r="K112" s="139">
+        <f>K111+J111</f>
+        <v/>
+      </c>
+      <c r="L112" s="139">
+        <f>L111+D111</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="139" t="n">
+        <v>56</v>
+      </c>
+      <c r="B113" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A113-1))</f>
+        <v/>
+      </c>
+      <c r="C113" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A113-1))</f>
+        <v/>
+      </c>
+      <c r="D113" s="139">
+        <f>DAY(EOMONTH(DATE(B113,C113,1),0))</f>
+        <v/>
+      </c>
+      <c r="E113" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B113,법정공휴일!$A$4:$A$20,0),C113),0)</f>
+        <v/>
+      </c>
+      <c r="F113" s="139">
+        <f>INDEX($D$25:$O$25,C113)</f>
+        <v/>
+      </c>
+      <c r="G113" s="139">
+        <f>ROUND(F113*E113/D113,1)</f>
+        <v/>
+      </c>
+      <c r="H113" s="139">
+        <f>F113+E113-G113</f>
+        <v/>
+      </c>
+      <c r="I113" s="139">
+        <f>ROUND(MAX(H113,8),0)</f>
+        <v/>
+      </c>
+      <c r="J113" s="139">
+        <f>D113-I113</f>
+        <v/>
+      </c>
+      <c r="K113" s="139">
+        <f>K112+J112</f>
+        <v/>
+      </c>
+      <c r="L113" s="139">
+        <f>L112+D112</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="139" t="n">
+        <v>57</v>
+      </c>
+      <c r="B114" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A114-1))</f>
+        <v/>
+      </c>
+      <c r="C114" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A114-1))</f>
+        <v/>
+      </c>
+      <c r="D114" s="139">
+        <f>DAY(EOMONTH(DATE(B114,C114,1),0))</f>
+        <v/>
+      </c>
+      <c r="E114" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B114,법정공휴일!$A$4:$A$20,0),C114),0)</f>
+        <v/>
+      </c>
+      <c r="F114" s="139">
+        <f>INDEX($D$25:$O$25,C114)</f>
+        <v/>
+      </c>
+      <c r="G114" s="139">
+        <f>ROUND(F114*E114/D114,1)</f>
+        <v/>
+      </c>
+      <c r="H114" s="139">
+        <f>F114+E114-G114</f>
+        <v/>
+      </c>
+      <c r="I114" s="139">
+        <f>ROUND(MAX(H114,8),0)</f>
+        <v/>
+      </c>
+      <c r="J114" s="139">
+        <f>D114-I114</f>
+        <v/>
+      </c>
+      <c r="K114" s="139">
+        <f>K113+J113</f>
+        <v/>
+      </c>
+      <c r="L114" s="139">
+        <f>L113+D113</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="139" t="n">
+        <v>58</v>
+      </c>
+      <c r="B115" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A115-1))</f>
+        <v/>
+      </c>
+      <c r="C115" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A115-1))</f>
+        <v/>
+      </c>
+      <c r="D115" s="139">
+        <f>DAY(EOMONTH(DATE(B115,C115,1),0))</f>
+        <v/>
+      </c>
+      <c r="E115" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B115,법정공휴일!$A$4:$A$20,0),C115),0)</f>
+        <v/>
+      </c>
+      <c r="F115" s="139">
+        <f>INDEX($D$25:$O$25,C115)</f>
+        <v/>
+      </c>
+      <c r="G115" s="139">
+        <f>ROUND(F115*E115/D115,1)</f>
+        <v/>
+      </c>
+      <c r="H115" s="139">
+        <f>F115+E115-G115</f>
+        <v/>
+      </c>
+      <c r="I115" s="139">
+        <f>ROUND(MAX(H115,8),0)</f>
+        <v/>
+      </c>
+      <c r="J115" s="139">
+        <f>D115-I115</f>
+        <v/>
+      </c>
+      <c r="K115" s="139">
+        <f>K114+J114</f>
+        <v/>
+      </c>
+      <c r="L115" s="139">
+        <f>L114+D114</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="139" t="n">
+        <v>59</v>
+      </c>
+      <c r="B116" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A116-1))</f>
+        <v/>
+      </c>
+      <c r="C116" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A116-1))</f>
+        <v/>
+      </c>
+      <c r="D116" s="139">
+        <f>DAY(EOMONTH(DATE(B116,C116,1),0))</f>
+        <v/>
+      </c>
+      <c r="E116" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B116,법정공휴일!$A$4:$A$20,0),C116),0)</f>
+        <v/>
+      </c>
+      <c r="F116" s="139">
+        <f>INDEX($D$25:$O$25,C116)</f>
+        <v/>
+      </c>
+      <c r="G116" s="139">
+        <f>ROUND(F116*E116/D116,1)</f>
+        <v/>
+      </c>
+      <c r="H116" s="139">
+        <f>F116+E116-G116</f>
+        <v/>
+      </c>
+      <c r="I116" s="139">
+        <f>ROUND(MAX(H116,8),0)</f>
+        <v/>
+      </c>
+      <c r="J116" s="139">
+        <f>D116-I116</f>
+        <v/>
+      </c>
+      <c r="K116" s="139">
+        <f>K115+J115</f>
+        <v/>
+      </c>
+      <c r="L116" s="139">
+        <f>L115+D115</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="139" t="n">
+        <v>60</v>
+      </c>
+      <c r="B117" s="139">
+        <f>YEAR(EDATE(DATE($B$5,$B$6,1),A117-1))</f>
+        <v/>
+      </c>
+      <c r="C117" s="139">
+        <f>MONTH(EDATE(DATE($B$5,$B$6,1),A117-1))</f>
+        <v/>
+      </c>
+      <c r="D117" s="139">
+        <f>DAY(EOMONTH(DATE(B117,C117,1),0))</f>
+        <v/>
+      </c>
+      <c r="E117" s="139">
+        <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B117,법정공휴일!$A$4:$A$20,0),C117),0)</f>
+        <v/>
+      </c>
+      <c r="F117" s="139">
+        <f>INDEX($D$25:$O$25,C117)</f>
+        <v/>
+      </c>
+      <c r="G117" s="139">
+        <f>ROUND(F117*E117/D117,1)</f>
+        <v/>
+      </c>
+      <c r="H117" s="139">
+        <f>F117+E117-G117</f>
+        <v/>
+      </c>
+      <c r="I117" s="139">
+        <f>ROUND(MAX(H117,8),0)</f>
+        <v/>
+      </c>
+      <c r="J117" s="139">
+        <f>D117-I117</f>
+        <v/>
+      </c>
+      <c r="K117" s="139">
+        <f>K116+J116</f>
+        <v/>
+      </c>
+      <c r="L117" s="139">
+        <f>L116+D116</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>※ 마지막 달은 '비작업일수 = 총 비작업일수 × 잔여작업일수 ÷ 그 달 총 작업가능일수' 규칙(가이드라인 1150행)으로 안분합니다. 가이드라인 예시(철골세우기)는 20+23+12+10+10을 74일로 적었으나 실제 합은 75일입니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:L2"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>=지점목록!$A$2:$A$96</formula1>
+    </dataValidation>
+    <dataValidation sqref="C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"O,X"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/공기산정_2026기준.xlsx
+++ b/공기산정_2026기준.xlsx
@@ -12,8 +12,9 @@
     <sheet name="기상자료" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="지점목록" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="법정공휴일" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="시설물별공기(토목)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="공기산정(1일작업량)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="1일작업량(토목)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="시설물별공기(토목)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="공기산정(1일작업량)" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="내선전공">#REF!</definedName>
@@ -27,7 +28,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="12">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="0.0_ "/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="&quot;x &quot;0.0"/>
@@ -40,6 +41,7 @@
     <numFmt numFmtId="173" formatCode="0&quot;일&quot;"/>
     <numFmt numFmtId="174" formatCode="0&quot;월&quot;"/>
     <numFmt numFmtId="175" formatCode="0.0%"/>
+    <numFmt numFmtId="176" formatCode="#,##0.0000"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -667,7 +669,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1051,6 +1053,7 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -84853,7 +84856,2335 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:D117"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" style="92" min="1" max="1"/>
+    <col width="20" customWidth="1" style="92" min="3" max="3"/>
+    <col width="22" customWidth="1" style="92" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="134" t="inlineStr">
+        <is>
+          <t>선택명 (분류&gt;공종 (작업조건))</t>
+        </is>
+      </c>
+      <c r="B1" s="134" t="inlineStr">
+        <is>
+          <t>수량 단위</t>
+        </is>
+      </c>
+      <c r="C1" s="134" t="inlineStr">
+        <is>
+          <t>1일 작업량 (수량/일)</t>
+        </is>
+      </c>
+      <c r="D1" s="134" t="inlineStr">
+        <is>
+          <t>원문 표기 (부록 4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>공통가설공사&gt;가설사무실</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>개소</t>
+        </is>
+      </c>
+      <c r="C2" s="135" t="n">
+        <v>0.01298701298701299</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>77일/개소</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>공통가설공사&gt;가설울타리 (H형강지주 4m 이하)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C3" s="135" t="n">
+        <v>30</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>30m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>공통가설공사&gt;가설방음벽 (H형강지주 4m 이하)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C4" s="135" t="n">
+        <v>30</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>30m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>공통가설공사&gt;구조물 동바리 (시스템 동바리 30m 이하)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C5" s="135" t="n">
+        <v>82</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>82㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>공통가설공사&gt;구조물 비계 (강관비계 30m 이하)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="C6" s="135" t="n">
+        <v>102</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>102㎡/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>공통가설공사&gt;가설흙막이(진동파일해머-H파일) (파일 근입장 20m)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>본</t>
+        </is>
+      </c>
+      <c r="C7" s="135" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8본/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>공통가설공사&gt;가설흙막이(진동파일해머-강널말뚝) (파일 근입장 20m)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>본</t>
+        </is>
+      </c>
+      <c r="C8" s="135" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10본/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>공통가설공사&gt;가설흙막이(워터제트 병용-강널말뚝) (파일 근입장 20m)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>본</t>
+        </is>
+      </c>
+      <c r="C9" s="135" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6본/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>공통가설공사&gt;가설흙막이(유압식 압입 인발기-강널말뚝) (파일 근입장 20m)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>본</t>
+        </is>
+      </c>
+      <c r="C10" s="135" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8본/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>공통가설공사&gt;가설흙막이(말뚝박기용 천공/근입) (파일 근입장 20m)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>본</t>
+        </is>
+      </c>
+      <c r="C11" s="135" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8본/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>토공사&gt;기존시설물 깨기 (아스콘 t=30㎝ 이상)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C12" s="135" t="n">
+        <v>54</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>54㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>토공사&gt;벌목 (벌목 8m 이상)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="C13" s="135" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1,375㎡/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>토공사&gt;벌개제근</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="C14" s="135" t="n">
+        <v>1110</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1,110㎡/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>토공사&gt;표토제거 (답구간)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="C15" s="135" t="n">
+        <v>1915</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1,915㎡/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>토공사&gt;흙깎기-토사 (굴삭기 1.0㎥)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C16" s="135" t="n">
+        <v>520</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>520㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>토공사&gt;흙깎기-리핑암 (리퍼 2본+불도저 32톤)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C17" s="135" t="n">
+        <v>367</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>367㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>토공사&gt;흙깎기-발파암(브레이커) (연암, 보통암, 경암 평균)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C18" s="135" t="n">
+        <v>27</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>27㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>토공사&gt;흙깎기-발파암(발파) (진동제어발파(소규모))</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C19" s="135" t="n">
+        <v>83</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>83㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>토공사&gt;터파기-토사 (굴삭기 0.7㎥, 자연터파기)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C20" s="135" t="n">
+        <v>349</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>349㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>토공사&gt;터파기-리핑암 (브레이커 0.7㎥, 자연터파기)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C21" s="135" t="n">
+        <v>25</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>25㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>토공사&gt;터파기-발파암 (브레이커 0.7㎥, 자연터파기)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C22" s="135" t="n">
+        <v>18</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>18㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>토공사&gt;흙쌓기-노상 (모터그레이더 3.6㎥)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C23" s="135" t="n">
+        <v>745</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>745㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>토공사&gt;흙쌓기-노체 (모터그레이더 3.6㎥)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C24" s="135" t="n">
+        <v>1118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1,118㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>토공사&gt;흙쌓기-암쌓기 (불도저 32톤)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C25" s="135" t="n">
+        <v>647</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>647㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>토공사&gt;흙쌓기-녹지대 (불도저 32톤)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C26" s="135" t="n">
+        <v>1231</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1,231㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>토공사&gt;흙쌓기-되메우기 (램머(80kg) 다짐)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C27" s="135" t="n">
+        <v>42</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>42㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>토공사&gt;연약지반-매트부설(PP, PET)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="C28" s="135" t="n">
+        <v>3571</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3,571㎡/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>토공사&gt;연약지반-샌드매트 포설 (불도저(습지) 13톤)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C29" s="135" t="n">
+        <v>421</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>421㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>토공사&gt;연약지반-플라스틱 보드 드레인(PBD) (PBD L=25m 이하)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C30" s="135" t="n">
+        <v>9396</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>9,396m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>토공사&gt;연약지반-침하토, 과재쌓기 (과재쌓기, 모터그레이더)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C31" s="135" t="n">
+        <v>1597</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1,597㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>토공사&gt;연약지반-과재쌓기 제거 (불도저 19톤)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C32" s="135" t="n">
+        <v>383</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>383㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>토공사&gt;연약지반-활동방지공(S.C.P) (모래다짐말뚝 L=25m (원문 표기: 모대다짐말뚝))</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>본</t>
+        </is>
+      </c>
+      <c r="C33" s="135" t="n">
+        <v>14</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>14본/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>토공사&gt;연약지반-지반보강(고압분사주입공법) (직경 800mm, L=25m)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>본</t>
+        </is>
+      </c>
+      <c r="C34" s="135" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2.2본/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>토공사&gt;비탈면 보호공 (평떼)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="C35" s="135" t="n">
+        <v>505</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>505㎡/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>토공사&gt;비탈면 보강공 (천공/보강재-연암)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C36" s="135" t="n">
+        <v>64</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>64m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>배수공사&gt;암거공-지중강판 (B=5m, L=15m)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>15m/1span</t>
+        </is>
+      </c>
+      <c r="C37" s="135" t="n">
+        <v>0.02380952380952381</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>42일/15m/1span</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>배수공사&gt;암거공-철근콘크리트 (B=3m, H=1.8m, L=15m)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>15m/1span</t>
+        </is>
+      </c>
+      <c r="C38" s="135" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>27일/15m/1span</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>배수공사&gt;암거공-날개벽 (B=2.5m, H=2.4m, L=5m (옹벽식))</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>개소</t>
+        </is>
+      </c>
+      <c r="C39" s="135" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>13일/개소</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>배수공사&gt;배수관-흄관, V.R관 (직경 600mm, 고무링접합)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C40" s="135" t="n">
+        <v>43</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>43m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>배수공사&gt;배수관-강관 (직경 800mm, 접합제외)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C41" s="135" t="n">
+        <v>38</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>38m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>배수공사&gt;배수관-강관압입추진 (직경 800mm, 접합제외)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C42" s="135" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>배수공사&gt;옹벽-콘크리트옹벽 (B=4m, H=5m, L=15m)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>15m/1span</t>
+        </is>
+      </c>
+      <c r="C43" s="135" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>25일/15m/1span</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>배수공사&gt;옹벽-보강토옹벽 (블록식, 뒤채움 제외)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="C44" s="135" t="n">
+        <v>14</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>14㎡/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>배수공사&gt;측구공-L형측구 (B=0.9m, H=2.3m, L=20m)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>20m/1span</t>
+        </is>
+      </c>
+      <c r="C45" s="135" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8일/20m/1span</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>배수공사&gt;측구공-U형측구 (B=1.08m, H=1.0m, L=20m)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>20m/1span</t>
+        </is>
+      </c>
+      <c r="C46" s="135" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>9일/20m/1span</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>배수공사&gt;측구공-V형측구 (B=1.46m, H=0.8m, L=20m)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>20m/1span</t>
+        </is>
+      </c>
+      <c r="C47" s="135" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>8일/20m/1span</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>배수공사&gt;측구공-산마루 측구 (B=1.34m, H=1.15m, L=20m)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>20m/1span</t>
+        </is>
+      </c>
+      <c r="C48" s="135" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>8일/20m/1span</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>포장공사&gt;아스팔트포장 1단계-작업준비 (스틱 설치간격 10m)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C49" s="135" t="n">
+        <v>1900</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1,900m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>포장공사&gt;아스팔트포장 1단계-작업준비 (스틱 설치간격 6m)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C50" s="135" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1,600m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>포장공사&gt;아스팔트포장 1단계-작업준비 인수인계/위치측량 (고정 5일)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>식</t>
+        </is>
+      </c>
+      <c r="C51" s="135" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>5일</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>포장공사&gt;아스팔트포장 1단계-동상방지층(선택) (대형 다짐장비, 본선 포설)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C52" s="135" t="n">
+        <v>600</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>600㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>포장공사&gt;아스팔트포장 1단계-보조기층 (대형 다짐장비, 본선 포설)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C53" s="135" t="n">
+        <v>550</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>550㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>포장공사&gt;아스팔트포장 2단계-작업준비 (스틱 설치간격 10m)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C54" s="135" t="n">
+        <v>1900</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1,900m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>포장공사&gt;아스팔트포장 2단계-작업준비 (스틱 설치간격 6m)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C55" s="135" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1,600m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>포장공사&gt;아스팔트포장 2단계-작업준비 자재발주/유도선 (고정 3일)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>식</t>
+        </is>
+      </c>
+      <c r="C56" s="135" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3일</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>포장공사&gt;아스팔트포장 2단계-택코팅 (역청재 살포)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="C57" s="135" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>20,000㎡/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>포장공사&gt;아스팔트포장 2단계-프라임코팅 (역청재 살포 (양생 2일 별도 계상))</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="C58" s="135" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>20,000㎡/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>포장공사&gt;아스팔트포장 2단계-기층 (시공폭 3m 이상, 두께 5~7㎝)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="C59" s="135" t="n">
+        <v>4900</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>4,900㎡/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>포장공사&gt;아스팔트포장 2단계-기층 (시공폭 3m 이상, 두께 8~10㎝)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="C60" s="135" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>4,500㎡/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>포장공사&gt;아스팔트포장 2단계-중간층/표층 (시공폭 3m 이상, 5~7㎝)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="C61" s="135" t="n">
+        <v>4800</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>4,800㎡/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>포장공사&gt;아스팔트포장-부대공사 (차선도색, 안전시설 (준공 전))</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>km</t>
+        </is>
+      </c>
+      <c r="C62" s="135" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3일/km</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>포장공사&gt;콘크리트포장 1단계-작업준비 (스틱 설치간격 10m)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C63" s="135" t="n">
+        <v>1900</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1,900m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>포장공사&gt;콘크리트포장 1단계-작업준비 (스틱 설치간격 6m)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C64" s="135" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1,600m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>포장공사&gt;콘크리트포장 1단계-작업준비 인수인계/위치측량 (고정 5일)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>식</t>
+        </is>
+      </c>
+      <c r="C65" s="135" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>5일</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>포장공사&gt;콘크리트포장 1단계-동상방지층(선택) (대형 다짐장비, 본선 포설)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C66" s="135" t="n">
+        <v>600</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>600㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>포장공사&gt;콘크리트포장 1단계-린콘크리트 (린 콘크리트 기층 포설)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C67" s="135" t="n">
+        <v>550</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>550㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>포장공사&gt;콘크리트포장 2단계-작업준비 (스틱 설치간격 10m)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C68" s="135" t="n">
+        <v>1900</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1,900m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>포장공사&gt;콘크리트포장 2단계-작업준비 (스틱 설치간격 6m)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C69" s="135" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1,600m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>포장공사&gt;콘크리트포장 2단계-작업준비 자재발주/유도선 (고정 3일)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>식</t>
+        </is>
+      </c>
+      <c r="C70" s="135" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>3일</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>포장공사&gt;콘크리트포장 2단계-콘크리트표층 (일반구간 1차로 (교량구간 별도))</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C71" s="135" t="n">
+        <v>300</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>300㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>포장공사&gt;콘크리트포장 2단계-콘크리트표층 (일반구간 2차로 (교량구간 별도))</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>㎥</t>
+        </is>
+      </c>
+      <c r="C72" s="135" t="n">
+        <v>700</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>700㎥/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>포장공사&gt;콘크리트포장 2단계-포장절단 및 줄눈설치 (표층 포설기간에 추가)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>식</t>
+        </is>
+      </c>
+      <c r="C73" s="135" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>3일</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>포장공사&gt;콘크리트포장-부대공사 (차선도색, 안전시설 (준공 전))</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>km</t>
+        </is>
+      </c>
+      <c r="C74" s="135" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>3일/km</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>교량공사&gt;기초공-직접기초</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>개소</t>
+        </is>
+      </c>
+      <c r="C75" s="135" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>18일/개소</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>교량공사&gt;기초공-말뚝기초 (SDA)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>본</t>
+        </is>
+      </c>
+      <c r="C76" s="135" t="n">
+        <v>10</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>10본/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>교량공사&gt;하부공-교대 벽체 (1Lot=2.5m)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="C77" s="135" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>10일/1Lot</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>교량공사&gt;하부공-교각 기둥 (1Lot=3.0m)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="C78" s="135" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>7일/1Lot</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>교량공사&gt;하부공-교각 코핑</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>개소</t>
+        </is>
+      </c>
+      <c r="C79" s="135" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>20일/개소</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>교량공사&gt;하부공-부지조성 (토공사(부지 조성 및 평탄화))</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>식</t>
+        </is>
+      </c>
+      <c r="C80" s="135" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>10일</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>교량공사&gt;상부공-거더 제작</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>본</t>
+        </is>
+      </c>
+      <c r="C81" s="135" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>18일/본</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>교량공사&gt;상부공-거더 운반 및 거치</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>본</t>
+        </is>
+      </c>
+      <c r="C82" s="135" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2본/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>교량공사&gt;상부공-상부슬래브 (1경간 기준 (2경간이면 40일))</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>경간</t>
+        </is>
+      </c>
+      <c r="C83" s="135" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>25일/1경간</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>교량공사&gt;상부공-교면포장(LMC) 포설</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="C84" s="135" t="n">
+        <v>200</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>200㎡/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>교량공사&gt;상부공-교면포장(LMC) 마무리</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>경간</t>
+        </is>
+      </c>
+      <c r="C85" s="135" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>8일/경간</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>교량공사&gt;교량부대공사 (교량난간+배수시설+방음벽 등)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>교량</t>
+        </is>
+      </c>
+      <c r="C86" s="135" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>15일/교량</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>터널공사&gt;갱구부 보강-시점부</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>개소</t>
+        </is>
+      </c>
+      <c r="C87" s="135" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>25일/개소</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>터널공사&gt;갱구부 보강-종점부</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>개소</t>
+        </is>
+      </c>
+      <c r="C88" s="135" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>25일/개소</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>터널공사&gt;굴착 및 보강-P-1</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C89" s="135" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>4.3m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>터널공사&gt;굴착 및 보강-P-2</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C90" s="135" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>4.1m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>터널공사&gt;굴착 및 보강-P-3</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C91" s="135" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2.9m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>터널공사&gt;굴착 및 보강-P-4 상반</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C92" s="135" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2.6m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>터널공사&gt;굴착 및 보강-P-4 하반</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C93" s="135" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>7.1m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>터널공사&gt;굴착 및 보강-P-5 상반</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C94" s="135" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2.2m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>터널공사&gt;굴착 및 보강-P-5 하반</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C95" s="135" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3.6m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>터널공사&gt;굴착 및 보강-P-6 상반</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C96" s="135" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2.2m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>터널공사&gt;굴착 및 보강-P-6 하반</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C97" s="135" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2.9m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>터널공사&gt;보조공법-강관보강 그라우팅</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>개소</t>
+        </is>
+      </c>
+      <c r="C98" s="135" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3일/개소</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>터널공사&gt;보조공법-차수 그라우팅</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>개소</t>
+        </is>
+      </c>
+      <c r="C99" s="135" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>5일/개소</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>터널공사&gt;후속공종-방수</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C100" s="135" t="n">
+        <v>50</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>50m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>터널공사&gt;후속공종-배수공동구</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C101" s="135" t="n">
+        <v>8.333333333333334</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>25m/3일</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>터널공사&gt;후속공종-라이닝 콘크리트</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C102" s="135" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>10m/3일</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>터널공사&gt;후속공종-갱문조성</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>개소</t>
+        </is>
+      </c>
+      <c r="C103" s="135" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>25일/개소</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>부대공사&gt;중앙분리대 (H=1.27m)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C104" s="135" t="n">
+        <v>300</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>300m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>부대공사&gt;가드레일 (판설치(2W), 지주간격 2m)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="C105" s="135" t="n">
+        <v>130</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>130개/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>부대공사&gt;방음벽 (H=7.0m 이하)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C106" s="135" t="n">
+        <v>19</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>19m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>부대공사&gt;표지판 (교통안전표지판)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>개소</t>
+        </is>
+      </c>
+      <c r="C107" s="135" t="n">
+        <v>5</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>5개소/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>부대공사&gt;VMS</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>개소</t>
+        </is>
+      </c>
+      <c r="C108" s="135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>1개소/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>부대공사&gt;낙석방지책 (L=300m, H=3m, 간격 3m)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C109" s="135" t="n">
+        <v>32</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>32m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>부대공사&gt;낙석방지망 (기계작업)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="C110" s="135" t="n">
+        <v>85</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>85㎡/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>부대공사&gt;시선유도표지 (가드레일용)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="C111" s="135" t="n">
+        <v>150</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>150개/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>부대공사&gt;분리대병</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="C112" s="135" t="n">
+        <v>70</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>70개/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>부대공사&gt;방초매트</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="C113" s="135" t="n">
+        <v>600</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>600m/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>부대공사&gt;비점오염저감시설 (전처리조 5m×2m, 침투도랑 30m)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>개소</t>
+        </is>
+      </c>
+      <c r="C114" s="135" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>20일/개소</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>부대공사&gt;비탈면점검시설 (L=30m, B=1m, H=20m 이하)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>㎡</t>
+        </is>
+      </c>
+      <c r="C115" s="135" t="n">
+        <v>90</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>90㎡/일</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>※ 가이드라인 부록 4 '토목분야 &gt; 도로시설물'을 옮긴 것입니다. '일/개소' 형태는 1일 작업량을 1÷일수로 환산했습니다. 표에 없는 공종은 공종표에 직접 입력하세요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="92" min="1" max="1"/>
@@ -84863,14 +87194,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="135" t="inlineStr">
+      <c r="A1" s="136" t="inlineStr">
         <is>
           <t>토목 시설물 공사기간 산정 (가이드라인 부록 5 산정공식)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="45" customHeight="1" s="92">
-      <c r="A2" s="136" t="inlineStr">
+      <c r="A2" s="137" t="inlineStr">
         <is>
           <t>※ 노란 칸에 입력합니다. 산정값 Y는 비작업일수를 포함하므로, 준비기간과 정리기간만 더합니다. 적용범위를 넘으면 산정공식을 쓰지 말고 '공기산정(1일작업량)' 시트로 산정합니다.</t>
         </is>
@@ -84882,7 +87213,7 @@
           <t>시설물</t>
         </is>
       </c>
-      <c r="B4" s="137" t="inlineStr">
+      <c r="B4" s="138" t="inlineStr">
         <is>
           <t>도로포장</t>
         </is>
@@ -84894,7 +87225,7 @@
           <t>총공사비 C (백만원)</t>
         </is>
       </c>
-      <c r="B5" s="137" t="n"/>
+      <c r="B5" s="138" t="n"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>추정금액(추정가격+부가가치세+관급자재비)</t>
@@ -84907,9 +87238,9 @@
           <t>도로연장(m) L</t>
         </is>
       </c>
-      <c r="B6" s="137" t="n"/>
+      <c r="B6" s="138" t="n"/>
       <c r="C6">
-        <f>IF(INDEX(F23:F28,MATCH($B$4,$A$23:$A$28,0))=1,"← 필요","")</f>
+        <f>IF(INDEX(F25:F30,MATCH($B$4,$A$25:$A$30,0))=1,"← 필요","")</f>
         <v/>
       </c>
     </row>
@@ -84919,9 +87250,9 @@
           <t>도로폭원(m) W</t>
         </is>
       </c>
-      <c r="B7" s="137" t="n"/>
+      <c r="B7" s="138" t="n"/>
       <c r="C7">
-        <f>IF(INDEX(G23:G28,MATCH($B$4,$A$23:$A$28,0))=1,"← 필요","")</f>
+        <f>IF(INDEX(G25:G30,MATCH($B$4,$A$25:$A$30,0))=1,"← 필요","")</f>
         <v/>
       </c>
     </row>
@@ -84931,9 +87262,9 @@
           <t>교량연장(m) BL</t>
         </is>
       </c>
-      <c r="B8" s="137" t="n"/>
+      <c r="B8" s="138" t="n"/>
       <c r="C8">
-        <f>IF(INDEX(H23:H28,MATCH($B$4,$A$23:$A$28,0))=1,"← 필요","")</f>
+        <f>IF(INDEX(H25:H30,MATCH($B$4,$A$25:$A$30,0))=1,"← 필요","")</f>
         <v/>
       </c>
     </row>
@@ -84943,9 +87274,9 @@
           <t>관경(mm) D</t>
         </is>
       </c>
-      <c r="B9" s="137" t="n"/>
+      <c r="B9" s="138" t="n"/>
       <c r="C9">
-        <f>IF(INDEX(I23:I28,MATCH($B$4,$A$23:$A$28,0))=1,"← 필요","")</f>
+        <f>IF(INDEX(I25:I30,MATCH($B$4,$A$25:$A$30,0))=1,"← 필요","")</f>
         <v/>
       </c>
     </row>
@@ -84955,9 +87286,9 @@
           <t>양수장/배수장/가압장 개수 S</t>
         </is>
       </c>
-      <c r="B10" s="137" t="n"/>
+      <c r="B10" s="138" t="n"/>
       <c r="C10">
-        <f>IF(INDEX(J23:J28,MATCH($B$4,$A$23:$A$28,0))=1,"← 필요","")</f>
+        <f>IF(INDEX(J25:J30,MATCH($B$4,$A$25:$A$30,0))=1,"← 필요","")</f>
         <v/>
       </c>
     </row>
@@ -84967,9 +87298,9 @@
           <t>하수도 연장(m) SL</t>
         </is>
       </c>
-      <c r="B11" s="137" t="n"/>
+      <c r="B11" s="138" t="n"/>
       <c r="C11">
-        <f>IF(INDEX(K23:K28,MATCH($B$4,$A$23:$A$28,0))=1,"← 필요","")</f>
+        <f>IF(INDEX(K25:K30,MATCH($B$4,$A$25:$A$30,0))=1,"← 필요","")</f>
         <v/>
       </c>
     </row>
@@ -84979,30 +87310,30 @@
           <t>궤도연장(m) RL</t>
         </is>
       </c>
-      <c r="B12" s="137" t="n"/>
+      <c r="B12" s="138" t="n"/>
       <c r="C12">
-        <f>IF(INDEX(L23:L28,MATCH($B$4,$A$23:$A$28,0))=1,"← 필요","")</f>
+        <f>IF(INDEX(L25:L30,MATCH($B$4,$A$25:$A$30,0))=1,"← 필요","")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="131" t="inlineStr">
         <is>
-          <t>준비기간 (일)</t>
-        </is>
-      </c>
-      <c r="B14" s="137" t="n">
-        <v>60</v>
+          <t>준비기간 (일, 직접 입력)</t>
+        </is>
+      </c>
+      <c r="B14" s="138" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="131" t="inlineStr">
         <is>
-          <t>정리기간 (일)</t>
-        </is>
-      </c>
-      <c r="B15" s="137" t="n">
-        <v>30</v>
+          <t>정리기간 (일, 직접 입력)</t>
+        </is>
+      </c>
+      <c r="B15" s="138" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -85011,8 +87342,8 @@
           <t>적용범위 판정</t>
         </is>
       </c>
-      <c r="B17" s="138">
-        <f>IF(NOT(ISNUMBER(B5)),"총공사비를 입력하세요",IF(AND(B5&gt;=INDEX($C$23:$C$28,MATCH($B$4,$A$23:$A$28,0)),B5&lt;=INDEX($D$23:$D$28,MATCH($B$4,$A$23:$A$28,0))),"적용범위 이내 (산정공식 사용 가능)","적용범위 초과 → 산정공식 사용 불가. 1일 작업량 방식으로 산정하세요"))</f>
+      <c r="B17" s="139">
+        <f>IF(NOT(ISNUMBER(B5)),"총공사비를 입력하세요",IF(AND(B5&gt;=INDEX($C$25:$C$30,MATCH($B$4,$A$25:$A$30,0)),B5&lt;=INDEX($D$25:$D$30,MATCH($B$4,$A$25:$A$30,0))),"적용범위 이내 (산정공식 사용 가능)","적용범위 초과 → 산정공식 사용 불가. 1일 작업량 방식으로 산정하세요"))</f>
         <v/>
       </c>
     </row>
@@ -85022,7 +87353,7 @@
           <t>산정공식 값 Y (일)</t>
         </is>
       </c>
-      <c r="B18" s="138">
+      <c r="B18" s="139">
         <f>IF(LEFT(B17,4)="적용범위",IF(ISNUMBER(SEARCH("이내",B17)),IFERROR(ROUND(IF($B$4="도로포장",-637.009+173.198*LN(B6)+0.049*B5,IF($B$4="도로(토공+교량)",-160.855-14.288*B7+164.473*LN(B6)-1.474*B8+0.052*B5,IF($B$4="농업용수",-2251.569+415.137*LN(B5),IF($B$4="상수도",-1175.174+119.731*B10-0.273*B9+222.426*LN(B5),IF($B$4="하수도",-452.433+98.364*LN(B11)+0.083*B5,-1723.316-74.26*LN(B12)+372.266*LN(B5)))))),0),"입력 확인"),"적용불가"),"")</f>
         <v/>
       </c>
@@ -85033,7 +87364,7 @@
           <t>공사기간 (Y + 준비 + 정리, 일)</t>
         </is>
       </c>
-      <c r="B19" s="138">
+      <c r="B19" s="139">
         <f>IF(ISNUMBER(B18),B18+B14+B15,"-")</f>
         <v/>
       </c>
@@ -85044,326 +87375,334 @@
           <t>환산 (개월)</t>
         </is>
       </c>
-      <c r="B20" s="138">
+      <c r="B20" s="139">
         <f>IF(ISNUMBER(B19),ROUND(B19/30,1),"-")</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="21" ht="32" customHeight="1" s="92">
+      <c r="A21" s="137" t="inlineStr">
+        <is>
+          <t>※ 산정공식은 과거 공사 실적의 회귀식(평균값)이라, 소규모 공사는 실제 공기보다 크게 나올 수 있습니다. 이 값은 적정성 검토용이며 최종 공기는 1일 작업량 방식으로 산정하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>▼ 시설물별 산정공식과 적용범위 (부록 5)  Y=공사기간(일), 금액 단위는 백만원(농업용수·상수도 등 범위는 억원을 백만원으로 환산)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="134" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="134" t="inlineStr">
         <is>
           <t>시설물</t>
         </is>
       </c>
-      <c r="B22" s="134" t="inlineStr">
+      <c r="B24" s="134" t="inlineStr">
         <is>
           <t>산정공식</t>
         </is>
       </c>
-      <c r="C22" s="134" t="inlineStr">
+      <c r="C24" s="134" t="inlineStr">
         <is>
           <t>총공사비 하한(백만원)</t>
         </is>
       </c>
-      <c r="D22" s="134" t="inlineStr">
+      <c r="D24" s="134" t="inlineStr">
         <is>
           <t>총공사비 상한(백만원)</t>
         </is>
       </c>
-      <c r="E22" s="134" t="inlineStr"/>
-      <c r="F22" s="134" t="inlineStr">
+      <c r="E24" s="134" t="inlineStr"/>
+      <c r="F24" s="134" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="G22" s="134" t="inlineStr">
+      <c r="G24" s="134" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="H22" s="134" t="inlineStr">
+      <c r="H24" s="134" t="inlineStr">
         <is>
           <t>BL</t>
         </is>
       </c>
-      <c r="I22" s="134" t="inlineStr">
+      <c r="I24" s="134" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="J22" s="134" t="inlineStr">
+      <c r="J24" s="134" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="K22" s="134" t="inlineStr">
+      <c r="K24" s="134" t="inlineStr">
         <is>
           <t>SL</t>
         </is>
       </c>
-      <c r="L22" s="134" t="inlineStr">
+      <c r="L24" s="134" t="inlineStr">
         <is>
           <t>RL</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="139" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="140" t="inlineStr">
         <is>
           <t>도로포장</t>
         </is>
       </c>
-      <c r="B23" s="139" t="inlineStr">
+      <c r="B25" s="140" t="inlineStr">
         <is>
           <t>Y = -637.009 + 173.198×ln(L) + 0.049×C</t>
         </is>
       </c>
-      <c r="C23" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="139" t="n">
+      <c r="C25" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="140" t="n">
         <v>35000</v>
       </c>
-      <c r="E23" s="139" t="n"/>
-      <c r="F23" s="139" t="n">
+      <c r="E25" s="140" t="n"/>
+      <c r="F25" s="140" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="139" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="139" t="inlineStr">
+      <c r="G25" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="140" t="inlineStr">
         <is>
           <t>도로(토공+교량)</t>
         </is>
       </c>
-      <c r="B24" s="139" t="inlineStr">
+      <c r="B26" s="140" t="inlineStr">
         <is>
           <t>Y = -160.855 - 14.288×W + 164.473×ln(L) - 1.474×BL + 0.052×C</t>
         </is>
       </c>
-      <c r="C24" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="139" t="n">
+      <c r="C26" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="140" t="n">
         <v>35000</v>
       </c>
-      <c r="E24" s="139" t="n"/>
-      <c r="F24" s="139" t="n">
+      <c r="E26" s="140" t="n"/>
+      <c r="F26" s="140" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="139" t="n">
+      <c r="G26" s="140" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="139" t="n">
+      <c r="H26" s="140" t="n">
         <v>1</v>
       </c>
-      <c r="I24" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="139" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="139" t="inlineStr">
+      <c r="I26" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="140" t="inlineStr">
         <is>
           <t>농업용수</t>
         </is>
       </c>
-      <c r="B25" s="139" t="inlineStr">
+      <c r="B27" s="140" t="inlineStr">
         <is>
           <t>Y = -2251.569 + 415.137×ln(C)</t>
         </is>
       </c>
-      <c r="C25" s="139" t="n">
+      <c r="C27" s="140" t="n">
         <v>1000</v>
       </c>
-      <c r="D25" s="139" t="n">
+      <c r="D27" s="140" t="n">
         <v>20000</v>
       </c>
-      <c r="E25" s="139" t="n"/>
-      <c r="F25" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="139" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="139" t="inlineStr">
+      <c r="E27" s="140" t="n"/>
+      <c r="F27" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="140" t="inlineStr">
         <is>
           <t>상수도</t>
         </is>
       </c>
-      <c r="B26" s="139" t="inlineStr">
+      <c r="B28" s="140" t="inlineStr">
         <is>
           <t>Y = -1175.174 + 119.731×S - 0.273×D + 222.426×ln(C)</t>
         </is>
       </c>
-      <c r="C26" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="139" t="n">
+      <c r="C28" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="140" t="n">
         <v>8000</v>
       </c>
-      <c r="E26" s="139" t="n"/>
-      <c r="F26" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="139" t="n">
+      <c r="E28" s="140" t="n"/>
+      <c r="F28" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="140" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="139" t="n">
+      <c r="J28" s="140" t="n">
         <v>1</v>
       </c>
-      <c r="K26" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="139" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="139" t="inlineStr">
+      <c r="K28" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="140" t="inlineStr">
         <is>
           <t>하수도</t>
         </is>
       </c>
-      <c r="B27" s="139" t="inlineStr">
+      <c r="B29" s="140" t="inlineStr">
         <is>
           <t>Y = -452.433 + 98.364×ln(SL) + 0.083×C</t>
         </is>
       </c>
-      <c r="C27" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="139" t="n">
+      <c r="C29" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="140" t="n">
         <v>15000</v>
       </c>
-      <c r="E27" s="139" t="n"/>
-      <c r="F27" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="139" t="n">
+      <c r="E29" s="140" t="n"/>
+      <c r="F29" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="140" t="n">
         <v>1</v>
       </c>
-      <c r="L27" s="139" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="139" t="inlineStr">
+      <c r="L29" s="140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="140" t="inlineStr">
         <is>
           <t>철도(궤도)</t>
         </is>
       </c>
-      <c r="B28" s="139" t="inlineStr">
+      <c r="B30" s="140" t="inlineStr">
         <is>
           <t>Y = -1723.316 - 74.260×ln(RL) + 372.266×ln(C)</t>
         </is>
       </c>
-      <c r="C28" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="139" t="n">
+      <c r="C30" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="140" t="n">
         <v>120000</v>
       </c>
-      <c r="E28" s="139" t="n"/>
-      <c r="F28" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="139" t="n">
+      <c r="E30" s="140" t="n"/>
+      <c r="F30" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="140" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>※ ln은 자연로그. 상수도는 다종의 관일 때 물량이 가장 많거나 가장 큰 관경을 적용. 도로포장은 토공+교량이 함께 있으면 '도로(토공+교량)' 공식을 적용. 철도(궤도)는 설비 부분 공기 별도.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -85374,7 +87713,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -85383,8 +87722,8 @@
   <dimension ref="A1:P119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" style="92" min="1" max="1"/>
-    <col width="34" customWidth="1" style="92" min="2" max="2"/>
+    <col width="60" customWidth="1" style="92" min="1" max="1"/>
+    <col width="20" customWidth="1" style="92" min="2" max="2"/>
     <col width="14" customWidth="1" style="92" min="3" max="3"/>
     <col width="14" customWidth="1" style="92" min="4" max="4"/>
     <col width="14" customWidth="1" style="92" min="5" max="5"/>
@@ -85398,14 +87737,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="135" t="inlineStr">
+      <c r="A1" s="136" t="inlineStr">
         <is>
           <t>1일 작업량에 의한 공사기간 산정 (가이드라인 제2장)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="48" customHeight="1" s="92">
-      <c r="A2" s="136" t="inlineStr">
+      <c r="A2" s="137" t="inlineStr">
         <is>
           <t>공사기간 = 준비기간 + 주공정(CP) 공종별 공사기간의 합 + 정리기간,  공종별 공사기간 = 작업일수 + 비작업일수.  월별 비작업일수 = A(기후)+B(공휴일)-C(A×B÷달력일수), 월 8일(주40시간) 미만이면 8일 적용.  공종은 입력 순서대로 이어서 시공하는 것으로 계산합니다. 준비·정리기간에는 비작업일수를 넣지 않습니다.</t>
         </is>
@@ -85417,7 +87756,7 @@
           <t>기상 지점</t>
         </is>
       </c>
-      <c r="B4" s="137" t="inlineStr">
+      <c r="B4" s="138" t="inlineStr">
         <is>
           <t>서울</t>
         </is>
@@ -85433,7 +87772,7 @@
           <t>본공사 착수 연도</t>
         </is>
       </c>
-      <c r="B5" s="137" t="n">
+      <c r="B5" s="138" t="n">
         <v>2026</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -85448,7 +87787,7 @@
           <t>본공사 착수 월</t>
         </is>
       </c>
-      <c r="B6" s="137" t="n">
+      <c r="B6" s="138" t="n">
         <v>7</v>
       </c>
     </row>
@@ -85458,7 +87797,7 @@
           <t>준비기간 (일)</t>
         </is>
       </c>
-      <c r="B7" s="137">
+      <c r="B7" s="138">
         <f>'시설물별공기(토목)'!B14</f>
         <v/>
       </c>
@@ -85469,7 +87808,7 @@
           <t>정리기간 (일)</t>
         </is>
       </c>
-      <c r="B8" s="137">
+      <c r="B8" s="138">
         <f>'시설물별공기(토목)'!B15</f>
         <v/>
       </c>
@@ -85564,872 +87903,872 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="139" t="n">
+      <c r="A12" s="140" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="139" t="inlineStr">
+      <c r="B12" s="140" t="inlineStr">
         <is>
           <t>혹서기：체감온도 33°C 이상</t>
         </is>
       </c>
-      <c r="C12" s="137" t="inlineStr">
+      <c r="C12" s="138" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="D12" s="139">
+      <c r="D12" s="140">
         <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
         <v/>
       </c>
-      <c r="E12" s="139">
+      <c r="E12" s="140">
         <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
         <v/>
       </c>
-      <c r="F12" s="139">
+      <c r="F12" s="140">
         <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
         <v/>
       </c>
-      <c r="G12" s="139">
+      <c r="G12" s="140">
         <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
         <v/>
       </c>
-      <c r="H12" s="139">
+      <c r="H12" s="140">
         <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
         <v/>
       </c>
-      <c r="I12" s="139">
+      <c r="I12" s="140">
         <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
         <v/>
       </c>
-      <c r="J12" s="139">
+      <c r="J12" s="140">
         <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
         <v/>
       </c>
-      <c r="K12" s="139">
+      <c r="K12" s="140">
         <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
         <v/>
       </c>
-      <c r="L12" s="139">
+      <c r="L12" s="140">
         <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
         <v/>
       </c>
-      <c r="M12" s="139">
+      <c r="M12" s="140">
         <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
         <v/>
       </c>
-      <c r="N12" s="139">
+      <c r="N12" s="140">
         <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
         <v/>
       </c>
-      <c r="O12" s="139">
+      <c r="O12" s="140">
         <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A12)</f>
         <v/>
       </c>
-      <c r="P12" s="139">
+      <c r="P12" s="140">
         <f>SUM(D12:O12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="139" t="n">
+      <c r="A13" s="140" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="139" t="inlineStr">
+      <c r="B13" s="140" t="inlineStr">
         <is>
           <t>혹서기：체감온도 35°C 이상</t>
         </is>
       </c>
-      <c r="C13" s="137" t="inlineStr">
+      <c r="C13" s="138" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D13" s="139">
+      <c r="D13" s="140">
         <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
         <v/>
       </c>
-      <c r="E13" s="139">
+      <c r="E13" s="140">
         <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
         <v/>
       </c>
-      <c r="F13" s="139">
+      <c r="F13" s="140">
         <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
         <v/>
       </c>
-      <c r="G13" s="139">
+      <c r="G13" s="140">
         <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
         <v/>
       </c>
-      <c r="H13" s="139">
+      <c r="H13" s="140">
         <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
         <v/>
       </c>
-      <c r="I13" s="139">
+      <c r="I13" s="140">
         <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
         <v/>
       </c>
-      <c r="J13" s="139">
+      <c r="J13" s="140">
         <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
         <v/>
       </c>
-      <c r="K13" s="139">
+      <c r="K13" s="140">
         <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
         <v/>
       </c>
-      <c r="L13" s="139">
+      <c r="L13" s="140">
         <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
         <v/>
       </c>
-      <c r="M13" s="139">
+      <c r="M13" s="140">
         <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
         <v/>
       </c>
-      <c r="N13" s="139">
+      <c r="N13" s="140">
         <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
         <v/>
       </c>
-      <c r="O13" s="139">
+      <c r="O13" s="140">
         <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A13)</f>
         <v/>
       </c>
-      <c r="P13" s="139">
+      <c r="P13" s="140">
         <f>SUM(D13:O13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="139" t="n">
+      <c r="A14" s="140" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="139" t="inlineStr">
+      <c r="B14" s="140" t="inlineStr">
         <is>
           <t>혹서기：일최고온도 33°C 이상</t>
         </is>
       </c>
-      <c r="C14" s="137" t="inlineStr">
+      <c r="C14" s="138" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D14" s="139">
+      <c r="D14" s="140">
         <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
         <v/>
       </c>
-      <c r="E14" s="139">
+      <c r="E14" s="140">
         <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
         <v/>
       </c>
-      <c r="F14" s="139">
+      <c r="F14" s="140">
         <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
         <v/>
       </c>
-      <c r="G14" s="139">
+      <c r="G14" s="140">
         <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
         <v/>
       </c>
-      <c r="H14" s="139">
+      <c r="H14" s="140">
         <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
         <v/>
       </c>
-      <c r="I14" s="139">
+      <c r="I14" s="140">
         <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
         <v/>
       </c>
-      <c r="J14" s="139">
+      <c r="J14" s="140">
         <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
         <v/>
       </c>
-      <c r="K14" s="139">
+      <c r="K14" s="140">
         <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
         <v/>
       </c>
-      <c r="L14" s="139">
+      <c r="L14" s="140">
         <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
         <v/>
       </c>
-      <c r="M14" s="139">
+      <c r="M14" s="140">
         <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
         <v/>
       </c>
-      <c r="N14" s="139">
+      <c r="N14" s="140">
         <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
         <v/>
       </c>
-      <c r="O14" s="139">
+      <c r="O14" s="140">
         <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A14)</f>
         <v/>
       </c>
-      <c r="P14" s="139">
+      <c r="P14" s="140">
         <f>SUM(D14:O14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="139" t="n">
+      <c r="A15" s="140" t="n">
         <v>4</v>
       </c>
-      <c r="B15" s="139" t="inlineStr">
+      <c r="B15" s="140" t="inlineStr">
         <is>
           <t>혹서기：일최고온도 35°C 이상</t>
         </is>
       </c>
-      <c r="C15" s="137" t="inlineStr">
+      <c r="C15" s="138" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D15" s="139">
+      <c r="D15" s="140">
         <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
         <v/>
       </c>
-      <c r="E15" s="139">
+      <c r="E15" s="140">
         <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
         <v/>
       </c>
-      <c r="F15" s="139">
+      <c r="F15" s="140">
         <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
         <v/>
       </c>
-      <c r="G15" s="139">
+      <c r="G15" s="140">
         <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
         <v/>
       </c>
-      <c r="H15" s="139">
+      <c r="H15" s="140">
         <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
         <v/>
       </c>
-      <c r="I15" s="139">
+      <c r="I15" s="140">
         <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
         <v/>
       </c>
-      <c r="J15" s="139">
+      <c r="J15" s="140">
         <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
         <v/>
       </c>
-      <c r="K15" s="139">
+      <c r="K15" s="140">
         <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
         <v/>
       </c>
-      <c r="L15" s="139">
+      <c r="L15" s="140">
         <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
         <v/>
       </c>
-      <c r="M15" s="139">
+      <c r="M15" s="140">
         <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
         <v/>
       </c>
-      <c r="N15" s="139">
+      <c r="N15" s="140">
         <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
         <v/>
       </c>
-      <c r="O15" s="139">
+      <c r="O15" s="140">
         <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A15)</f>
         <v/>
       </c>
-      <c r="P15" s="139">
+      <c r="P15" s="140">
         <f>SUM(D15:O15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="139" t="n">
+      <c r="A16" s="140" t="n">
         <v>5</v>
       </c>
-      <c r="B16" s="139" t="inlineStr">
+      <c r="B16" s="140" t="inlineStr">
         <is>
           <t>동절기：일최고기온 0°C 이하</t>
         </is>
       </c>
-      <c r="C16" s="137" t="inlineStr">
+      <c r="C16" s="138" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="D16" s="139">
+      <c r="D16" s="140">
         <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
         <v/>
       </c>
-      <c r="E16" s="139">
+      <c r="E16" s="140">
         <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
         <v/>
       </c>
-      <c r="F16" s="139">
+      <c r="F16" s="140">
         <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
         <v/>
       </c>
-      <c r="G16" s="139">
+      <c r="G16" s="140">
         <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
         <v/>
       </c>
-      <c r="H16" s="139">
+      <c r="H16" s="140">
         <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
         <v/>
       </c>
-      <c r="I16" s="139">
+      <c r="I16" s="140">
         <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
         <v/>
       </c>
-      <c r="J16" s="139">
+      <c r="J16" s="140">
         <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
         <v/>
       </c>
-      <c r="K16" s="139">
+      <c r="K16" s="140">
         <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
         <v/>
       </c>
-      <c r="L16" s="139">
+      <c r="L16" s="140">
         <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
         <v/>
       </c>
-      <c r="M16" s="139">
+      <c r="M16" s="140">
         <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
         <v/>
       </c>
-      <c r="N16" s="139">
+      <c r="N16" s="140">
         <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
         <v/>
       </c>
-      <c r="O16" s="139">
+      <c r="O16" s="140">
         <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A16)</f>
         <v/>
       </c>
-      <c r="P16" s="139">
+      <c r="P16" s="140">
         <f>SUM(D16:O16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="139" t="n">
+      <c r="A17" s="140" t="n">
         <v>6</v>
       </c>
-      <c r="B17" s="139" t="inlineStr">
+      <c r="B17" s="140" t="inlineStr">
         <is>
           <t>동절기：일최심신적설 5㎝ 이상</t>
         </is>
       </c>
-      <c r="C17" s="137" t="inlineStr">
+      <c r="C17" s="138" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="D17" s="139">
+      <c r="D17" s="140">
         <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
         <v/>
       </c>
-      <c r="E17" s="139">
+      <c r="E17" s="140">
         <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
         <v/>
       </c>
-      <c r="F17" s="139">
+      <c r="F17" s="140">
         <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
         <v/>
       </c>
-      <c r="G17" s="139">
+      <c r="G17" s="140">
         <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
         <v/>
       </c>
-      <c r="H17" s="139">
+      <c r="H17" s="140">
         <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
         <v/>
       </c>
-      <c r="I17" s="139">
+      <c r="I17" s="140">
         <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
         <v/>
       </c>
-      <c r="J17" s="139">
+      <c r="J17" s="140">
         <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
         <v/>
       </c>
-      <c r="K17" s="139">
+      <c r="K17" s="140">
         <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
         <v/>
       </c>
-      <c r="L17" s="139">
+      <c r="L17" s="140">
         <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
         <v/>
       </c>
-      <c r="M17" s="139">
+      <c r="M17" s="140">
         <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
         <v/>
       </c>
-      <c r="N17" s="139">
+      <c r="N17" s="140">
         <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
         <v/>
       </c>
-      <c r="O17" s="139">
+      <c r="O17" s="140">
         <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A17)</f>
         <v/>
       </c>
-      <c r="P17" s="139">
+      <c r="P17" s="140">
         <f>SUM(D17:O17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="139" t="n">
+      <c r="A18" s="140" t="n">
         <v>7</v>
       </c>
-      <c r="B18" s="139" t="inlineStr">
+      <c r="B18" s="140" t="inlineStr">
         <is>
           <t>동절기：일최고기온 0°C 이하 이거나 일최심신적설 5㎝ 이상</t>
         </is>
       </c>
-      <c r="C18" s="137" t="inlineStr">
+      <c r="C18" s="138" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D18" s="139">
+      <c r="D18" s="140">
         <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
         <v/>
       </c>
-      <c r="E18" s="139">
+      <c r="E18" s="140">
         <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
         <v/>
       </c>
-      <c r="F18" s="139">
+      <c r="F18" s="140">
         <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
         <v/>
       </c>
-      <c r="G18" s="139">
+      <c r="G18" s="140">
         <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
         <v/>
       </c>
-      <c r="H18" s="139">
+      <c r="H18" s="140">
         <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
         <v/>
       </c>
-      <c r="I18" s="139">
+      <c r="I18" s="140">
         <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
         <v/>
       </c>
-      <c r="J18" s="139">
+      <c r="J18" s="140">
         <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
         <v/>
       </c>
-      <c r="K18" s="139">
+      <c r="K18" s="140">
         <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
         <v/>
       </c>
-      <c r="L18" s="139">
+      <c r="L18" s="140">
         <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
         <v/>
       </c>
-      <c r="M18" s="139">
+      <c r="M18" s="140">
         <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
         <v/>
       </c>
-      <c r="N18" s="139">
+      <c r="N18" s="140">
         <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
         <v/>
       </c>
-      <c r="O18" s="139">
+      <c r="O18" s="140">
         <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A18)</f>
         <v/>
       </c>
-      <c r="P18" s="139">
+      <c r="P18" s="140">
         <f>SUM(D18:O18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="139" t="n">
+      <c r="A19" s="140" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="139" t="inlineStr">
+      <c r="B19" s="140" t="inlineStr">
         <is>
           <t>동절기：일최저기온 -12°C 이하</t>
         </is>
       </c>
-      <c r="C19" s="137" t="inlineStr">
+      <c r="C19" s="138" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D19" s="139">
+      <c r="D19" s="140">
         <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
         <v/>
       </c>
-      <c r="E19" s="139">
+      <c r="E19" s="140">
         <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
         <v/>
       </c>
-      <c r="F19" s="139">
+      <c r="F19" s="140">
         <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
         <v/>
       </c>
-      <c r="G19" s="139">
+      <c r="G19" s="140">
         <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
         <v/>
       </c>
-      <c r="H19" s="139">
+      <c r="H19" s="140">
         <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
         <v/>
       </c>
-      <c r="I19" s="139">
+      <c r="I19" s="140">
         <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
         <v/>
       </c>
-      <c r="J19" s="139">
+      <c r="J19" s="140">
         <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
         <v/>
       </c>
-      <c r="K19" s="139">
+      <c r="K19" s="140">
         <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
         <v/>
       </c>
-      <c r="L19" s="139">
+      <c r="L19" s="140">
         <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
         <v/>
       </c>
-      <c r="M19" s="139">
+      <c r="M19" s="140">
         <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
         <v/>
       </c>
-      <c r="N19" s="139">
+      <c r="N19" s="140">
         <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
         <v/>
       </c>
-      <c r="O19" s="139">
+      <c r="O19" s="140">
         <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A19)</f>
         <v/>
       </c>
-      <c r="P19" s="139">
+      <c r="P19" s="140">
         <f>SUM(D19:O19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="139" t="n">
+      <c r="A20" s="140" t="n">
         <v>9</v>
       </c>
-      <c r="B20" s="139" t="inlineStr">
+      <c r="B20" s="140" t="inlineStr">
         <is>
           <t>일강수량：3㎜ 이상</t>
         </is>
       </c>
-      <c r="C20" s="137" t="inlineStr">
+      <c r="C20" s="138" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="D20" s="139">
+      <c r="D20" s="140">
         <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
         <v/>
       </c>
-      <c r="E20" s="139">
+      <c r="E20" s="140">
         <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
         <v/>
       </c>
-      <c r="F20" s="139">
+      <c r="F20" s="140">
         <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
         <v/>
       </c>
-      <c r="G20" s="139">
+      <c r="G20" s="140">
         <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
         <v/>
       </c>
-      <c r="H20" s="139">
+      <c r="H20" s="140">
         <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
         <v/>
       </c>
-      <c r="I20" s="139">
+      <c r="I20" s="140">
         <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
         <v/>
       </c>
-      <c r="J20" s="139">
+      <c r="J20" s="140">
         <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
         <v/>
       </c>
-      <c r="K20" s="139">
+      <c r="K20" s="140">
         <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
         <v/>
       </c>
-      <c r="L20" s="139">
+      <c r="L20" s="140">
         <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
         <v/>
       </c>
-      <c r="M20" s="139">
+      <c r="M20" s="140">
         <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
         <v/>
       </c>
-      <c r="N20" s="139">
+      <c r="N20" s="140">
         <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
         <v/>
       </c>
-      <c r="O20" s="139">
+      <c r="O20" s="140">
         <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A20)</f>
         <v/>
       </c>
-      <c r="P20" s="139">
+      <c r="P20" s="140">
         <f>SUM(D20:O20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="139" t="n">
+      <c r="A21" s="140" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="139" t="inlineStr">
+      <c r="B21" s="140" t="inlineStr">
         <is>
           <t>일강수량：5㎜ 이상</t>
         </is>
       </c>
-      <c r="C21" s="137" t="inlineStr">
+      <c r="C21" s="138" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D21" s="139">
+      <c r="D21" s="140">
         <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
         <v/>
       </c>
-      <c r="E21" s="139">
+      <c r="E21" s="140">
         <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
         <v/>
       </c>
-      <c r="F21" s="139">
+      <c r="F21" s="140">
         <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
         <v/>
       </c>
-      <c r="G21" s="139">
+      <c r="G21" s="140">
         <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
         <v/>
       </c>
-      <c r="H21" s="139">
+      <c r="H21" s="140">
         <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
         <v/>
       </c>
-      <c r="I21" s="139">
+      <c r="I21" s="140">
         <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
         <v/>
       </c>
-      <c r="J21" s="139">
+      <c r="J21" s="140">
         <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
         <v/>
       </c>
-      <c r="K21" s="139">
+      <c r="K21" s="140">
         <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
         <v/>
       </c>
-      <c r="L21" s="139">
+      <c r="L21" s="140">
         <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
         <v/>
       </c>
-      <c r="M21" s="139">
+      <c r="M21" s="140">
         <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
         <v/>
       </c>
-      <c r="N21" s="139">
+      <c r="N21" s="140">
         <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
         <v/>
       </c>
-      <c r="O21" s="139">
+      <c r="O21" s="140">
         <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A21)</f>
         <v/>
       </c>
-      <c r="P21" s="139">
+      <c r="P21" s="140">
         <f>SUM(D21:O21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="139" t="n">
+      <c r="A22" s="140" t="n">
         <v>11</v>
       </c>
-      <c r="B22" s="139" t="inlineStr">
+      <c r="B22" s="140" t="inlineStr">
         <is>
           <t>일강수량：10㎜ 이상</t>
         </is>
       </c>
-      <c r="C22" s="137" t="inlineStr">
+      <c r="C22" s="138" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D22" s="139">
+      <c r="D22" s="140">
         <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
         <v/>
       </c>
-      <c r="E22" s="139">
+      <c r="E22" s="140">
         <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
         <v/>
       </c>
-      <c r="F22" s="139">
+      <c r="F22" s="140">
         <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
         <v/>
       </c>
-      <c r="G22" s="139">
+      <c r="G22" s="140">
         <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
         <v/>
       </c>
-      <c r="H22" s="139">
+      <c r="H22" s="140">
         <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
         <v/>
       </c>
-      <c r="I22" s="139">
+      <c r="I22" s="140">
         <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
         <v/>
       </c>
-      <c r="J22" s="139">
+      <c r="J22" s="140">
         <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
         <v/>
       </c>
-      <c r="K22" s="139">
+      <c r="K22" s="140">
         <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
         <v/>
       </c>
-      <c r="L22" s="139">
+      <c r="L22" s="140">
         <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
         <v/>
       </c>
-      <c r="M22" s="139">
+      <c r="M22" s="140">
         <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
         <v/>
       </c>
-      <c r="N22" s="139">
+      <c r="N22" s="140">
         <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
         <v/>
       </c>
-      <c r="O22" s="139">
+      <c r="O22" s="140">
         <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A22)</f>
         <v/>
       </c>
-      <c r="P22" s="139">
+      <c r="P22" s="140">
         <f>SUM(D22:O22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="139" t="n">
+      <c r="A23" s="140" t="n">
         <v>12</v>
       </c>
-      <c r="B23" s="139" t="inlineStr">
+      <c r="B23" s="140" t="inlineStr">
         <is>
           <t>일강수량：20㎜ 이상</t>
         </is>
       </c>
-      <c r="C23" s="137" t="inlineStr">
+      <c r="C23" s="138" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D23" s="139">
+      <c r="D23" s="140">
         <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
         <v/>
       </c>
-      <c r="E23" s="139">
+      <c r="E23" s="140">
         <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
         <v/>
       </c>
-      <c r="F23" s="139">
+      <c r="F23" s="140">
         <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
         <v/>
       </c>
-      <c r="G23" s="139">
+      <c r="G23" s="140">
         <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
         <v/>
       </c>
-      <c r="H23" s="139">
+      <c r="H23" s="140">
         <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
         <v/>
       </c>
-      <c r="I23" s="139">
+      <c r="I23" s="140">
         <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
         <v/>
       </c>
-      <c r="J23" s="139">
+      <c r="J23" s="140">
         <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
         <v/>
       </c>
-      <c r="K23" s="139">
+      <c r="K23" s="140">
         <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
         <v/>
       </c>
-      <c r="L23" s="139">
+      <c r="L23" s="140">
         <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
         <v/>
       </c>
-      <c r="M23" s="139">
+      <c r="M23" s="140">
         <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
         <v/>
       </c>
-      <c r="N23" s="139">
+      <c r="N23" s="140">
         <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
         <v/>
       </c>
-      <c r="O23" s="139">
+      <c r="O23" s="140">
         <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A23)</f>
         <v/>
       </c>
-      <c r="P23" s="139">
+      <c r="P23" s="140">
         <f>SUM(D23:O23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="139" t="n">
+      <c r="A24" s="140" t="n">
         <v>13</v>
       </c>
-      <c r="B24" s="139" t="inlineStr">
+      <c r="B24" s="140" t="inlineStr">
         <is>
           <t>일최대순간풍속：15m/s 이상</t>
         </is>
       </c>
-      <c r="C24" s="137" t="inlineStr">
+      <c r="C24" s="138" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="D24" s="139">
+      <c r="D24" s="140">
         <f>SUMIFS(기상자료!$F$2:$F$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
         <v/>
       </c>
-      <c r="E24" s="139">
+      <c r="E24" s="140">
         <f>SUMIFS(기상자료!$G$2:$G$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
         <v/>
       </c>
-      <c r="F24" s="139">
+      <c r="F24" s="140">
         <f>SUMIFS(기상자료!$H$2:$H$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
         <v/>
       </c>
-      <c r="G24" s="139">
+      <c r="G24" s="140">
         <f>SUMIFS(기상자료!$I$2:$I$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
         <v/>
       </c>
-      <c r="H24" s="139">
+      <c r="H24" s="140">
         <f>SUMIFS(기상자료!$J$2:$J$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
         <v/>
       </c>
-      <c r="I24" s="139">
+      <c r="I24" s="140">
         <f>SUMIFS(기상자료!$K$2:$K$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
         <v/>
       </c>
-      <c r="J24" s="139">
+      <c r="J24" s="140">
         <f>SUMIFS(기상자료!$L$2:$L$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
         <v/>
       </c>
-      <c r="K24" s="139">
+      <c r="K24" s="140">
         <f>SUMIFS(기상자료!$M$2:$M$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
         <v/>
       </c>
-      <c r="L24" s="139">
+      <c r="L24" s="140">
         <f>SUMIFS(기상자료!$N$2:$N$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
         <v/>
       </c>
-      <c r="M24" s="139">
+      <c r="M24" s="140">
         <f>SUMIFS(기상자료!$O$2:$O$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
         <v/>
       </c>
-      <c r="N24" s="139">
+      <c r="N24" s="140">
         <f>SUMIFS(기상자료!$P$2:$P$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
         <v/>
       </c>
-      <c r="O24" s="139">
+      <c r="O24" s="140">
         <f>SUMIFS(기상자료!$Q$2:$Q$1236,기상자료!$A$2:$A$1236,INDEX(지점목록!$C$2:$C$96,MATCH($B$4,지점목록!$A$2:$A$96,0)),기상자료!$D$2:$D$1236,$A24)</f>
         <v/>
       </c>
-      <c r="P24" s="139">
+      <c r="P24" s="140">
         <f>SUM(D24:O24)</f>
         <v/>
       </c>
@@ -86440,51 +88779,51 @@
           <t>적용 조건 합계 (A: 기후여건)</t>
         </is>
       </c>
-      <c r="D25" s="140">
+      <c r="D25" s="141">
         <f>SUMPRODUCT(($C$12:$C$24="O")*D12:D24)</f>
         <v/>
       </c>
-      <c r="E25" s="140">
+      <c r="E25" s="141">
         <f>SUMPRODUCT(($C$12:$C$24="O")*E12:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="140">
+      <c r="F25" s="141">
         <f>SUMPRODUCT(($C$12:$C$24="O")*F12:F24)</f>
         <v/>
       </c>
-      <c r="G25" s="140">
+      <c r="G25" s="141">
         <f>SUMPRODUCT(($C$12:$C$24="O")*G12:G24)</f>
         <v/>
       </c>
-      <c r="H25" s="140">
+      <c r="H25" s="141">
         <f>SUMPRODUCT(($C$12:$C$24="O")*H12:H24)</f>
         <v/>
       </c>
-      <c r="I25" s="140">
+      <c r="I25" s="141">
         <f>SUMPRODUCT(($C$12:$C$24="O")*I12:I24)</f>
         <v/>
       </c>
-      <c r="J25" s="140">
+      <c r="J25" s="141">
         <f>SUMPRODUCT(($C$12:$C$24="O")*J12:J24)</f>
         <v/>
       </c>
-      <c r="K25" s="140">
+      <c r="K25" s="141">
         <f>SUMPRODUCT(($C$12:$C$24="O")*K12:K24)</f>
         <v/>
       </c>
-      <c r="L25" s="140">
+      <c r="L25" s="141">
         <f>SUMPRODUCT(($C$12:$C$24="O")*L12:L24)</f>
         <v/>
       </c>
-      <c r="M25" s="140">
+      <c r="M25" s="141">
         <f>SUMPRODUCT(($C$12:$C$24="O")*M12:M24)</f>
         <v/>
       </c>
-      <c r="N25" s="140">
+      <c r="N25" s="141">
         <f>SUMPRODUCT(($C$12:$C$24="O")*N12:N24)</f>
         <v/>
       </c>
-      <c r="O25" s="140">
+      <c r="O25" s="141">
         <f>SUMPRODUCT(($C$12:$C$24="O")*O12:O24)</f>
         <v/>
       </c>
@@ -86499,11 +88838,16 @@
           <t>▼ 공종별 작업량 입력 (주공정=Y인 공종만 공사기간에 합산, 위에서 아래 순서로 이어서 시공)</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>※ 예시 값입니다. 덮어써서 사용하세요.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="134" t="inlineStr">
         <is>
-          <t>공종</t>
+          <t>공종 (목록 선택 또는 직접 입력)</t>
         </is>
       </c>
       <c r="B28" s="134" t="inlineStr">
@@ -86518,7 +88862,7 @@
       </c>
       <c r="D28" s="134" t="inlineStr">
         <is>
-          <t>1일 작업량</t>
+          <t>1일 작업량 (수정 가능)</t>
         </is>
       </c>
       <c r="E28" s="134" t="inlineStr">
@@ -86553,486 +88897,546 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="137" t="inlineStr">
-        <is>
-          <t>철골세우기</t>
-        </is>
-      </c>
-      <c r="B29" s="137" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C29" s="137" t="inlineStr">
-        <is>
-          <t>톤</t>
-        </is>
-      </c>
-      <c r="D29" s="137" t="n">
-        <v>50</v>
-      </c>
-      <c r="E29" s="137" t="inlineStr">
+      <c r="A29" s="138" t="inlineStr">
+        <is>
+          <t>공통가설공사&gt;가설울타리 (H형강지주 4m 이하)</t>
+        </is>
+      </c>
+      <c r="B29" s="138" t="n">
+        <v>300</v>
+      </c>
+      <c r="C29" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$B$2:$B$115,MATCH($A29,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$C$2:$C$115,MATCH($A29,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="138" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F29" s="139">
-        <f>IF(AND(ISNUMBER(B29),ISNUMBER(D29),N(D29)&gt;0),ROUNDUP(B29/D29,0),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="139">
+      <c r="F29" s="140">
+        <f>IF(AND(ISNUMBER(B29),ISNUMBER(D29),N(D29)&gt;0),ROUNDUP(ROUND(B29/D29,6),0),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="140">
         <f>IF(F29="","",N(G28)+IF(E29="Y",F29,0))</f>
         <v/>
       </c>
-      <c r="H29" s="139">
+      <c r="H29" s="140">
         <f>IF(G29="","",IF(G29=0,0,IF(G29&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G29,$K$58:$K$117,1))+(G29-INDEX($K$58:$K$117,MATCH(G29,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G29,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G29,$K$58:$K$117,1)))))</f>
         <v/>
       </c>
-      <c r="I29" s="139">
+      <c r="I29" s="140">
         <f>IF(F29="","",IF(E29="Y",IF(ISNUMBER(H29),ROUND(H29-N(H28),1),"기간초과"),"-"))</f>
         <v/>
       </c>
-      <c r="J29" s="139">
+      <c r="J29" s="140">
         <f>IF(ISNUMBER(I29),ROUND(I29-F29,1),"")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="137" t="inlineStr">
-        <is>
-          <t>데크플레이트 설치</t>
-        </is>
-      </c>
-      <c r="B30" s="137" t="n">
-        <v>33800</v>
-      </c>
-      <c r="C30" s="137" t="inlineStr">
-        <is>
-          <t>㎡</t>
-        </is>
-      </c>
-      <c r="D30" s="137" t="n">
-        <v>440</v>
-      </c>
-      <c r="E30" s="137" t="inlineStr">
+      <c r="A30" s="138" t="inlineStr">
+        <is>
+          <t>토공사&gt;흙쌓기-노체 (모터그레이더 3.6㎥)</t>
+        </is>
+      </c>
+      <c r="B30" s="138" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C30" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$B$2:$B$115,MATCH($A30,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$C$2:$C$115,MATCH($A30,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="138" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F30" s="139">
-        <f>IF(AND(ISNUMBER(B30),ISNUMBER(D30),N(D30)&gt;0),ROUNDUP(B30/D30,0),"")</f>
-        <v/>
-      </c>
-      <c r="G30" s="139">
+      <c r="F30" s="140">
+        <f>IF(AND(ISNUMBER(B30),ISNUMBER(D30),N(D30)&gt;0),ROUNDUP(ROUND(B30/D30,6),0),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="140">
         <f>IF(F30="","",N(G29)+IF(E30="Y",F30,0))</f>
         <v/>
       </c>
-      <c r="H30" s="139">
+      <c r="H30" s="140">
         <f>IF(G30="","",IF(G30=0,0,IF(G30&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G30,$K$58:$K$117,1))+(G30-INDEX($K$58:$K$117,MATCH(G30,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G30,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G30,$K$58:$K$117,1)))))</f>
         <v/>
       </c>
-      <c r="I30" s="139">
+      <c r="I30" s="140">
         <f>IF(F30="","",IF(E30="Y",IF(ISNUMBER(H30),ROUND(H30-N(H29),1),"기간초과"),"-"))</f>
         <v/>
       </c>
-      <c r="J30" s="139">
+      <c r="J30" s="140">
         <f>IF(ISNUMBER(I30),ROUND(I30-F30,1),"")</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="137" t="inlineStr">
-        <is>
-          <t>철근 가공/조립</t>
-        </is>
-      </c>
-      <c r="B31" s="137" t="n">
-        <v>940</v>
-      </c>
-      <c r="C31" s="137" t="inlineStr">
-        <is>
-          <t>톤</t>
-        </is>
-      </c>
-      <c r="D31" s="137" t="n">
-        <v>12</v>
-      </c>
-      <c r="E31" s="137" t="inlineStr">
+      <c r="A31" s="138" t="inlineStr">
+        <is>
+          <t>포장공사&gt;아스팔트포장 1단계-보조기층 (대형 다짐장비, 본선 포설)</t>
+        </is>
+      </c>
+      <c r="B31" s="138" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C31" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$B$2:$B$115,MATCH($A31,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$C$2:$C$115,MATCH($A31,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="138" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F31" s="139">
-        <f>IF(AND(ISNUMBER(B31),ISNUMBER(D31),N(D31)&gt;0),ROUNDUP(B31/D31,0),"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="139">
+      <c r="F31" s="140">
+        <f>IF(AND(ISNUMBER(B31),ISNUMBER(D31),N(D31)&gt;0),ROUNDUP(ROUND(B31/D31,6),0),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="140">
         <f>IF(F31="","",N(G30)+IF(E31="Y",F31,0))</f>
         <v/>
       </c>
-      <c r="H31" s="139">
+      <c r="H31" s="140">
         <f>IF(G31="","",IF(G31=0,0,IF(G31&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G31,$K$58:$K$117,1))+(G31-INDEX($K$58:$K$117,MATCH(G31,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G31,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G31,$K$58:$K$117,1)))))</f>
         <v/>
       </c>
-      <c r="I31" s="139">
+      <c r="I31" s="140">
         <f>IF(F31="","",IF(E31="Y",IF(ISNUMBER(H31),ROUND(H31-N(H30),1),"기간초과"),"-"))</f>
         <v/>
       </c>
-      <c r="J31" s="139">
+      <c r="J31" s="140">
         <f>IF(ISNUMBER(I31),ROUND(I31-F31,1),"")</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="137" t="inlineStr">
-        <is>
-          <t>형틀 조립</t>
-        </is>
-      </c>
-      <c r="B32" s="137" t="n">
-        <v>24500</v>
-      </c>
-      <c r="C32" s="137" t="inlineStr">
-        <is>
-          <t>㎡</t>
-        </is>
-      </c>
-      <c r="D32" s="137" t="n">
-        <v>320</v>
-      </c>
-      <c r="E32" s="137" t="inlineStr">
+      <c r="A32" s="138" t="inlineStr">
+        <is>
+          <t>포장공사&gt;아스팔트포장 2단계-기층 (시공폭 3m 이상, 두께 5~7㎝)</t>
+        </is>
+      </c>
+      <c r="B32" s="138" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C32" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$B$2:$B$115,MATCH($A32,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$C$2:$C$115,MATCH($A32,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="138" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F32" s="139">
-        <f>IF(AND(ISNUMBER(B32),ISNUMBER(D32),N(D32)&gt;0),ROUNDUP(B32/D32,0),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="139">
+      <c r="F32" s="140">
+        <f>IF(AND(ISNUMBER(B32),ISNUMBER(D32),N(D32)&gt;0),ROUNDUP(ROUND(B32/D32,6),0),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="140">
         <f>IF(F32="","",N(G31)+IF(E32="Y",F32,0))</f>
         <v/>
       </c>
-      <c r="H32" s="139">
+      <c r="H32" s="140">
         <f>IF(G32="","",IF(G32=0,0,IF(G32&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G32,$K$58:$K$117,1))+(G32-INDEX($K$58:$K$117,MATCH(G32,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G32,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G32,$K$58:$K$117,1)))))</f>
         <v/>
       </c>
-      <c r="I32" s="139">
+      <c r="I32" s="140">
         <f>IF(F32="","",IF(E32="Y",IF(ISNUMBER(H32),ROUND(H32-N(H31),1),"기간초과"),"-"))</f>
         <v/>
       </c>
-      <c r="J32" s="139">
+      <c r="J32" s="140">
         <f>IF(ISNUMBER(I32),ROUND(I32-F32,1),"")</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="137" t="inlineStr">
-        <is>
-          <t>콘크리트 타설</t>
-        </is>
-      </c>
-      <c r="B33" s="137" t="n">
-        <v>10300</v>
-      </c>
-      <c r="C33" s="137" t="inlineStr">
-        <is>
-          <t>㎥</t>
-        </is>
-      </c>
-      <c r="D33" s="137" t="n">
-        <v>930</v>
-      </c>
-      <c r="E33" s="137" t="inlineStr">
+      <c r="A33" s="138" t="inlineStr">
+        <is>
+          <t>포장공사&gt;아스팔트포장 2단계-중간층/표층 (시공폭 3m 이상, 5~7㎝)</t>
+        </is>
+      </c>
+      <c r="B33" s="138" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C33" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$B$2:$B$115,MATCH($A33,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$C$2:$C$115,MATCH($A33,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="138" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F33" s="139">
-        <f>IF(AND(ISNUMBER(B33),ISNUMBER(D33),N(D33)&gt;0),ROUNDUP(B33/D33,0),"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="139">
+      <c r="F33" s="140">
+        <f>IF(AND(ISNUMBER(B33),ISNUMBER(D33),N(D33)&gt;0),ROUNDUP(ROUND(B33/D33,6),0),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="140">
         <f>IF(F33="","",N(G32)+IF(E33="Y",F33,0))</f>
         <v/>
       </c>
-      <c r="H33" s="139">
+      <c r="H33" s="140">
         <f>IF(G33="","",IF(G33=0,0,IF(G33&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G33,$K$58:$K$117,1))+(G33-INDEX($K$58:$K$117,MATCH(G33,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G33,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G33,$K$58:$K$117,1)))))</f>
         <v/>
       </c>
-      <c r="I33" s="139">
+      <c r="I33" s="140">
         <f>IF(F33="","",IF(E33="Y",IF(ISNUMBER(H33),ROUND(H33-N(H32),1),"기간초과"),"-"))</f>
         <v/>
       </c>
-      <c r="J33" s="139">
+      <c r="J33" s="140">
         <f>IF(ISNUMBER(I33),ROUND(I33-F33,1),"")</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="137" t="n"/>
-      <c r="B34" s="137" t="n"/>
-      <c r="C34" s="137" t="n"/>
-      <c r="D34" s="137" t="n"/>
-      <c r="E34" s="137" t="n"/>
-      <c r="F34" s="139">
-        <f>IF(AND(ISNUMBER(B34),ISNUMBER(D34),N(D34)&gt;0),ROUNDUP(B34/D34,0),"")</f>
-        <v/>
-      </c>
-      <c r="G34" s="139">
+      <c r="A34" s="138" t="n"/>
+      <c r="B34" s="138" t="n"/>
+      <c r="C34" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$B$2:$B$115,MATCH($A34,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$C$2:$C$115,MATCH($A34,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="138" t="n"/>
+      <c r="F34" s="140">
+        <f>IF(AND(ISNUMBER(B34),ISNUMBER(D34),N(D34)&gt;0),ROUNDUP(ROUND(B34/D34,6),0),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="140">
         <f>IF(F34="","",N(G33)+IF(E34="Y",F34,0))</f>
         <v/>
       </c>
-      <c r="H34" s="139">
+      <c r="H34" s="140">
         <f>IF(G34="","",IF(G34=0,0,IF(G34&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G34,$K$58:$K$117,1))+(G34-INDEX($K$58:$K$117,MATCH(G34,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G34,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G34,$K$58:$K$117,1)))))</f>
         <v/>
       </c>
-      <c r="I34" s="139">
+      <c r="I34" s="140">
         <f>IF(F34="","",IF(E34="Y",IF(ISNUMBER(H34),ROUND(H34-N(H33),1),"기간초과"),"-"))</f>
         <v/>
       </c>
-      <c r="J34" s="139">
+      <c r="J34" s="140">
         <f>IF(ISNUMBER(I34),ROUND(I34-F34,1),"")</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="137" t="n"/>
-      <c r="B35" s="137" t="n"/>
-      <c r="C35" s="137" t="n"/>
-      <c r="D35" s="137" t="n"/>
-      <c r="E35" s="137" t="n"/>
-      <c r="F35" s="139">
-        <f>IF(AND(ISNUMBER(B35),ISNUMBER(D35),N(D35)&gt;0),ROUNDUP(B35/D35,0),"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="139">
+      <c r="A35" s="138" t="n"/>
+      <c r="B35" s="138" t="n"/>
+      <c r="C35" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$B$2:$B$115,MATCH($A35,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$C$2:$C$115,MATCH($A35,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="138" t="n"/>
+      <c r="F35" s="140">
+        <f>IF(AND(ISNUMBER(B35),ISNUMBER(D35),N(D35)&gt;0),ROUNDUP(ROUND(B35/D35,6),0),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="140">
         <f>IF(F35="","",N(G34)+IF(E35="Y",F35,0))</f>
         <v/>
       </c>
-      <c r="H35" s="139">
+      <c r="H35" s="140">
         <f>IF(G35="","",IF(G35=0,0,IF(G35&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G35,$K$58:$K$117,1))+(G35-INDEX($K$58:$K$117,MATCH(G35,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G35,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G35,$K$58:$K$117,1)))))</f>
         <v/>
       </c>
-      <c r="I35" s="139">
+      <c r="I35" s="140">
         <f>IF(F35="","",IF(E35="Y",IF(ISNUMBER(H35),ROUND(H35-N(H34),1),"기간초과"),"-"))</f>
         <v/>
       </c>
-      <c r="J35" s="139">
+      <c r="J35" s="140">
         <f>IF(ISNUMBER(I35),ROUND(I35-F35,1),"")</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="137" t="n"/>
-      <c r="B36" s="137" t="n"/>
-      <c r="C36" s="137" t="n"/>
-      <c r="D36" s="137" t="n"/>
-      <c r="E36" s="137" t="n"/>
-      <c r="F36" s="139">
-        <f>IF(AND(ISNUMBER(B36),ISNUMBER(D36),N(D36)&gt;0),ROUNDUP(B36/D36,0),"")</f>
-        <v/>
-      </c>
-      <c r="G36" s="139">
+      <c r="A36" s="138" t="n"/>
+      <c r="B36" s="138" t="n"/>
+      <c r="C36" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$B$2:$B$115,MATCH($A36,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$C$2:$C$115,MATCH($A36,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="138" t="n"/>
+      <c r="F36" s="140">
+        <f>IF(AND(ISNUMBER(B36),ISNUMBER(D36),N(D36)&gt;0),ROUNDUP(ROUND(B36/D36,6),0),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="140">
         <f>IF(F36="","",N(G35)+IF(E36="Y",F36,0))</f>
         <v/>
       </c>
-      <c r="H36" s="139">
+      <c r="H36" s="140">
         <f>IF(G36="","",IF(G36=0,0,IF(G36&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G36,$K$58:$K$117,1))+(G36-INDEX($K$58:$K$117,MATCH(G36,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G36,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G36,$K$58:$K$117,1)))))</f>
         <v/>
       </c>
-      <c r="I36" s="139">
+      <c r="I36" s="140">
         <f>IF(F36="","",IF(E36="Y",IF(ISNUMBER(H36),ROUND(H36-N(H35),1),"기간초과"),"-"))</f>
         <v/>
       </c>
-      <c r="J36" s="139">
+      <c r="J36" s="140">
         <f>IF(ISNUMBER(I36),ROUND(I36-F36,1),"")</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="137" t="n"/>
-      <c r="B37" s="137" t="n"/>
-      <c r="C37" s="137" t="n"/>
-      <c r="D37" s="137" t="n"/>
-      <c r="E37" s="137" t="n"/>
-      <c r="F37" s="139">
-        <f>IF(AND(ISNUMBER(B37),ISNUMBER(D37),N(D37)&gt;0),ROUNDUP(B37/D37,0),"")</f>
-        <v/>
-      </c>
-      <c r="G37" s="139">
+      <c r="A37" s="138" t="n"/>
+      <c r="B37" s="138" t="n"/>
+      <c r="C37" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$B$2:$B$115,MATCH($A37,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$C$2:$C$115,MATCH($A37,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="138" t="n"/>
+      <c r="F37" s="140">
+        <f>IF(AND(ISNUMBER(B37),ISNUMBER(D37),N(D37)&gt;0),ROUNDUP(ROUND(B37/D37,6),0),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="140">
         <f>IF(F37="","",N(G36)+IF(E37="Y",F37,0))</f>
         <v/>
       </c>
-      <c r="H37" s="139">
+      <c r="H37" s="140">
         <f>IF(G37="","",IF(G37=0,0,IF(G37&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G37,$K$58:$K$117,1))+(G37-INDEX($K$58:$K$117,MATCH(G37,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G37,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G37,$K$58:$K$117,1)))))</f>
         <v/>
       </c>
-      <c r="I37" s="139">
+      <c r="I37" s="140">
         <f>IF(F37="","",IF(E37="Y",IF(ISNUMBER(H37),ROUND(H37-N(H36),1),"기간초과"),"-"))</f>
         <v/>
       </c>
-      <c r="J37" s="139">
+      <c r="J37" s="140">
         <f>IF(ISNUMBER(I37),ROUND(I37-F37,1),"")</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="137" t="n"/>
-      <c r="B38" s="137" t="n"/>
-      <c r="C38" s="137" t="n"/>
-      <c r="D38" s="137" t="n"/>
-      <c r="E38" s="137" t="n"/>
-      <c r="F38" s="139">
-        <f>IF(AND(ISNUMBER(B38),ISNUMBER(D38),N(D38)&gt;0),ROUNDUP(B38/D38,0),"")</f>
-        <v/>
-      </c>
-      <c r="G38" s="139">
+      <c r="A38" s="138" t="n"/>
+      <c r="B38" s="138" t="n"/>
+      <c r="C38" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$B$2:$B$115,MATCH($A38,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$C$2:$C$115,MATCH($A38,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="138" t="n"/>
+      <c r="F38" s="140">
+        <f>IF(AND(ISNUMBER(B38),ISNUMBER(D38),N(D38)&gt;0),ROUNDUP(ROUND(B38/D38,6),0),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="140">
         <f>IF(F38="","",N(G37)+IF(E38="Y",F38,0))</f>
         <v/>
       </c>
-      <c r="H38" s="139">
+      <c r="H38" s="140">
         <f>IF(G38="","",IF(G38=0,0,IF(G38&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G38,$K$58:$K$117,1))+(G38-INDEX($K$58:$K$117,MATCH(G38,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G38,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G38,$K$58:$K$117,1)))))</f>
         <v/>
       </c>
-      <c r="I38" s="139">
+      <c r="I38" s="140">
         <f>IF(F38="","",IF(E38="Y",IF(ISNUMBER(H38),ROUND(H38-N(H37),1),"기간초과"),"-"))</f>
         <v/>
       </c>
-      <c r="J38" s="139">
+      <c r="J38" s="140">
         <f>IF(ISNUMBER(I38),ROUND(I38-F38,1),"")</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="137" t="n"/>
-      <c r="B39" s="137" t="n"/>
-      <c r="C39" s="137" t="n"/>
-      <c r="D39" s="137" t="n"/>
-      <c r="E39" s="137" t="n"/>
-      <c r="F39" s="139">
-        <f>IF(AND(ISNUMBER(B39),ISNUMBER(D39),N(D39)&gt;0),ROUNDUP(B39/D39,0),"")</f>
-        <v/>
-      </c>
-      <c r="G39" s="139">
+      <c r="A39" s="138" t="n"/>
+      <c r="B39" s="138" t="n"/>
+      <c r="C39" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$B$2:$B$115,MATCH($A39,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$C$2:$C$115,MATCH($A39,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="138" t="n"/>
+      <c r="F39" s="140">
+        <f>IF(AND(ISNUMBER(B39),ISNUMBER(D39),N(D39)&gt;0),ROUNDUP(ROUND(B39/D39,6),0),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="140">
         <f>IF(F39="","",N(G38)+IF(E39="Y",F39,0))</f>
         <v/>
       </c>
-      <c r="H39" s="139">
+      <c r="H39" s="140">
         <f>IF(G39="","",IF(G39=0,0,IF(G39&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G39,$K$58:$K$117,1))+(G39-INDEX($K$58:$K$117,MATCH(G39,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G39,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G39,$K$58:$K$117,1)))))</f>
         <v/>
       </c>
-      <c r="I39" s="139">
+      <c r="I39" s="140">
         <f>IF(F39="","",IF(E39="Y",IF(ISNUMBER(H39),ROUND(H39-N(H38),1),"기간초과"),"-"))</f>
         <v/>
       </c>
-      <c r="J39" s="139">
+      <c r="J39" s="140">
         <f>IF(ISNUMBER(I39),ROUND(I39-F39,1),"")</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="137" t="n"/>
-      <c r="B40" s="137" t="n"/>
-      <c r="C40" s="137" t="n"/>
-      <c r="D40" s="137" t="n"/>
-      <c r="E40" s="137" t="n"/>
-      <c r="F40" s="139">
-        <f>IF(AND(ISNUMBER(B40),ISNUMBER(D40),N(D40)&gt;0),ROUNDUP(B40/D40,0),"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="139">
+      <c r="A40" s="138" t="n"/>
+      <c r="B40" s="138" t="n"/>
+      <c r="C40" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$B$2:$B$115,MATCH($A40,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D40" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$C$2:$C$115,MATCH($A40,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="138" t="n"/>
+      <c r="F40" s="140">
+        <f>IF(AND(ISNUMBER(B40),ISNUMBER(D40),N(D40)&gt;0),ROUNDUP(ROUND(B40/D40,6),0),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="140">
         <f>IF(F40="","",N(G39)+IF(E40="Y",F40,0))</f>
         <v/>
       </c>
-      <c r="H40" s="139">
+      <c r="H40" s="140">
         <f>IF(G40="","",IF(G40=0,0,IF(G40&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G40,$K$58:$K$117,1))+(G40-INDEX($K$58:$K$117,MATCH(G40,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G40,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G40,$K$58:$K$117,1)))))</f>
         <v/>
       </c>
-      <c r="I40" s="139">
+      <c r="I40" s="140">
         <f>IF(F40="","",IF(E40="Y",IF(ISNUMBER(H40),ROUND(H40-N(H39),1),"기간초과"),"-"))</f>
         <v/>
       </c>
-      <c r="J40" s="139">
+      <c r="J40" s="140">
         <f>IF(ISNUMBER(I40),ROUND(I40-F40,1),"")</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="137" t="n"/>
-      <c r="B41" s="137" t="n"/>
-      <c r="C41" s="137" t="n"/>
-      <c r="D41" s="137" t="n"/>
-      <c r="E41" s="137" t="n"/>
-      <c r="F41" s="139">
-        <f>IF(AND(ISNUMBER(B41),ISNUMBER(D41),N(D41)&gt;0),ROUNDUP(B41/D41,0),"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="139">
+      <c r="A41" s="138" t="n"/>
+      <c r="B41" s="138" t="n"/>
+      <c r="C41" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$B$2:$B$115,MATCH($A41,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$C$2:$C$115,MATCH($A41,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="138" t="n"/>
+      <c r="F41" s="140">
+        <f>IF(AND(ISNUMBER(B41),ISNUMBER(D41),N(D41)&gt;0),ROUNDUP(ROUND(B41/D41,6),0),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="140">
         <f>IF(F41="","",N(G40)+IF(E41="Y",F41,0))</f>
         <v/>
       </c>
-      <c r="H41" s="139">
+      <c r="H41" s="140">
         <f>IF(G41="","",IF(G41=0,0,IF(G41&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G41,$K$58:$K$117,1))+(G41-INDEX($K$58:$K$117,MATCH(G41,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G41,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G41,$K$58:$K$117,1)))))</f>
         <v/>
       </c>
-      <c r="I41" s="139">
+      <c r="I41" s="140">
         <f>IF(F41="","",IF(E41="Y",IF(ISNUMBER(H41),ROUND(H41-N(H40),1),"기간초과"),"-"))</f>
         <v/>
       </c>
-      <c r="J41" s="139">
+      <c r="J41" s="140">
         <f>IF(ISNUMBER(I41),ROUND(I41-F41,1),"")</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="137" t="n"/>
-      <c r="B42" s="137" t="n"/>
-      <c r="C42" s="137" t="n"/>
-      <c r="D42" s="137" t="n"/>
-      <c r="E42" s="137" t="n"/>
-      <c r="F42" s="139">
-        <f>IF(AND(ISNUMBER(B42),ISNUMBER(D42),N(D42)&gt;0),ROUNDUP(B42/D42,0),"")</f>
-        <v/>
-      </c>
-      <c r="G42" s="139">
+      <c r="A42" s="138" t="n"/>
+      <c r="B42" s="138" t="n"/>
+      <c r="C42" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$B$2:$B$115,MATCH($A42,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D42" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$C$2:$C$115,MATCH($A42,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="138" t="n"/>
+      <c r="F42" s="140">
+        <f>IF(AND(ISNUMBER(B42),ISNUMBER(D42),N(D42)&gt;0),ROUNDUP(ROUND(B42/D42,6),0),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="140">
         <f>IF(F42="","",N(G41)+IF(E42="Y",F42,0))</f>
         <v/>
       </c>
-      <c r="H42" s="139">
+      <c r="H42" s="140">
         <f>IF(G42="","",IF(G42=0,0,IF(G42&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G42,$K$58:$K$117,1))+(G42-INDEX($K$58:$K$117,MATCH(G42,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G42,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G42,$K$58:$K$117,1)))))</f>
         <v/>
       </c>
-      <c r="I42" s="139">
+      <c r="I42" s="140">
         <f>IF(F42="","",IF(E42="Y",IF(ISNUMBER(H42),ROUND(H42-N(H41),1),"기간초과"),"-"))</f>
         <v/>
       </c>
-      <c r="J42" s="139">
+      <c r="J42" s="140">
         <f>IF(ISNUMBER(I42),ROUND(I42-F42,1),"")</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="137" t="n"/>
-      <c r="B43" s="137" t="n"/>
-      <c r="C43" s="137" t="n"/>
-      <c r="D43" s="137" t="n"/>
-      <c r="E43" s="137" t="n"/>
-      <c r="F43" s="139">
-        <f>IF(AND(ISNUMBER(B43),ISNUMBER(D43),N(D43)&gt;0),ROUNDUP(B43/D43,0),"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="139">
+      <c r="A43" s="138" t="n"/>
+      <c r="B43" s="138" t="n"/>
+      <c r="C43" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$B$2:$B$115,MATCH($A43,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="138">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$C$2:$C$115,MATCH($A43,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="138" t="n"/>
+      <c r="F43" s="140">
+        <f>IF(AND(ISNUMBER(B43),ISNUMBER(D43),N(D43)&gt;0),ROUNDUP(ROUND(B43/D43,6),0),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="140">
         <f>IF(F43="","",N(G42)+IF(E43="Y",F43,0))</f>
         <v/>
       </c>
-      <c r="H43" s="139">
+      <c r="H43" s="140">
         <f>IF(G43="","",IF(G43=0,0,IF(G43&gt;INDEX($K$58:$K$117,60)+INDEX($J$58:$J$117,60),"기간초과",INDEX($L$58:$L$117,MATCH(G43,$K$58:$K$117,1))+(G43-INDEX($K$58:$K$117,MATCH(G43,$K$58:$K$117,1)))*INDEX($D$58:$D$117,MATCH(G43,$K$58:$K$117,1))/INDEX($J$58:$J$117,MATCH(G43,$K$58:$K$117,1)))))</f>
         <v/>
       </c>
-      <c r="I43" s="139">
+      <c r="I43" s="140">
         <f>IF(F43="","",IF(E43="Y",IF(ISNUMBER(H43),ROUND(H43-N(H42),1),"기간초과"),"-"))</f>
         <v/>
       </c>
-      <c r="J43" s="139">
+      <c r="J43" s="140">
         <f>IF(ISNUMBER(I43),ROUND(I43-F43,1),"")</f>
         <v/>
       </c>
@@ -87050,7 +89454,7 @@
           <t>준비기간 (일)</t>
         </is>
       </c>
-      <c r="B46" s="138">
+      <c r="B46" s="139">
         <f>B7</f>
         <v/>
       </c>
@@ -87061,7 +89465,7 @@
           <t>주공정 공종별 공사기간의 합 (일)</t>
         </is>
       </c>
-      <c r="B47" s="138">
+      <c r="B47" s="139">
         <f>IFERROR(ROUNDUP(MAX(H29:H43),0),"기간초과")</f>
         <v/>
       </c>
@@ -87072,7 +89476,7 @@
           <t>정리기간 (일)</t>
         </is>
       </c>
-      <c r="B48" s="138">
+      <c r="B48" s="139">
         <f>B8</f>
         <v/>
       </c>
@@ -87083,7 +89487,7 @@
           <t>공사기간 A (일)</t>
         </is>
       </c>
-      <c r="B49" s="138">
+      <c r="B49" s="139">
         <f>IF(ISNUMBER(B47),B46+B47+B48,"-")</f>
         <v/>
       </c>
@@ -87094,7 +89498,7 @@
           <t>환산 (개월)</t>
         </is>
       </c>
-      <c r="B50" s="138">
+      <c r="B50" s="139">
         <f>IF(ISNUMBER(B49),ROUND(B49/30,1),"-")</f>
         <v/>
       </c>
@@ -87105,7 +89509,7 @@
           <t>산정공식 공사기간 B (일) — 시설물별공기(토목)</t>
         </is>
       </c>
-      <c r="B51" s="138">
+      <c r="B51" s="139">
         <f>'시설물별공기(토목)'!B19</f>
         <v/>
       </c>
@@ -87116,7 +89520,7 @@
           <t>적정성 검토 (A가 B의 ±20% 이내인지)</t>
         </is>
       </c>
-      <c r="B52" s="138">
+      <c r="B52" s="139">
         <f>IF(AND(ISNUMBER(B49),ISNUMBER(B51)),IF(ABS(B49/B51-1)&lt;=0.2,"±20% 이내 (적정)","±20% 초과 → 산정 과정 재검토 (편차 "&amp;TEXT(B49/B51-1,"0.0%")&amp;")"),"산정공식 적용범위 밖이거나 미입력 → 비교 생략")</f>
         <v/>
       </c>
@@ -87191,2939 +89595,2939 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="139" t="n">
+      <c r="A58" s="140" t="n">
         <v>1</v>
       </c>
-      <c r="B58" s="139">
+      <c r="B58" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A58-1))</f>
         <v/>
       </c>
-      <c r="C58" s="139">
+      <c r="C58" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A58-1))</f>
         <v/>
       </c>
-      <c r="D58" s="139">
+      <c r="D58" s="140">
         <f>DAY(EOMONTH(DATE(B58,C58,1),0))</f>
         <v/>
       </c>
-      <c r="E58" s="139">
+      <c r="E58" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B58,법정공휴일!$A$4:$A$20,0),C58),0)</f>
         <v/>
       </c>
-      <c r="F58" s="139">
+      <c r="F58" s="140">
         <f>INDEX($D$25:$O$25,C58)</f>
         <v/>
       </c>
-      <c r="G58" s="139">
+      <c r="G58" s="140">
         <f>ROUND(F58*E58/D58,1)</f>
         <v/>
       </c>
-      <c r="H58" s="139">
+      <c r="H58" s="140">
         <f>F58+E58-G58</f>
         <v/>
       </c>
-      <c r="I58" s="139">
+      <c r="I58" s="140">
         <f>ROUND(MAX(H58,8),0)</f>
         <v/>
       </c>
-      <c r="J58" s="139">
+      <c r="J58" s="140">
         <f>D58-I58</f>
         <v/>
       </c>
-      <c r="K58" s="139" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="139" t="n">
+      <c r="K58" s="140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="140" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="139" t="n">
+      <c r="A59" s="140" t="n">
         <v>2</v>
       </c>
-      <c r="B59" s="139">
+      <c r="B59" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A59-1))</f>
         <v/>
       </c>
-      <c r="C59" s="139">
+      <c r="C59" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A59-1))</f>
         <v/>
       </c>
-      <c r="D59" s="139">
+      <c r="D59" s="140">
         <f>DAY(EOMONTH(DATE(B59,C59,1),0))</f>
         <v/>
       </c>
-      <c r="E59" s="139">
+      <c r="E59" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B59,법정공휴일!$A$4:$A$20,0),C59),0)</f>
         <v/>
       </c>
-      <c r="F59" s="139">
+      <c r="F59" s="140">
         <f>INDEX($D$25:$O$25,C59)</f>
         <v/>
       </c>
-      <c r="G59" s="139">
+      <c r="G59" s="140">
         <f>ROUND(F59*E59/D59,1)</f>
         <v/>
       </c>
-      <c r="H59" s="139">
+      <c r="H59" s="140">
         <f>F59+E59-G59</f>
         <v/>
       </c>
-      <c r="I59" s="139">
+      <c r="I59" s="140">
         <f>ROUND(MAX(H59,8),0)</f>
         <v/>
       </c>
-      <c r="J59" s="139">
+      <c r="J59" s="140">
         <f>D59-I59</f>
         <v/>
       </c>
-      <c r="K59" s="139">
+      <c r="K59" s="140">
         <f>K58+J58</f>
         <v/>
       </c>
-      <c r="L59" s="139">
+      <c r="L59" s="140">
         <f>L58+D58</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="139" t="n">
+      <c r="A60" s="140" t="n">
         <v>3</v>
       </c>
-      <c r="B60" s="139">
+      <c r="B60" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A60-1))</f>
         <v/>
       </c>
-      <c r="C60" s="139">
+      <c r="C60" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A60-1))</f>
         <v/>
       </c>
-      <c r="D60" s="139">
+      <c r="D60" s="140">
         <f>DAY(EOMONTH(DATE(B60,C60,1),0))</f>
         <v/>
       </c>
-      <c r="E60" s="139">
+      <c r="E60" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B60,법정공휴일!$A$4:$A$20,0),C60),0)</f>
         <v/>
       </c>
-      <c r="F60" s="139">
+      <c r="F60" s="140">
         <f>INDEX($D$25:$O$25,C60)</f>
         <v/>
       </c>
-      <c r="G60" s="139">
+      <c r="G60" s="140">
         <f>ROUND(F60*E60/D60,1)</f>
         <v/>
       </c>
-      <c r="H60" s="139">
+      <c r="H60" s="140">
         <f>F60+E60-G60</f>
         <v/>
       </c>
-      <c r="I60" s="139">
+      <c r="I60" s="140">
         <f>ROUND(MAX(H60,8),0)</f>
         <v/>
       </c>
-      <c r="J60" s="139">
+      <c r="J60" s="140">
         <f>D60-I60</f>
         <v/>
       </c>
-      <c r="K60" s="139">
+      <c r="K60" s="140">
         <f>K59+J59</f>
         <v/>
       </c>
-      <c r="L60" s="139">
+      <c r="L60" s="140">
         <f>L59+D59</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="139" t="n">
+      <c r="A61" s="140" t="n">
         <v>4</v>
       </c>
-      <c r="B61" s="139">
+      <c r="B61" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A61-1))</f>
         <v/>
       </c>
-      <c r="C61" s="139">
+      <c r="C61" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A61-1))</f>
         <v/>
       </c>
-      <c r="D61" s="139">
+      <c r="D61" s="140">
         <f>DAY(EOMONTH(DATE(B61,C61,1),0))</f>
         <v/>
       </c>
-      <c r="E61" s="139">
+      <c r="E61" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B61,법정공휴일!$A$4:$A$20,0),C61),0)</f>
         <v/>
       </c>
-      <c r="F61" s="139">
+      <c r="F61" s="140">
         <f>INDEX($D$25:$O$25,C61)</f>
         <v/>
       </c>
-      <c r="G61" s="139">
+      <c r="G61" s="140">
         <f>ROUND(F61*E61/D61,1)</f>
         <v/>
       </c>
-      <c r="H61" s="139">
+      <c r="H61" s="140">
         <f>F61+E61-G61</f>
         <v/>
       </c>
-      <c r="I61" s="139">
+      <c r="I61" s="140">
         <f>ROUND(MAX(H61,8),0)</f>
         <v/>
       </c>
-      <c r="J61" s="139">
+      <c r="J61" s="140">
         <f>D61-I61</f>
         <v/>
       </c>
-      <c r="K61" s="139">
+      <c r="K61" s="140">
         <f>K60+J60</f>
         <v/>
       </c>
-      <c r="L61" s="139">
+      <c r="L61" s="140">
         <f>L60+D60</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="139" t="n">
+      <c r="A62" s="140" t="n">
         <v>5</v>
       </c>
-      <c r="B62" s="139">
+      <c r="B62" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A62-1))</f>
         <v/>
       </c>
-      <c r="C62" s="139">
+      <c r="C62" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A62-1))</f>
         <v/>
       </c>
-      <c r="D62" s="139">
+      <c r="D62" s="140">
         <f>DAY(EOMONTH(DATE(B62,C62,1),0))</f>
         <v/>
       </c>
-      <c r="E62" s="139">
+      <c r="E62" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B62,법정공휴일!$A$4:$A$20,0),C62),0)</f>
         <v/>
       </c>
-      <c r="F62" s="139">
+      <c r="F62" s="140">
         <f>INDEX($D$25:$O$25,C62)</f>
         <v/>
       </c>
-      <c r="G62" s="139">
+      <c r="G62" s="140">
         <f>ROUND(F62*E62/D62,1)</f>
         <v/>
       </c>
-      <c r="H62" s="139">
+      <c r="H62" s="140">
         <f>F62+E62-G62</f>
         <v/>
       </c>
-      <c r="I62" s="139">
+      <c r="I62" s="140">
         <f>ROUND(MAX(H62,8),0)</f>
         <v/>
       </c>
-      <c r="J62" s="139">
+      <c r="J62" s="140">
         <f>D62-I62</f>
         <v/>
       </c>
-      <c r="K62" s="139">
+      <c r="K62" s="140">
         <f>K61+J61</f>
         <v/>
       </c>
-      <c r="L62" s="139">
+      <c r="L62" s="140">
         <f>L61+D61</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="139" t="n">
+      <c r="A63" s="140" t="n">
         <v>6</v>
       </c>
-      <c r="B63" s="139">
+      <c r="B63" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A63-1))</f>
         <v/>
       </c>
-      <c r="C63" s="139">
+      <c r="C63" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A63-1))</f>
         <v/>
       </c>
-      <c r="D63" s="139">
+      <c r="D63" s="140">
         <f>DAY(EOMONTH(DATE(B63,C63,1),0))</f>
         <v/>
       </c>
-      <c r="E63" s="139">
+      <c r="E63" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B63,법정공휴일!$A$4:$A$20,0),C63),0)</f>
         <v/>
       </c>
-      <c r="F63" s="139">
+      <c r="F63" s="140">
         <f>INDEX($D$25:$O$25,C63)</f>
         <v/>
       </c>
-      <c r="G63" s="139">
+      <c r="G63" s="140">
         <f>ROUND(F63*E63/D63,1)</f>
         <v/>
       </c>
-      <c r="H63" s="139">
+      <c r="H63" s="140">
         <f>F63+E63-G63</f>
         <v/>
       </c>
-      <c r="I63" s="139">
+      <c r="I63" s="140">
         <f>ROUND(MAX(H63,8),0)</f>
         <v/>
       </c>
-      <c r="J63" s="139">
+      <c r="J63" s="140">
         <f>D63-I63</f>
         <v/>
       </c>
-      <c r="K63" s="139">
+      <c r="K63" s="140">
         <f>K62+J62</f>
         <v/>
       </c>
-      <c r="L63" s="139">
+      <c r="L63" s="140">
         <f>L62+D62</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="139" t="n">
+      <c r="A64" s="140" t="n">
         <v>7</v>
       </c>
-      <c r="B64" s="139">
+      <c r="B64" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A64-1))</f>
         <v/>
       </c>
-      <c r="C64" s="139">
+      <c r="C64" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A64-1))</f>
         <v/>
       </c>
-      <c r="D64" s="139">
+      <c r="D64" s="140">
         <f>DAY(EOMONTH(DATE(B64,C64,1),0))</f>
         <v/>
       </c>
-      <c r="E64" s="139">
+      <c r="E64" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B64,법정공휴일!$A$4:$A$20,0),C64),0)</f>
         <v/>
       </c>
-      <c r="F64" s="139">
+      <c r="F64" s="140">
         <f>INDEX($D$25:$O$25,C64)</f>
         <v/>
       </c>
-      <c r="G64" s="139">
+      <c r="G64" s="140">
         <f>ROUND(F64*E64/D64,1)</f>
         <v/>
       </c>
-      <c r="H64" s="139">
+      <c r="H64" s="140">
         <f>F64+E64-G64</f>
         <v/>
       </c>
-      <c r="I64" s="139">
+      <c r="I64" s="140">
         <f>ROUND(MAX(H64,8),0)</f>
         <v/>
       </c>
-      <c r="J64" s="139">
+      <c r="J64" s="140">
         <f>D64-I64</f>
         <v/>
       </c>
-      <c r="K64" s="139">
+      <c r="K64" s="140">
         <f>K63+J63</f>
         <v/>
       </c>
-      <c r="L64" s="139">
+      <c r="L64" s="140">
         <f>L63+D63</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="139" t="n">
+      <c r="A65" s="140" t="n">
         <v>8</v>
       </c>
-      <c r="B65" s="139">
+      <c r="B65" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A65-1))</f>
         <v/>
       </c>
-      <c r="C65" s="139">
+      <c r="C65" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A65-1))</f>
         <v/>
       </c>
-      <c r="D65" s="139">
+      <c r="D65" s="140">
         <f>DAY(EOMONTH(DATE(B65,C65,1),0))</f>
         <v/>
       </c>
-      <c r="E65" s="139">
+      <c r="E65" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B65,법정공휴일!$A$4:$A$20,0),C65),0)</f>
         <v/>
       </c>
-      <c r="F65" s="139">
+      <c r="F65" s="140">
         <f>INDEX($D$25:$O$25,C65)</f>
         <v/>
       </c>
-      <c r="G65" s="139">
+      <c r="G65" s="140">
         <f>ROUND(F65*E65/D65,1)</f>
         <v/>
       </c>
-      <c r="H65" s="139">
+      <c r="H65" s="140">
         <f>F65+E65-G65</f>
         <v/>
       </c>
-      <c r="I65" s="139">
+      <c r="I65" s="140">
         <f>ROUND(MAX(H65,8),0)</f>
         <v/>
       </c>
-      <c r="J65" s="139">
+      <c r="J65" s="140">
         <f>D65-I65</f>
         <v/>
       </c>
-      <c r="K65" s="139">
+      <c r="K65" s="140">
         <f>K64+J64</f>
         <v/>
       </c>
-      <c r="L65" s="139">
+      <c r="L65" s="140">
         <f>L64+D64</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="139" t="n">
+      <c r="A66" s="140" t="n">
         <v>9</v>
       </c>
-      <c r="B66" s="139">
+      <c r="B66" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A66-1))</f>
         <v/>
       </c>
-      <c r="C66" s="139">
+      <c r="C66" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A66-1))</f>
         <v/>
       </c>
-      <c r="D66" s="139">
+      <c r="D66" s="140">
         <f>DAY(EOMONTH(DATE(B66,C66,1),0))</f>
         <v/>
       </c>
-      <c r="E66" s="139">
+      <c r="E66" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B66,법정공휴일!$A$4:$A$20,0),C66),0)</f>
         <v/>
       </c>
-      <c r="F66" s="139">
+      <c r="F66" s="140">
         <f>INDEX($D$25:$O$25,C66)</f>
         <v/>
       </c>
-      <c r="G66" s="139">
+      <c r="G66" s="140">
         <f>ROUND(F66*E66/D66,1)</f>
         <v/>
       </c>
-      <c r="H66" s="139">
+      <c r="H66" s="140">
         <f>F66+E66-G66</f>
         <v/>
       </c>
-      <c r="I66" s="139">
+      <c r="I66" s="140">
         <f>ROUND(MAX(H66,8),0)</f>
         <v/>
       </c>
-      <c r="J66" s="139">
+      <c r="J66" s="140">
         <f>D66-I66</f>
         <v/>
       </c>
-      <c r="K66" s="139">
+      <c r="K66" s="140">
         <f>K65+J65</f>
         <v/>
       </c>
-      <c r="L66" s="139">
+      <c r="L66" s="140">
         <f>L65+D65</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="139" t="n">
+      <c r="A67" s="140" t="n">
         <v>10</v>
       </c>
-      <c r="B67" s="139">
+      <c r="B67" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A67-1))</f>
         <v/>
       </c>
-      <c r="C67" s="139">
+      <c r="C67" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A67-1))</f>
         <v/>
       </c>
-      <c r="D67" s="139">
+      <c r="D67" s="140">
         <f>DAY(EOMONTH(DATE(B67,C67,1),0))</f>
         <v/>
       </c>
-      <c r="E67" s="139">
+      <c r="E67" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B67,법정공휴일!$A$4:$A$20,0),C67),0)</f>
         <v/>
       </c>
-      <c r="F67" s="139">
+      <c r="F67" s="140">
         <f>INDEX($D$25:$O$25,C67)</f>
         <v/>
       </c>
-      <c r="G67" s="139">
+      <c r="G67" s="140">
         <f>ROUND(F67*E67/D67,1)</f>
         <v/>
       </c>
-      <c r="H67" s="139">
+      <c r="H67" s="140">
         <f>F67+E67-G67</f>
         <v/>
       </c>
-      <c r="I67" s="139">
+      <c r="I67" s="140">
         <f>ROUND(MAX(H67,8),0)</f>
         <v/>
       </c>
-      <c r="J67" s="139">
+      <c r="J67" s="140">
         <f>D67-I67</f>
         <v/>
       </c>
-      <c r="K67" s="139">
+      <c r="K67" s="140">
         <f>K66+J66</f>
         <v/>
       </c>
-      <c r="L67" s="139">
+      <c r="L67" s="140">
         <f>L66+D66</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="139" t="n">
+      <c r="A68" s="140" t="n">
         <v>11</v>
       </c>
-      <c r="B68" s="139">
+      <c r="B68" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A68-1))</f>
         <v/>
       </c>
-      <c r="C68" s="139">
+      <c r="C68" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A68-1))</f>
         <v/>
       </c>
-      <c r="D68" s="139">
+      <c r="D68" s="140">
         <f>DAY(EOMONTH(DATE(B68,C68,1),0))</f>
         <v/>
       </c>
-      <c r="E68" s="139">
+      <c r="E68" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B68,법정공휴일!$A$4:$A$20,0),C68),0)</f>
         <v/>
       </c>
-      <c r="F68" s="139">
+      <c r="F68" s="140">
         <f>INDEX($D$25:$O$25,C68)</f>
         <v/>
       </c>
-      <c r="G68" s="139">
+      <c r="G68" s="140">
         <f>ROUND(F68*E68/D68,1)</f>
         <v/>
       </c>
-      <c r="H68" s="139">
+      <c r="H68" s="140">
         <f>F68+E68-G68</f>
         <v/>
       </c>
-      <c r="I68" s="139">
+      <c r="I68" s="140">
         <f>ROUND(MAX(H68,8),0)</f>
         <v/>
       </c>
-      <c r="J68" s="139">
+      <c r="J68" s="140">
         <f>D68-I68</f>
         <v/>
       </c>
-      <c r="K68" s="139">
+      <c r="K68" s="140">
         <f>K67+J67</f>
         <v/>
       </c>
-      <c r="L68" s="139">
+      <c r="L68" s="140">
         <f>L67+D67</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="139" t="n">
+      <c r="A69" s="140" t="n">
         <v>12</v>
       </c>
-      <c r="B69" s="139">
+      <c r="B69" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A69-1))</f>
         <v/>
       </c>
-      <c r="C69" s="139">
+      <c r="C69" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A69-1))</f>
         <v/>
       </c>
-      <c r="D69" s="139">
+      <c r="D69" s="140">
         <f>DAY(EOMONTH(DATE(B69,C69,1),0))</f>
         <v/>
       </c>
-      <c r="E69" s="139">
+      <c r="E69" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B69,법정공휴일!$A$4:$A$20,0),C69),0)</f>
         <v/>
       </c>
-      <c r="F69" s="139">
+      <c r="F69" s="140">
         <f>INDEX($D$25:$O$25,C69)</f>
         <v/>
       </c>
-      <c r="G69" s="139">
+      <c r="G69" s="140">
         <f>ROUND(F69*E69/D69,1)</f>
         <v/>
       </c>
-      <c r="H69" s="139">
+      <c r="H69" s="140">
         <f>F69+E69-G69</f>
         <v/>
       </c>
-      <c r="I69" s="139">
+      <c r="I69" s="140">
         <f>ROUND(MAX(H69,8),0)</f>
         <v/>
       </c>
-      <c r="J69" s="139">
+      <c r="J69" s="140">
         <f>D69-I69</f>
         <v/>
       </c>
-      <c r="K69" s="139">
+      <c r="K69" s="140">
         <f>K68+J68</f>
         <v/>
       </c>
-      <c r="L69" s="139">
+      <c r="L69" s="140">
         <f>L68+D68</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="139" t="n">
+      <c r="A70" s="140" t="n">
         <v>13</v>
       </c>
-      <c r="B70" s="139">
+      <c r="B70" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A70-1))</f>
         <v/>
       </c>
-      <c r="C70" s="139">
+      <c r="C70" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A70-1))</f>
         <v/>
       </c>
-      <c r="D70" s="139">
+      <c r="D70" s="140">
         <f>DAY(EOMONTH(DATE(B70,C70,1),0))</f>
         <v/>
       </c>
-      <c r="E70" s="139">
+      <c r="E70" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B70,법정공휴일!$A$4:$A$20,0),C70),0)</f>
         <v/>
       </c>
-      <c r="F70" s="139">
+      <c r="F70" s="140">
         <f>INDEX($D$25:$O$25,C70)</f>
         <v/>
       </c>
-      <c r="G70" s="139">
+      <c r="G70" s="140">
         <f>ROUND(F70*E70/D70,1)</f>
         <v/>
       </c>
-      <c r="H70" s="139">
+      <c r="H70" s="140">
         <f>F70+E70-G70</f>
         <v/>
       </c>
-      <c r="I70" s="139">
+      <c r="I70" s="140">
         <f>ROUND(MAX(H70,8),0)</f>
         <v/>
       </c>
-      <c r="J70" s="139">
+      <c r="J70" s="140">
         <f>D70-I70</f>
         <v/>
       </c>
-      <c r="K70" s="139">
+      <c r="K70" s="140">
         <f>K69+J69</f>
         <v/>
       </c>
-      <c r="L70" s="139">
+      <c r="L70" s="140">
         <f>L69+D69</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="139" t="n">
+      <c r="A71" s="140" t="n">
         <v>14</v>
       </c>
-      <c r="B71" s="139">
+      <c r="B71" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A71-1))</f>
         <v/>
       </c>
-      <c r="C71" s="139">
+      <c r="C71" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A71-1))</f>
         <v/>
       </c>
-      <c r="D71" s="139">
+      <c r="D71" s="140">
         <f>DAY(EOMONTH(DATE(B71,C71,1),0))</f>
         <v/>
       </c>
-      <c r="E71" s="139">
+      <c r="E71" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B71,법정공휴일!$A$4:$A$20,0),C71),0)</f>
         <v/>
       </c>
-      <c r="F71" s="139">
+      <c r="F71" s="140">
         <f>INDEX($D$25:$O$25,C71)</f>
         <v/>
       </c>
-      <c r="G71" s="139">
+      <c r="G71" s="140">
         <f>ROUND(F71*E71/D71,1)</f>
         <v/>
       </c>
-      <c r="H71" s="139">
+      <c r="H71" s="140">
         <f>F71+E71-G71</f>
         <v/>
       </c>
-      <c r="I71" s="139">
+      <c r="I71" s="140">
         <f>ROUND(MAX(H71,8),0)</f>
         <v/>
       </c>
-      <c r="J71" s="139">
+      <c r="J71" s="140">
         <f>D71-I71</f>
         <v/>
       </c>
-      <c r="K71" s="139">
+      <c r="K71" s="140">
         <f>K70+J70</f>
         <v/>
       </c>
-      <c r="L71" s="139">
+      <c r="L71" s="140">
         <f>L70+D70</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="139" t="n">
+      <c r="A72" s="140" t="n">
         <v>15</v>
       </c>
-      <c r="B72" s="139">
+      <c r="B72" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A72-1))</f>
         <v/>
       </c>
-      <c r="C72" s="139">
+      <c r="C72" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A72-1))</f>
         <v/>
       </c>
-      <c r="D72" s="139">
+      <c r="D72" s="140">
         <f>DAY(EOMONTH(DATE(B72,C72,1),0))</f>
         <v/>
       </c>
-      <c r="E72" s="139">
+      <c r="E72" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B72,법정공휴일!$A$4:$A$20,0),C72),0)</f>
         <v/>
       </c>
-      <c r="F72" s="139">
+      <c r="F72" s="140">
         <f>INDEX($D$25:$O$25,C72)</f>
         <v/>
       </c>
-      <c r="G72" s="139">
+      <c r="G72" s="140">
         <f>ROUND(F72*E72/D72,1)</f>
         <v/>
       </c>
-      <c r="H72" s="139">
+      <c r="H72" s="140">
         <f>F72+E72-G72</f>
         <v/>
       </c>
-      <c r="I72" s="139">
+      <c r="I72" s="140">
         <f>ROUND(MAX(H72,8),0)</f>
         <v/>
       </c>
-      <c r="J72" s="139">
+      <c r="J72" s="140">
         <f>D72-I72</f>
         <v/>
       </c>
-      <c r="K72" s="139">
+      <c r="K72" s="140">
         <f>K71+J71</f>
         <v/>
       </c>
-      <c r="L72" s="139">
+      <c r="L72" s="140">
         <f>L71+D71</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="139" t="n">
+      <c r="A73" s="140" t="n">
         <v>16</v>
       </c>
-      <c r="B73" s="139">
+      <c r="B73" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A73-1))</f>
         <v/>
       </c>
-      <c r="C73" s="139">
+      <c r="C73" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A73-1))</f>
         <v/>
       </c>
-      <c r="D73" s="139">
+      <c r="D73" s="140">
         <f>DAY(EOMONTH(DATE(B73,C73,1),0))</f>
         <v/>
       </c>
-      <c r="E73" s="139">
+      <c r="E73" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B73,법정공휴일!$A$4:$A$20,0),C73),0)</f>
         <v/>
       </c>
-      <c r="F73" s="139">
+      <c r="F73" s="140">
         <f>INDEX($D$25:$O$25,C73)</f>
         <v/>
       </c>
-      <c r="G73" s="139">
+      <c r="G73" s="140">
         <f>ROUND(F73*E73/D73,1)</f>
         <v/>
       </c>
-      <c r="H73" s="139">
+      <c r="H73" s="140">
         <f>F73+E73-G73</f>
         <v/>
       </c>
-      <c r="I73" s="139">
+      <c r="I73" s="140">
         <f>ROUND(MAX(H73,8),0)</f>
         <v/>
       </c>
-      <c r="J73" s="139">
+      <c r="J73" s="140">
         <f>D73-I73</f>
         <v/>
       </c>
-      <c r="K73" s="139">
+      <c r="K73" s="140">
         <f>K72+J72</f>
         <v/>
       </c>
-      <c r="L73" s="139">
+      <c r="L73" s="140">
         <f>L72+D72</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="139" t="n">
+      <c r="A74" s="140" t="n">
         <v>17</v>
       </c>
-      <c r="B74" s="139">
+      <c r="B74" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A74-1))</f>
         <v/>
       </c>
-      <c r="C74" s="139">
+      <c r="C74" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A74-1))</f>
         <v/>
       </c>
-      <c r="D74" s="139">
+      <c r="D74" s="140">
         <f>DAY(EOMONTH(DATE(B74,C74,1),0))</f>
         <v/>
       </c>
-      <c r="E74" s="139">
+      <c r="E74" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B74,법정공휴일!$A$4:$A$20,0),C74),0)</f>
         <v/>
       </c>
-      <c r="F74" s="139">
+      <c r="F74" s="140">
         <f>INDEX($D$25:$O$25,C74)</f>
         <v/>
       </c>
-      <c r="G74" s="139">
+      <c r="G74" s="140">
         <f>ROUND(F74*E74/D74,1)</f>
         <v/>
       </c>
-      <c r="H74" s="139">
+      <c r="H74" s="140">
         <f>F74+E74-G74</f>
         <v/>
       </c>
-      <c r="I74" s="139">
+      <c r="I74" s="140">
         <f>ROUND(MAX(H74,8),0)</f>
         <v/>
       </c>
-      <c r="J74" s="139">
+      <c r="J74" s="140">
         <f>D74-I74</f>
         <v/>
       </c>
-      <c r="K74" s="139">
+      <c r="K74" s="140">
         <f>K73+J73</f>
         <v/>
       </c>
-      <c r="L74" s="139">
+      <c r="L74" s="140">
         <f>L73+D73</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="139" t="n">
+      <c r="A75" s="140" t="n">
         <v>18</v>
       </c>
-      <c r="B75" s="139">
+      <c r="B75" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A75-1))</f>
         <v/>
       </c>
-      <c r="C75" s="139">
+      <c r="C75" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A75-1))</f>
         <v/>
       </c>
-      <c r="D75" s="139">
+      <c r="D75" s="140">
         <f>DAY(EOMONTH(DATE(B75,C75,1),0))</f>
         <v/>
       </c>
-      <c r="E75" s="139">
+      <c r="E75" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B75,법정공휴일!$A$4:$A$20,0),C75),0)</f>
         <v/>
       </c>
-      <c r="F75" s="139">
+      <c r="F75" s="140">
         <f>INDEX($D$25:$O$25,C75)</f>
         <v/>
       </c>
-      <c r="G75" s="139">
+      <c r="G75" s="140">
         <f>ROUND(F75*E75/D75,1)</f>
         <v/>
       </c>
-      <c r="H75" s="139">
+      <c r="H75" s="140">
         <f>F75+E75-G75</f>
         <v/>
       </c>
-      <c r="I75" s="139">
+      <c r="I75" s="140">
         <f>ROUND(MAX(H75,8),0)</f>
         <v/>
       </c>
-      <c r="J75" s="139">
+      <c r="J75" s="140">
         <f>D75-I75</f>
         <v/>
       </c>
-      <c r="K75" s="139">
+      <c r="K75" s="140">
         <f>K74+J74</f>
         <v/>
       </c>
-      <c r="L75" s="139">
+      <c r="L75" s="140">
         <f>L74+D74</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="139" t="n">
+      <c r="A76" s="140" t="n">
         <v>19</v>
       </c>
-      <c r="B76" s="139">
+      <c r="B76" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A76-1))</f>
         <v/>
       </c>
-      <c r="C76" s="139">
+      <c r="C76" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A76-1))</f>
         <v/>
       </c>
-      <c r="D76" s="139">
+      <c r="D76" s="140">
         <f>DAY(EOMONTH(DATE(B76,C76,1),0))</f>
         <v/>
       </c>
-      <c r="E76" s="139">
+      <c r="E76" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B76,법정공휴일!$A$4:$A$20,0),C76),0)</f>
         <v/>
       </c>
-      <c r="F76" s="139">
+      <c r="F76" s="140">
         <f>INDEX($D$25:$O$25,C76)</f>
         <v/>
       </c>
-      <c r="G76" s="139">
+      <c r="G76" s="140">
         <f>ROUND(F76*E76/D76,1)</f>
         <v/>
       </c>
-      <c r="H76" s="139">
+      <c r="H76" s="140">
         <f>F76+E76-G76</f>
         <v/>
       </c>
-      <c r="I76" s="139">
+      <c r="I76" s="140">
         <f>ROUND(MAX(H76,8),0)</f>
         <v/>
       </c>
-      <c r="J76" s="139">
+      <c r="J76" s="140">
         <f>D76-I76</f>
         <v/>
       </c>
-      <c r="K76" s="139">
+      <c r="K76" s="140">
         <f>K75+J75</f>
         <v/>
       </c>
-      <c r="L76" s="139">
+      <c r="L76" s="140">
         <f>L75+D75</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="139" t="n">
+      <c r="A77" s="140" t="n">
         <v>20</v>
       </c>
-      <c r="B77" s="139">
+      <c r="B77" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A77-1))</f>
         <v/>
       </c>
-      <c r="C77" s="139">
+      <c r="C77" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A77-1))</f>
         <v/>
       </c>
-      <c r="D77" s="139">
+      <c r="D77" s="140">
         <f>DAY(EOMONTH(DATE(B77,C77,1),0))</f>
         <v/>
       </c>
-      <c r="E77" s="139">
+      <c r="E77" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B77,법정공휴일!$A$4:$A$20,0),C77),0)</f>
         <v/>
       </c>
-      <c r="F77" s="139">
+      <c r="F77" s="140">
         <f>INDEX($D$25:$O$25,C77)</f>
         <v/>
       </c>
-      <c r="G77" s="139">
+      <c r="G77" s="140">
         <f>ROUND(F77*E77/D77,1)</f>
         <v/>
       </c>
-      <c r="H77" s="139">
+      <c r="H77" s="140">
         <f>F77+E77-G77</f>
         <v/>
       </c>
-      <c r="I77" s="139">
+      <c r="I77" s="140">
         <f>ROUND(MAX(H77,8),0)</f>
         <v/>
       </c>
-      <c r="J77" s="139">
+      <c r="J77" s="140">
         <f>D77-I77</f>
         <v/>
       </c>
-      <c r="K77" s="139">
+      <c r="K77" s="140">
         <f>K76+J76</f>
         <v/>
       </c>
-      <c r="L77" s="139">
+      <c r="L77" s="140">
         <f>L76+D76</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="139" t="n">
+      <c r="A78" s="140" t="n">
         <v>21</v>
       </c>
-      <c r="B78" s="139">
+      <c r="B78" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A78-1))</f>
         <v/>
       </c>
-      <c r="C78" s="139">
+      <c r="C78" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A78-1))</f>
         <v/>
       </c>
-      <c r="D78" s="139">
+      <c r="D78" s="140">
         <f>DAY(EOMONTH(DATE(B78,C78,1),0))</f>
         <v/>
       </c>
-      <c r="E78" s="139">
+      <c r="E78" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B78,법정공휴일!$A$4:$A$20,0),C78),0)</f>
         <v/>
       </c>
-      <c r="F78" s="139">
+      <c r="F78" s="140">
         <f>INDEX($D$25:$O$25,C78)</f>
         <v/>
       </c>
-      <c r="G78" s="139">
+      <c r="G78" s="140">
         <f>ROUND(F78*E78/D78,1)</f>
         <v/>
       </c>
-      <c r="H78" s="139">
+      <c r="H78" s="140">
         <f>F78+E78-G78</f>
         <v/>
       </c>
-      <c r="I78" s="139">
+      <c r="I78" s="140">
         <f>ROUND(MAX(H78,8),0)</f>
         <v/>
       </c>
-      <c r="J78" s="139">
+      <c r="J78" s="140">
         <f>D78-I78</f>
         <v/>
       </c>
-      <c r="K78" s="139">
+      <c r="K78" s="140">
         <f>K77+J77</f>
         <v/>
       </c>
-      <c r="L78" s="139">
+      <c r="L78" s="140">
         <f>L77+D77</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="139" t="n">
+      <c r="A79" s="140" t="n">
         <v>22</v>
       </c>
-      <c r="B79" s="139">
+      <c r="B79" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A79-1))</f>
         <v/>
       </c>
-      <c r="C79" s="139">
+      <c r="C79" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A79-1))</f>
         <v/>
       </c>
-      <c r="D79" s="139">
+      <c r="D79" s="140">
         <f>DAY(EOMONTH(DATE(B79,C79,1),0))</f>
         <v/>
       </c>
-      <c r="E79" s="139">
+      <c r="E79" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B79,법정공휴일!$A$4:$A$20,0),C79),0)</f>
         <v/>
       </c>
-      <c r="F79" s="139">
+      <c r="F79" s="140">
         <f>INDEX($D$25:$O$25,C79)</f>
         <v/>
       </c>
-      <c r="G79" s="139">
+      <c r="G79" s="140">
         <f>ROUND(F79*E79/D79,1)</f>
         <v/>
       </c>
-      <c r="H79" s="139">
+      <c r="H79" s="140">
         <f>F79+E79-G79</f>
         <v/>
       </c>
-      <c r="I79" s="139">
+      <c r="I79" s="140">
         <f>ROUND(MAX(H79,8),0)</f>
         <v/>
       </c>
-      <c r="J79" s="139">
+      <c r="J79" s="140">
         <f>D79-I79</f>
         <v/>
       </c>
-      <c r="K79" s="139">
+      <c r="K79" s="140">
         <f>K78+J78</f>
         <v/>
       </c>
-      <c r="L79" s="139">
+      <c r="L79" s="140">
         <f>L78+D78</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="139" t="n">
+      <c r="A80" s="140" t="n">
         <v>23</v>
       </c>
-      <c r="B80" s="139">
+      <c r="B80" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A80-1))</f>
         <v/>
       </c>
-      <c r="C80" s="139">
+      <c r="C80" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A80-1))</f>
         <v/>
       </c>
-      <c r="D80" s="139">
+      <c r="D80" s="140">
         <f>DAY(EOMONTH(DATE(B80,C80,1),0))</f>
         <v/>
       </c>
-      <c r="E80" s="139">
+      <c r="E80" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B80,법정공휴일!$A$4:$A$20,0),C80),0)</f>
         <v/>
       </c>
-      <c r="F80" s="139">
+      <c r="F80" s="140">
         <f>INDEX($D$25:$O$25,C80)</f>
         <v/>
       </c>
-      <c r="G80" s="139">
+      <c r="G80" s="140">
         <f>ROUND(F80*E80/D80,1)</f>
         <v/>
       </c>
-      <c r="H80" s="139">
+      <c r="H80" s="140">
         <f>F80+E80-G80</f>
         <v/>
       </c>
-      <c r="I80" s="139">
+      <c r="I80" s="140">
         <f>ROUND(MAX(H80,8),0)</f>
         <v/>
       </c>
-      <c r="J80" s="139">
+      <c r="J80" s="140">
         <f>D80-I80</f>
         <v/>
       </c>
-      <c r="K80" s="139">
+      <c r="K80" s="140">
         <f>K79+J79</f>
         <v/>
       </c>
-      <c r="L80" s="139">
+      <c r="L80" s="140">
         <f>L79+D79</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="139" t="n">
+      <c r="A81" s="140" t="n">
         <v>24</v>
       </c>
-      <c r="B81" s="139">
+      <c r="B81" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A81-1))</f>
         <v/>
       </c>
-      <c r="C81" s="139">
+      <c r="C81" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A81-1))</f>
         <v/>
       </c>
-      <c r="D81" s="139">
+      <c r="D81" s="140">
         <f>DAY(EOMONTH(DATE(B81,C81,1),0))</f>
         <v/>
       </c>
-      <c r="E81" s="139">
+      <c r="E81" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B81,법정공휴일!$A$4:$A$20,0),C81),0)</f>
         <v/>
       </c>
-      <c r="F81" s="139">
+      <c r="F81" s="140">
         <f>INDEX($D$25:$O$25,C81)</f>
         <v/>
       </c>
-      <c r="G81" s="139">
+      <c r="G81" s="140">
         <f>ROUND(F81*E81/D81,1)</f>
         <v/>
       </c>
-      <c r="H81" s="139">
+      <c r="H81" s="140">
         <f>F81+E81-G81</f>
         <v/>
       </c>
-      <c r="I81" s="139">
+      <c r="I81" s="140">
         <f>ROUND(MAX(H81,8),0)</f>
         <v/>
       </c>
-      <c r="J81" s="139">
+      <c r="J81" s="140">
         <f>D81-I81</f>
         <v/>
       </c>
-      <c r="K81" s="139">
+      <c r="K81" s="140">
         <f>K80+J80</f>
         <v/>
       </c>
-      <c r="L81" s="139">
+      <c r="L81" s="140">
         <f>L80+D80</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="139" t="n">
+      <c r="A82" s="140" t="n">
         <v>25</v>
       </c>
-      <c r="B82" s="139">
+      <c r="B82" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A82-1))</f>
         <v/>
       </c>
-      <c r="C82" s="139">
+      <c r="C82" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A82-1))</f>
         <v/>
       </c>
-      <c r="D82" s="139">
+      <c r="D82" s="140">
         <f>DAY(EOMONTH(DATE(B82,C82,1),0))</f>
         <v/>
       </c>
-      <c r="E82" s="139">
+      <c r="E82" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B82,법정공휴일!$A$4:$A$20,0),C82),0)</f>
         <v/>
       </c>
-      <c r="F82" s="139">
+      <c r="F82" s="140">
         <f>INDEX($D$25:$O$25,C82)</f>
         <v/>
       </c>
-      <c r="G82" s="139">
+      <c r="G82" s="140">
         <f>ROUND(F82*E82/D82,1)</f>
         <v/>
       </c>
-      <c r="H82" s="139">
+      <c r="H82" s="140">
         <f>F82+E82-G82</f>
         <v/>
       </c>
-      <c r="I82" s="139">
+      <c r="I82" s="140">
         <f>ROUND(MAX(H82,8),0)</f>
         <v/>
       </c>
-      <c r="J82" s="139">
+      <c r="J82" s="140">
         <f>D82-I82</f>
         <v/>
       </c>
-      <c r="K82" s="139">
+      <c r="K82" s="140">
         <f>K81+J81</f>
         <v/>
       </c>
-      <c r="L82" s="139">
+      <c r="L82" s="140">
         <f>L81+D81</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="139" t="n">
+      <c r="A83" s="140" t="n">
         <v>26</v>
       </c>
-      <c r="B83" s="139">
+      <c r="B83" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A83-1))</f>
         <v/>
       </c>
-      <c r="C83" s="139">
+      <c r="C83" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A83-1))</f>
         <v/>
       </c>
-      <c r="D83" s="139">
+      <c r="D83" s="140">
         <f>DAY(EOMONTH(DATE(B83,C83,1),0))</f>
         <v/>
       </c>
-      <c r="E83" s="139">
+      <c r="E83" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B83,법정공휴일!$A$4:$A$20,0),C83),0)</f>
         <v/>
       </c>
-      <c r="F83" s="139">
+      <c r="F83" s="140">
         <f>INDEX($D$25:$O$25,C83)</f>
         <v/>
       </c>
-      <c r="G83" s="139">
+      <c r="G83" s="140">
         <f>ROUND(F83*E83/D83,1)</f>
         <v/>
       </c>
-      <c r="H83" s="139">
+      <c r="H83" s="140">
         <f>F83+E83-G83</f>
         <v/>
       </c>
-      <c r="I83" s="139">
+      <c r="I83" s="140">
         <f>ROUND(MAX(H83,8),0)</f>
         <v/>
       </c>
-      <c r="J83" s="139">
+      <c r="J83" s="140">
         <f>D83-I83</f>
         <v/>
       </c>
-      <c r="K83" s="139">
+      <c r="K83" s="140">
         <f>K82+J82</f>
         <v/>
       </c>
-      <c r="L83" s="139">
+      <c r="L83" s="140">
         <f>L82+D82</f>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="139" t="n">
+      <c r="A84" s="140" t="n">
         <v>27</v>
       </c>
-      <c r="B84" s="139">
+      <c r="B84" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A84-1))</f>
         <v/>
       </c>
-      <c r="C84" s="139">
+      <c r="C84" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A84-1))</f>
         <v/>
       </c>
-      <c r="D84" s="139">
+      <c r="D84" s="140">
         <f>DAY(EOMONTH(DATE(B84,C84,1),0))</f>
         <v/>
       </c>
-      <c r="E84" s="139">
+      <c r="E84" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B84,법정공휴일!$A$4:$A$20,0),C84),0)</f>
         <v/>
       </c>
-      <c r="F84" s="139">
+      <c r="F84" s="140">
         <f>INDEX($D$25:$O$25,C84)</f>
         <v/>
       </c>
-      <c r="G84" s="139">
+      <c r="G84" s="140">
         <f>ROUND(F84*E84/D84,1)</f>
         <v/>
       </c>
-      <c r="H84" s="139">
+      <c r="H84" s="140">
         <f>F84+E84-G84</f>
         <v/>
       </c>
-      <c r="I84" s="139">
+      <c r="I84" s="140">
         <f>ROUND(MAX(H84,8),0)</f>
         <v/>
       </c>
-      <c r="J84" s="139">
+      <c r="J84" s="140">
         <f>D84-I84</f>
         <v/>
       </c>
-      <c r="K84" s="139">
+      <c r="K84" s="140">
         <f>K83+J83</f>
         <v/>
       </c>
-      <c r="L84" s="139">
+      <c r="L84" s="140">
         <f>L83+D83</f>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="139" t="n">
+      <c r="A85" s="140" t="n">
         <v>28</v>
       </c>
-      <c r="B85" s="139">
+      <c r="B85" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A85-1))</f>
         <v/>
       </c>
-      <c r="C85" s="139">
+      <c r="C85" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A85-1))</f>
         <v/>
       </c>
-      <c r="D85" s="139">
+      <c r="D85" s="140">
         <f>DAY(EOMONTH(DATE(B85,C85,1),0))</f>
         <v/>
       </c>
-      <c r="E85" s="139">
+      <c r="E85" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B85,법정공휴일!$A$4:$A$20,0),C85),0)</f>
         <v/>
       </c>
-      <c r="F85" s="139">
+      <c r="F85" s="140">
         <f>INDEX($D$25:$O$25,C85)</f>
         <v/>
       </c>
-      <c r="G85" s="139">
+      <c r="G85" s="140">
         <f>ROUND(F85*E85/D85,1)</f>
         <v/>
       </c>
-      <c r="H85" s="139">
+      <c r="H85" s="140">
         <f>F85+E85-G85</f>
         <v/>
       </c>
-      <c r="I85" s="139">
+      <c r="I85" s="140">
         <f>ROUND(MAX(H85,8),0)</f>
         <v/>
       </c>
-      <c r="J85" s="139">
+      <c r="J85" s="140">
         <f>D85-I85</f>
         <v/>
       </c>
-      <c r="K85" s="139">
+      <c r="K85" s="140">
         <f>K84+J84</f>
         <v/>
       </c>
-      <c r="L85" s="139">
+      <c r="L85" s="140">
         <f>L84+D84</f>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="139" t="n">
+      <c r="A86" s="140" t="n">
         <v>29</v>
       </c>
-      <c r="B86" s="139">
+      <c r="B86" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A86-1))</f>
         <v/>
       </c>
-      <c r="C86" s="139">
+      <c r="C86" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A86-1))</f>
         <v/>
       </c>
-      <c r="D86" s="139">
+      <c r="D86" s="140">
         <f>DAY(EOMONTH(DATE(B86,C86,1),0))</f>
         <v/>
       </c>
-      <c r="E86" s="139">
+      <c r="E86" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B86,법정공휴일!$A$4:$A$20,0),C86),0)</f>
         <v/>
       </c>
-      <c r="F86" s="139">
+      <c r="F86" s="140">
         <f>INDEX($D$25:$O$25,C86)</f>
         <v/>
       </c>
-      <c r="G86" s="139">
+      <c r="G86" s="140">
         <f>ROUND(F86*E86/D86,1)</f>
         <v/>
       </c>
-      <c r="H86" s="139">
+      <c r="H86" s="140">
         <f>F86+E86-G86</f>
         <v/>
       </c>
-      <c r="I86" s="139">
+      <c r="I86" s="140">
         <f>ROUND(MAX(H86,8),0)</f>
         <v/>
       </c>
-      <c r="J86" s="139">
+      <c r="J86" s="140">
         <f>D86-I86</f>
         <v/>
       </c>
-      <c r="K86" s="139">
+      <c r="K86" s="140">
         <f>K85+J85</f>
         <v/>
       </c>
-      <c r="L86" s="139">
+      <c r="L86" s="140">
         <f>L85+D85</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="139" t="n">
+      <c r="A87" s="140" t="n">
         <v>30</v>
       </c>
-      <c r="B87" s="139">
+      <c r="B87" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A87-1))</f>
         <v/>
       </c>
-      <c r="C87" s="139">
+      <c r="C87" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A87-1))</f>
         <v/>
       </c>
-      <c r="D87" s="139">
+      <c r="D87" s="140">
         <f>DAY(EOMONTH(DATE(B87,C87,1),0))</f>
         <v/>
       </c>
-      <c r="E87" s="139">
+      <c r="E87" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B87,법정공휴일!$A$4:$A$20,0),C87),0)</f>
         <v/>
       </c>
-      <c r="F87" s="139">
+      <c r="F87" s="140">
         <f>INDEX($D$25:$O$25,C87)</f>
         <v/>
       </c>
-      <c r="G87" s="139">
+      <c r="G87" s="140">
         <f>ROUND(F87*E87/D87,1)</f>
         <v/>
       </c>
-      <c r="H87" s="139">
+      <c r="H87" s="140">
         <f>F87+E87-G87</f>
         <v/>
       </c>
-      <c r="I87" s="139">
+      <c r="I87" s="140">
         <f>ROUND(MAX(H87,8),0)</f>
         <v/>
       </c>
-      <c r="J87" s="139">
+      <c r="J87" s="140">
         <f>D87-I87</f>
         <v/>
       </c>
-      <c r="K87" s="139">
+      <c r="K87" s="140">
         <f>K86+J86</f>
         <v/>
       </c>
-      <c r="L87" s="139">
+      <c r="L87" s="140">
         <f>L86+D86</f>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="139" t="n">
+      <c r="A88" s="140" t="n">
         <v>31</v>
       </c>
-      <c r="B88" s="139">
+      <c r="B88" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A88-1))</f>
         <v/>
       </c>
-      <c r="C88" s="139">
+      <c r="C88" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A88-1))</f>
         <v/>
       </c>
-      <c r="D88" s="139">
+      <c r="D88" s="140">
         <f>DAY(EOMONTH(DATE(B88,C88,1),0))</f>
         <v/>
       </c>
-      <c r="E88" s="139">
+      <c r="E88" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B88,법정공휴일!$A$4:$A$20,0),C88),0)</f>
         <v/>
       </c>
-      <c r="F88" s="139">
+      <c r="F88" s="140">
         <f>INDEX($D$25:$O$25,C88)</f>
         <v/>
       </c>
-      <c r="G88" s="139">
+      <c r="G88" s="140">
         <f>ROUND(F88*E88/D88,1)</f>
         <v/>
       </c>
-      <c r="H88" s="139">
+      <c r="H88" s="140">
         <f>F88+E88-G88</f>
         <v/>
       </c>
-      <c r="I88" s="139">
+      <c r="I88" s="140">
         <f>ROUND(MAX(H88,8),0)</f>
         <v/>
       </c>
-      <c r="J88" s="139">
+      <c r="J88" s="140">
         <f>D88-I88</f>
         <v/>
       </c>
-      <c r="K88" s="139">
+      <c r="K88" s="140">
         <f>K87+J87</f>
         <v/>
       </c>
-      <c r="L88" s="139">
+      <c r="L88" s="140">
         <f>L87+D87</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="139" t="n">
+      <c r="A89" s="140" t="n">
         <v>32</v>
       </c>
-      <c r="B89" s="139">
+      <c r="B89" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A89-1))</f>
         <v/>
       </c>
-      <c r="C89" s="139">
+      <c r="C89" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A89-1))</f>
         <v/>
       </c>
-      <c r="D89" s="139">
+      <c r="D89" s="140">
         <f>DAY(EOMONTH(DATE(B89,C89,1),0))</f>
         <v/>
       </c>
-      <c r="E89" s="139">
+      <c r="E89" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B89,법정공휴일!$A$4:$A$20,0),C89),0)</f>
         <v/>
       </c>
-      <c r="F89" s="139">
+      <c r="F89" s="140">
         <f>INDEX($D$25:$O$25,C89)</f>
         <v/>
       </c>
-      <c r="G89" s="139">
+      <c r="G89" s="140">
         <f>ROUND(F89*E89/D89,1)</f>
         <v/>
       </c>
-      <c r="H89" s="139">
+      <c r="H89" s="140">
         <f>F89+E89-G89</f>
         <v/>
       </c>
-      <c r="I89" s="139">
+      <c r="I89" s="140">
         <f>ROUND(MAX(H89,8),0)</f>
         <v/>
       </c>
-      <c r="J89" s="139">
+      <c r="J89" s="140">
         <f>D89-I89</f>
         <v/>
       </c>
-      <c r="K89" s="139">
+      <c r="K89" s="140">
         <f>K88+J88</f>
         <v/>
       </c>
-      <c r="L89" s="139">
+      <c r="L89" s="140">
         <f>L88+D88</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="139" t="n">
+      <c r="A90" s="140" t="n">
         <v>33</v>
       </c>
-      <c r="B90" s="139">
+      <c r="B90" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A90-1))</f>
         <v/>
       </c>
-      <c r="C90" s="139">
+      <c r="C90" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A90-1))</f>
         <v/>
       </c>
-      <c r="D90" s="139">
+      <c r="D90" s="140">
         <f>DAY(EOMONTH(DATE(B90,C90,1),0))</f>
         <v/>
       </c>
-      <c r="E90" s="139">
+      <c r="E90" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B90,법정공휴일!$A$4:$A$20,0),C90),0)</f>
         <v/>
       </c>
-      <c r="F90" s="139">
+      <c r="F90" s="140">
         <f>INDEX($D$25:$O$25,C90)</f>
         <v/>
       </c>
-      <c r="G90" s="139">
+      <c r="G90" s="140">
         <f>ROUND(F90*E90/D90,1)</f>
         <v/>
       </c>
-      <c r="H90" s="139">
+      <c r="H90" s="140">
         <f>F90+E90-G90</f>
         <v/>
       </c>
-      <c r="I90" s="139">
+      <c r="I90" s="140">
         <f>ROUND(MAX(H90,8),0)</f>
         <v/>
       </c>
-      <c r="J90" s="139">
+      <c r="J90" s="140">
         <f>D90-I90</f>
         <v/>
       </c>
-      <c r="K90" s="139">
+      <c r="K90" s="140">
         <f>K89+J89</f>
         <v/>
       </c>
-      <c r="L90" s="139">
+      <c r="L90" s="140">
         <f>L89+D89</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="139" t="n">
+      <c r="A91" s="140" t="n">
         <v>34</v>
       </c>
-      <c r="B91" s="139">
+      <c r="B91" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A91-1))</f>
         <v/>
       </c>
-      <c r="C91" s="139">
+      <c r="C91" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A91-1))</f>
         <v/>
       </c>
-      <c r="D91" s="139">
+      <c r="D91" s="140">
         <f>DAY(EOMONTH(DATE(B91,C91,1),0))</f>
         <v/>
       </c>
-      <c r="E91" s="139">
+      <c r="E91" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B91,법정공휴일!$A$4:$A$20,0),C91),0)</f>
         <v/>
       </c>
-      <c r="F91" s="139">
+      <c r="F91" s="140">
         <f>INDEX($D$25:$O$25,C91)</f>
         <v/>
       </c>
-      <c r="G91" s="139">
+      <c r="G91" s="140">
         <f>ROUND(F91*E91/D91,1)</f>
         <v/>
       </c>
-      <c r="H91" s="139">
+      <c r="H91" s="140">
         <f>F91+E91-G91</f>
         <v/>
       </c>
-      <c r="I91" s="139">
+      <c r="I91" s="140">
         <f>ROUND(MAX(H91,8),0)</f>
         <v/>
       </c>
-      <c r="J91" s="139">
+      <c r="J91" s="140">
         <f>D91-I91</f>
         <v/>
       </c>
-      <c r="K91" s="139">
+      <c r="K91" s="140">
         <f>K90+J90</f>
         <v/>
       </c>
-      <c r="L91" s="139">
+      <c r="L91" s="140">
         <f>L90+D90</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="139" t="n">
+      <c r="A92" s="140" t="n">
         <v>35</v>
       </c>
-      <c r="B92" s="139">
+      <c r="B92" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A92-1))</f>
         <v/>
       </c>
-      <c r="C92" s="139">
+      <c r="C92" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A92-1))</f>
         <v/>
       </c>
-      <c r="D92" s="139">
+      <c r="D92" s="140">
         <f>DAY(EOMONTH(DATE(B92,C92,1),0))</f>
         <v/>
       </c>
-      <c r="E92" s="139">
+      <c r="E92" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B92,법정공휴일!$A$4:$A$20,0),C92),0)</f>
         <v/>
       </c>
-      <c r="F92" s="139">
+      <c r="F92" s="140">
         <f>INDEX($D$25:$O$25,C92)</f>
         <v/>
       </c>
-      <c r="G92" s="139">
+      <c r="G92" s="140">
         <f>ROUND(F92*E92/D92,1)</f>
         <v/>
       </c>
-      <c r="H92" s="139">
+      <c r="H92" s="140">
         <f>F92+E92-G92</f>
         <v/>
       </c>
-      <c r="I92" s="139">
+      <c r="I92" s="140">
         <f>ROUND(MAX(H92,8),0)</f>
         <v/>
       </c>
-      <c r="J92" s="139">
+      <c r="J92" s="140">
         <f>D92-I92</f>
         <v/>
       </c>
-      <c r="K92" s="139">
+      <c r="K92" s="140">
         <f>K91+J91</f>
         <v/>
       </c>
-      <c r="L92" s="139">
+      <c r="L92" s="140">
         <f>L91+D91</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="139" t="n">
+      <c r="A93" s="140" t="n">
         <v>36</v>
       </c>
-      <c r="B93" s="139">
+      <c r="B93" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A93-1))</f>
         <v/>
       </c>
-      <c r="C93" s="139">
+      <c r="C93" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A93-1))</f>
         <v/>
       </c>
-      <c r="D93" s="139">
+      <c r="D93" s="140">
         <f>DAY(EOMONTH(DATE(B93,C93,1),0))</f>
         <v/>
       </c>
-      <c r="E93" s="139">
+      <c r="E93" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B93,법정공휴일!$A$4:$A$20,0),C93),0)</f>
         <v/>
       </c>
-      <c r="F93" s="139">
+      <c r="F93" s="140">
         <f>INDEX($D$25:$O$25,C93)</f>
         <v/>
       </c>
-      <c r="G93" s="139">
+      <c r="G93" s="140">
         <f>ROUND(F93*E93/D93,1)</f>
         <v/>
       </c>
-      <c r="H93" s="139">
+      <c r="H93" s="140">
         <f>F93+E93-G93</f>
         <v/>
       </c>
-      <c r="I93" s="139">
+      <c r="I93" s="140">
         <f>ROUND(MAX(H93,8),0)</f>
         <v/>
       </c>
-      <c r="J93" s="139">
+      <c r="J93" s="140">
         <f>D93-I93</f>
         <v/>
       </c>
-      <c r="K93" s="139">
+      <c r="K93" s="140">
         <f>K92+J92</f>
         <v/>
       </c>
-      <c r="L93" s="139">
+      <c r="L93" s="140">
         <f>L92+D92</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="139" t="n">
+      <c r="A94" s="140" t="n">
         <v>37</v>
       </c>
-      <c r="B94" s="139">
+      <c r="B94" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A94-1))</f>
         <v/>
       </c>
-      <c r="C94" s="139">
+      <c r="C94" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A94-1))</f>
         <v/>
       </c>
-      <c r="D94" s="139">
+      <c r="D94" s="140">
         <f>DAY(EOMONTH(DATE(B94,C94,1),0))</f>
         <v/>
       </c>
-      <c r="E94" s="139">
+      <c r="E94" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B94,법정공휴일!$A$4:$A$20,0),C94),0)</f>
         <v/>
       </c>
-      <c r="F94" s="139">
+      <c r="F94" s="140">
         <f>INDEX($D$25:$O$25,C94)</f>
         <v/>
       </c>
-      <c r="G94" s="139">
+      <c r="G94" s="140">
         <f>ROUND(F94*E94/D94,1)</f>
         <v/>
       </c>
-      <c r="H94" s="139">
+      <c r="H94" s="140">
         <f>F94+E94-G94</f>
         <v/>
       </c>
-      <c r="I94" s="139">
+      <c r="I94" s="140">
         <f>ROUND(MAX(H94,8),0)</f>
         <v/>
       </c>
-      <c r="J94" s="139">
+      <c r="J94" s="140">
         <f>D94-I94</f>
         <v/>
       </c>
-      <c r="K94" s="139">
+      <c r="K94" s="140">
         <f>K93+J93</f>
         <v/>
       </c>
-      <c r="L94" s="139">
+      <c r="L94" s="140">
         <f>L93+D93</f>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="139" t="n">
+      <c r="A95" s="140" t="n">
         <v>38</v>
       </c>
-      <c r="B95" s="139">
+      <c r="B95" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A95-1))</f>
         <v/>
       </c>
-      <c r="C95" s="139">
+      <c r="C95" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A95-1))</f>
         <v/>
       </c>
-      <c r="D95" s="139">
+      <c r="D95" s="140">
         <f>DAY(EOMONTH(DATE(B95,C95,1),0))</f>
         <v/>
       </c>
-      <c r="E95" s="139">
+      <c r="E95" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B95,법정공휴일!$A$4:$A$20,0),C95),0)</f>
         <v/>
       </c>
-      <c r="F95" s="139">
+      <c r="F95" s="140">
         <f>INDEX($D$25:$O$25,C95)</f>
         <v/>
       </c>
-      <c r="G95" s="139">
+      <c r="G95" s="140">
         <f>ROUND(F95*E95/D95,1)</f>
         <v/>
       </c>
-      <c r="H95" s="139">
+      <c r="H95" s="140">
         <f>F95+E95-G95</f>
         <v/>
       </c>
-      <c r="I95" s="139">
+      <c r="I95" s="140">
         <f>ROUND(MAX(H95,8),0)</f>
         <v/>
       </c>
-      <c r="J95" s="139">
+      <c r="J95" s="140">
         <f>D95-I95</f>
         <v/>
       </c>
-      <c r="K95" s="139">
+      <c r="K95" s="140">
         <f>K94+J94</f>
         <v/>
       </c>
-      <c r="L95" s="139">
+      <c r="L95" s="140">
         <f>L94+D94</f>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="139" t="n">
+      <c r="A96" s="140" t="n">
         <v>39</v>
       </c>
-      <c r="B96" s="139">
+      <c r="B96" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A96-1))</f>
         <v/>
       </c>
-      <c r="C96" s="139">
+      <c r="C96" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A96-1))</f>
         <v/>
       </c>
-      <c r="D96" s="139">
+      <c r="D96" s="140">
         <f>DAY(EOMONTH(DATE(B96,C96,1),0))</f>
         <v/>
       </c>
-      <c r="E96" s="139">
+      <c r="E96" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B96,법정공휴일!$A$4:$A$20,0),C96),0)</f>
         <v/>
       </c>
-      <c r="F96" s="139">
+      <c r="F96" s="140">
         <f>INDEX($D$25:$O$25,C96)</f>
         <v/>
       </c>
-      <c r="G96" s="139">
+      <c r="G96" s="140">
         <f>ROUND(F96*E96/D96,1)</f>
         <v/>
       </c>
-      <c r="H96" s="139">
+      <c r="H96" s="140">
         <f>F96+E96-G96</f>
         <v/>
       </c>
-      <c r="I96" s="139">
+      <c r="I96" s="140">
         <f>ROUND(MAX(H96,8),0)</f>
         <v/>
       </c>
-      <c r="J96" s="139">
+      <c r="J96" s="140">
         <f>D96-I96</f>
         <v/>
       </c>
-      <c r="K96" s="139">
+      <c r="K96" s="140">
         <f>K95+J95</f>
         <v/>
       </c>
-      <c r="L96" s="139">
+      <c r="L96" s="140">
         <f>L95+D95</f>
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="139" t="n">
+      <c r="A97" s="140" t="n">
         <v>40</v>
       </c>
-      <c r="B97" s="139">
+      <c r="B97" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A97-1))</f>
         <v/>
       </c>
-      <c r="C97" s="139">
+      <c r="C97" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A97-1))</f>
         <v/>
       </c>
-      <c r="D97" s="139">
+      <c r="D97" s="140">
         <f>DAY(EOMONTH(DATE(B97,C97,1),0))</f>
         <v/>
       </c>
-      <c r="E97" s="139">
+      <c r="E97" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B97,법정공휴일!$A$4:$A$20,0),C97),0)</f>
         <v/>
       </c>
-      <c r="F97" s="139">
+      <c r="F97" s="140">
         <f>INDEX($D$25:$O$25,C97)</f>
         <v/>
       </c>
-      <c r="G97" s="139">
+      <c r="G97" s="140">
         <f>ROUND(F97*E97/D97,1)</f>
         <v/>
       </c>
-      <c r="H97" s="139">
+      <c r="H97" s="140">
         <f>F97+E97-G97</f>
         <v/>
       </c>
-      <c r="I97" s="139">
+      <c r="I97" s="140">
         <f>ROUND(MAX(H97,8),0)</f>
         <v/>
       </c>
-      <c r="J97" s="139">
+      <c r="J97" s="140">
         <f>D97-I97</f>
         <v/>
       </c>
-      <c r="K97" s="139">
+      <c r="K97" s="140">
         <f>K96+J96</f>
         <v/>
       </c>
-      <c r="L97" s="139">
+      <c r="L97" s="140">
         <f>L96+D96</f>
         <v/>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="139" t="n">
+      <c r="A98" s="140" t="n">
         <v>41</v>
       </c>
-      <c r="B98" s="139">
+      <c r="B98" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A98-1))</f>
         <v/>
       </c>
-      <c r="C98" s="139">
+      <c r="C98" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A98-1))</f>
         <v/>
       </c>
-      <c r="D98" s="139">
+      <c r="D98" s="140">
         <f>DAY(EOMONTH(DATE(B98,C98,1),0))</f>
         <v/>
       </c>
-      <c r="E98" s="139">
+      <c r="E98" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B98,법정공휴일!$A$4:$A$20,0),C98),0)</f>
         <v/>
       </c>
-      <c r="F98" s="139">
+      <c r="F98" s="140">
         <f>INDEX($D$25:$O$25,C98)</f>
         <v/>
       </c>
-      <c r="G98" s="139">
+      <c r="G98" s="140">
         <f>ROUND(F98*E98/D98,1)</f>
         <v/>
       </c>
-      <c r="H98" s="139">
+      <c r="H98" s="140">
         <f>F98+E98-G98</f>
         <v/>
       </c>
-      <c r="I98" s="139">
+      <c r="I98" s="140">
         <f>ROUND(MAX(H98,8),0)</f>
         <v/>
       </c>
-      <c r="J98" s="139">
+      <c r="J98" s="140">
         <f>D98-I98</f>
         <v/>
       </c>
-      <c r="K98" s="139">
+      <c r="K98" s="140">
         <f>K97+J97</f>
         <v/>
       </c>
-      <c r="L98" s="139">
+      <c r="L98" s="140">
         <f>L97+D97</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="139" t="n">
+      <c r="A99" s="140" t="n">
         <v>42</v>
       </c>
-      <c r="B99" s="139">
+      <c r="B99" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A99-1))</f>
         <v/>
       </c>
-      <c r="C99" s="139">
+      <c r="C99" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A99-1))</f>
         <v/>
       </c>
-      <c r="D99" s="139">
+      <c r="D99" s="140">
         <f>DAY(EOMONTH(DATE(B99,C99,1),0))</f>
         <v/>
       </c>
-      <c r="E99" s="139">
+      <c r="E99" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B99,법정공휴일!$A$4:$A$20,0),C99),0)</f>
         <v/>
       </c>
-      <c r="F99" s="139">
+      <c r="F99" s="140">
         <f>INDEX($D$25:$O$25,C99)</f>
         <v/>
       </c>
-      <c r="G99" s="139">
+      <c r="G99" s="140">
         <f>ROUND(F99*E99/D99,1)</f>
         <v/>
       </c>
-      <c r="H99" s="139">
+      <c r="H99" s="140">
         <f>F99+E99-G99</f>
         <v/>
       </c>
-      <c r="I99" s="139">
+      <c r="I99" s="140">
         <f>ROUND(MAX(H99,8),0)</f>
         <v/>
       </c>
-      <c r="J99" s="139">
+      <c r="J99" s="140">
         <f>D99-I99</f>
         <v/>
       </c>
-      <c r="K99" s="139">
+      <c r="K99" s="140">
         <f>K98+J98</f>
         <v/>
       </c>
-      <c r="L99" s="139">
+      <c r="L99" s="140">
         <f>L98+D98</f>
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="139" t="n">
+      <c r="A100" s="140" t="n">
         <v>43</v>
       </c>
-      <c r="B100" s="139">
+      <c r="B100" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A100-1))</f>
         <v/>
       </c>
-      <c r="C100" s="139">
+      <c r="C100" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A100-1))</f>
         <v/>
       </c>
-      <c r="D100" s="139">
+      <c r="D100" s="140">
         <f>DAY(EOMONTH(DATE(B100,C100,1),0))</f>
         <v/>
       </c>
-      <c r="E100" s="139">
+      <c r="E100" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B100,법정공휴일!$A$4:$A$20,0),C100),0)</f>
         <v/>
       </c>
-      <c r="F100" s="139">
+      <c r="F100" s="140">
         <f>INDEX($D$25:$O$25,C100)</f>
         <v/>
       </c>
-      <c r="G100" s="139">
+      <c r="G100" s="140">
         <f>ROUND(F100*E100/D100,1)</f>
         <v/>
       </c>
-      <c r="H100" s="139">
+      <c r="H100" s="140">
         <f>F100+E100-G100</f>
         <v/>
       </c>
-      <c r="I100" s="139">
+      <c r="I100" s="140">
         <f>ROUND(MAX(H100,8),0)</f>
         <v/>
       </c>
-      <c r="J100" s="139">
+      <c r="J100" s="140">
         <f>D100-I100</f>
         <v/>
       </c>
-      <c r="K100" s="139">
+      <c r="K100" s="140">
         <f>K99+J99</f>
         <v/>
       </c>
-      <c r="L100" s="139">
+      <c r="L100" s="140">
         <f>L99+D99</f>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="139" t="n">
+      <c r="A101" s="140" t="n">
         <v>44</v>
       </c>
-      <c r="B101" s="139">
+      <c r="B101" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A101-1))</f>
         <v/>
       </c>
-      <c r="C101" s="139">
+      <c r="C101" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A101-1))</f>
         <v/>
       </c>
-      <c r="D101" s="139">
+      <c r="D101" s="140">
         <f>DAY(EOMONTH(DATE(B101,C101,1),0))</f>
         <v/>
       </c>
-      <c r="E101" s="139">
+      <c r="E101" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B101,법정공휴일!$A$4:$A$20,0),C101),0)</f>
         <v/>
       </c>
-      <c r="F101" s="139">
+      <c r="F101" s="140">
         <f>INDEX($D$25:$O$25,C101)</f>
         <v/>
       </c>
-      <c r="G101" s="139">
+      <c r="G101" s="140">
         <f>ROUND(F101*E101/D101,1)</f>
         <v/>
       </c>
-      <c r="H101" s="139">
+      <c r="H101" s="140">
         <f>F101+E101-G101</f>
         <v/>
       </c>
-      <c r="I101" s="139">
+      <c r="I101" s="140">
         <f>ROUND(MAX(H101,8),0)</f>
         <v/>
       </c>
-      <c r="J101" s="139">
+      <c r="J101" s="140">
         <f>D101-I101</f>
         <v/>
       </c>
-      <c r="K101" s="139">
+      <c r="K101" s="140">
         <f>K100+J100</f>
         <v/>
       </c>
-      <c r="L101" s="139">
+      <c r="L101" s="140">
         <f>L100+D100</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="139" t="n">
+      <c r="A102" s="140" t="n">
         <v>45</v>
       </c>
-      <c r="B102" s="139">
+      <c r="B102" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A102-1))</f>
         <v/>
       </c>
-      <c r="C102" s="139">
+      <c r="C102" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A102-1))</f>
         <v/>
       </c>
-      <c r="D102" s="139">
+      <c r="D102" s="140">
         <f>DAY(EOMONTH(DATE(B102,C102,1),0))</f>
         <v/>
       </c>
-      <c r="E102" s="139">
+      <c r="E102" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B102,법정공휴일!$A$4:$A$20,0),C102),0)</f>
         <v/>
       </c>
-      <c r="F102" s="139">
+      <c r="F102" s="140">
         <f>INDEX($D$25:$O$25,C102)</f>
         <v/>
       </c>
-      <c r="G102" s="139">
+      <c r="G102" s="140">
         <f>ROUND(F102*E102/D102,1)</f>
         <v/>
       </c>
-      <c r="H102" s="139">
+      <c r="H102" s="140">
         <f>F102+E102-G102</f>
         <v/>
       </c>
-      <c r="I102" s="139">
+      <c r="I102" s="140">
         <f>ROUND(MAX(H102,8),0)</f>
         <v/>
       </c>
-      <c r="J102" s="139">
+      <c r="J102" s="140">
         <f>D102-I102</f>
         <v/>
       </c>
-      <c r="K102" s="139">
+      <c r="K102" s="140">
         <f>K101+J101</f>
         <v/>
       </c>
-      <c r="L102" s="139">
+      <c r="L102" s="140">
         <f>L101+D101</f>
         <v/>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="139" t="n">
+      <c r="A103" s="140" t="n">
         <v>46</v>
       </c>
-      <c r="B103" s="139">
+      <c r="B103" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A103-1))</f>
         <v/>
       </c>
-      <c r="C103" s="139">
+      <c r="C103" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A103-1))</f>
         <v/>
       </c>
-      <c r="D103" s="139">
+      <c r="D103" s="140">
         <f>DAY(EOMONTH(DATE(B103,C103,1),0))</f>
         <v/>
       </c>
-      <c r="E103" s="139">
+      <c r="E103" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B103,법정공휴일!$A$4:$A$20,0),C103),0)</f>
         <v/>
       </c>
-      <c r="F103" s="139">
+      <c r="F103" s="140">
         <f>INDEX($D$25:$O$25,C103)</f>
         <v/>
       </c>
-      <c r="G103" s="139">
+      <c r="G103" s="140">
         <f>ROUND(F103*E103/D103,1)</f>
         <v/>
       </c>
-      <c r="H103" s="139">
+      <c r="H103" s="140">
         <f>F103+E103-G103</f>
         <v/>
       </c>
-      <c r="I103" s="139">
+      <c r="I103" s="140">
         <f>ROUND(MAX(H103,8),0)</f>
         <v/>
       </c>
-      <c r="J103" s="139">
+      <c r="J103" s="140">
         <f>D103-I103</f>
         <v/>
       </c>
-      <c r="K103" s="139">
+      <c r="K103" s="140">
         <f>K102+J102</f>
         <v/>
       </c>
-      <c r="L103" s="139">
+      <c r="L103" s="140">
         <f>L102+D102</f>
         <v/>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="139" t="n">
+      <c r="A104" s="140" t="n">
         <v>47</v>
       </c>
-      <c r="B104" s="139">
+      <c r="B104" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A104-1))</f>
         <v/>
       </c>
-      <c r="C104" s="139">
+      <c r="C104" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A104-1))</f>
         <v/>
       </c>
-      <c r="D104" s="139">
+      <c r="D104" s="140">
         <f>DAY(EOMONTH(DATE(B104,C104,1),0))</f>
         <v/>
       </c>
-      <c r="E104" s="139">
+      <c r="E104" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B104,법정공휴일!$A$4:$A$20,0),C104),0)</f>
         <v/>
       </c>
-      <c r="F104" s="139">
+      <c r="F104" s="140">
         <f>INDEX($D$25:$O$25,C104)</f>
         <v/>
       </c>
-      <c r="G104" s="139">
+      <c r="G104" s="140">
         <f>ROUND(F104*E104/D104,1)</f>
         <v/>
       </c>
-      <c r="H104" s="139">
+      <c r="H104" s="140">
         <f>F104+E104-G104</f>
         <v/>
       </c>
-      <c r="I104" s="139">
+      <c r="I104" s="140">
         <f>ROUND(MAX(H104,8),0)</f>
         <v/>
       </c>
-      <c r="J104" s="139">
+      <c r="J104" s="140">
         <f>D104-I104</f>
         <v/>
       </c>
-      <c r="K104" s="139">
+      <c r="K104" s="140">
         <f>K103+J103</f>
         <v/>
       </c>
-      <c r="L104" s="139">
+      <c r="L104" s="140">
         <f>L103+D103</f>
         <v/>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="139" t="n">
+      <c r="A105" s="140" t="n">
         <v>48</v>
       </c>
-      <c r="B105" s="139">
+      <c r="B105" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A105-1))</f>
         <v/>
       </c>
-      <c r="C105" s="139">
+      <c r="C105" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A105-1))</f>
         <v/>
       </c>
-      <c r="D105" s="139">
+      <c r="D105" s="140">
         <f>DAY(EOMONTH(DATE(B105,C105,1),0))</f>
         <v/>
       </c>
-      <c r="E105" s="139">
+      <c r="E105" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B105,법정공휴일!$A$4:$A$20,0),C105),0)</f>
         <v/>
       </c>
-      <c r="F105" s="139">
+      <c r="F105" s="140">
         <f>INDEX($D$25:$O$25,C105)</f>
         <v/>
       </c>
-      <c r="G105" s="139">
+      <c r="G105" s="140">
         <f>ROUND(F105*E105/D105,1)</f>
         <v/>
       </c>
-      <c r="H105" s="139">
+      <c r="H105" s="140">
         <f>F105+E105-G105</f>
         <v/>
       </c>
-      <c r="I105" s="139">
+      <c r="I105" s="140">
         <f>ROUND(MAX(H105,8),0)</f>
         <v/>
       </c>
-      <c r="J105" s="139">
+      <c r="J105" s="140">
         <f>D105-I105</f>
         <v/>
       </c>
-      <c r="K105" s="139">
+      <c r="K105" s="140">
         <f>K104+J104</f>
         <v/>
       </c>
-      <c r="L105" s="139">
+      <c r="L105" s="140">
         <f>L104+D104</f>
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="139" t="n">
+      <c r="A106" s="140" t="n">
         <v>49</v>
       </c>
-      <c r="B106" s="139">
+      <c r="B106" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A106-1))</f>
         <v/>
       </c>
-      <c r="C106" s="139">
+      <c r="C106" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A106-1))</f>
         <v/>
       </c>
-      <c r="D106" s="139">
+      <c r="D106" s="140">
         <f>DAY(EOMONTH(DATE(B106,C106,1),0))</f>
         <v/>
       </c>
-      <c r="E106" s="139">
+      <c r="E106" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B106,법정공휴일!$A$4:$A$20,0),C106),0)</f>
         <v/>
       </c>
-      <c r="F106" s="139">
+      <c r="F106" s="140">
         <f>INDEX($D$25:$O$25,C106)</f>
         <v/>
       </c>
-      <c r="G106" s="139">
+      <c r="G106" s="140">
         <f>ROUND(F106*E106/D106,1)</f>
         <v/>
       </c>
-      <c r="H106" s="139">
+      <c r="H106" s="140">
         <f>F106+E106-G106</f>
         <v/>
       </c>
-      <c r="I106" s="139">
+      <c r="I106" s="140">
         <f>ROUND(MAX(H106,8),0)</f>
         <v/>
       </c>
-      <c r="J106" s="139">
+      <c r="J106" s="140">
         <f>D106-I106</f>
         <v/>
       </c>
-      <c r="K106" s="139">
+      <c r="K106" s="140">
         <f>K105+J105</f>
         <v/>
       </c>
-      <c r="L106" s="139">
+      <c r="L106" s="140">
         <f>L105+D105</f>
         <v/>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="139" t="n">
+      <c r="A107" s="140" t="n">
         <v>50</v>
       </c>
-      <c r="B107" s="139">
+      <c r="B107" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A107-1))</f>
         <v/>
       </c>
-      <c r="C107" s="139">
+      <c r="C107" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A107-1))</f>
         <v/>
       </c>
-      <c r="D107" s="139">
+      <c r="D107" s="140">
         <f>DAY(EOMONTH(DATE(B107,C107,1),0))</f>
         <v/>
       </c>
-      <c r="E107" s="139">
+      <c r="E107" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B107,법정공휴일!$A$4:$A$20,0),C107),0)</f>
         <v/>
       </c>
-      <c r="F107" s="139">
+      <c r="F107" s="140">
         <f>INDEX($D$25:$O$25,C107)</f>
         <v/>
       </c>
-      <c r="G107" s="139">
+      <c r="G107" s="140">
         <f>ROUND(F107*E107/D107,1)</f>
         <v/>
       </c>
-      <c r="H107" s="139">
+      <c r="H107" s="140">
         <f>F107+E107-G107</f>
         <v/>
       </c>
-      <c r="I107" s="139">
+      <c r="I107" s="140">
         <f>ROUND(MAX(H107,8),0)</f>
         <v/>
       </c>
-      <c r="J107" s="139">
+      <c r="J107" s="140">
         <f>D107-I107</f>
         <v/>
       </c>
-      <c r="K107" s="139">
+      <c r="K107" s="140">
         <f>K106+J106</f>
         <v/>
       </c>
-      <c r="L107" s="139">
+      <c r="L107" s="140">
         <f>L106+D106</f>
         <v/>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="139" t="n">
+      <c r="A108" s="140" t="n">
         <v>51</v>
       </c>
-      <c r="B108" s="139">
+      <c r="B108" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A108-1))</f>
         <v/>
       </c>
-      <c r="C108" s="139">
+      <c r="C108" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A108-1))</f>
         <v/>
       </c>
-      <c r="D108" s="139">
+      <c r="D108" s="140">
         <f>DAY(EOMONTH(DATE(B108,C108,1),0))</f>
         <v/>
       </c>
-      <c r="E108" s="139">
+      <c r="E108" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B108,법정공휴일!$A$4:$A$20,0),C108),0)</f>
         <v/>
       </c>
-      <c r="F108" s="139">
+      <c r="F108" s="140">
         <f>INDEX($D$25:$O$25,C108)</f>
         <v/>
       </c>
-      <c r="G108" s="139">
+      <c r="G108" s="140">
         <f>ROUND(F108*E108/D108,1)</f>
         <v/>
       </c>
-      <c r="H108" s="139">
+      <c r="H108" s="140">
         <f>F108+E108-G108</f>
         <v/>
       </c>
-      <c r="I108" s="139">
+      <c r="I108" s="140">
         <f>ROUND(MAX(H108,8),0)</f>
         <v/>
       </c>
-      <c r="J108" s="139">
+      <c r="J108" s="140">
         <f>D108-I108</f>
         <v/>
       </c>
-      <c r="K108" s="139">
+      <c r="K108" s="140">
         <f>K107+J107</f>
         <v/>
       </c>
-      <c r="L108" s="139">
+      <c r="L108" s="140">
         <f>L107+D107</f>
         <v/>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="139" t="n">
+      <c r="A109" s="140" t="n">
         <v>52</v>
       </c>
-      <c r="B109" s="139">
+      <c r="B109" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A109-1))</f>
         <v/>
       </c>
-      <c r="C109" s="139">
+      <c r="C109" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A109-1))</f>
         <v/>
       </c>
-      <c r="D109" s="139">
+      <c r="D109" s="140">
         <f>DAY(EOMONTH(DATE(B109,C109,1),0))</f>
         <v/>
       </c>
-      <c r="E109" s="139">
+      <c r="E109" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B109,법정공휴일!$A$4:$A$20,0),C109),0)</f>
         <v/>
       </c>
-      <c r="F109" s="139">
+      <c r="F109" s="140">
         <f>INDEX($D$25:$O$25,C109)</f>
         <v/>
       </c>
-      <c r="G109" s="139">
+      <c r="G109" s="140">
         <f>ROUND(F109*E109/D109,1)</f>
         <v/>
       </c>
-      <c r="H109" s="139">
+      <c r="H109" s="140">
         <f>F109+E109-G109</f>
         <v/>
       </c>
-      <c r="I109" s="139">
+      <c r="I109" s="140">
         <f>ROUND(MAX(H109,8),0)</f>
         <v/>
       </c>
-      <c r="J109" s="139">
+      <c r="J109" s="140">
         <f>D109-I109</f>
         <v/>
       </c>
-      <c r="K109" s="139">
+      <c r="K109" s="140">
         <f>K108+J108</f>
         <v/>
       </c>
-      <c r="L109" s="139">
+      <c r="L109" s="140">
         <f>L108+D108</f>
         <v/>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="139" t="n">
+      <c r="A110" s="140" t="n">
         <v>53</v>
       </c>
-      <c r="B110" s="139">
+      <c r="B110" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A110-1))</f>
         <v/>
       </c>
-      <c r="C110" s="139">
+      <c r="C110" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A110-1))</f>
         <v/>
       </c>
-      <c r="D110" s="139">
+      <c r="D110" s="140">
         <f>DAY(EOMONTH(DATE(B110,C110,1),0))</f>
         <v/>
       </c>
-      <c r="E110" s="139">
+      <c r="E110" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B110,법정공휴일!$A$4:$A$20,0),C110),0)</f>
         <v/>
       </c>
-      <c r="F110" s="139">
+      <c r="F110" s="140">
         <f>INDEX($D$25:$O$25,C110)</f>
         <v/>
       </c>
-      <c r="G110" s="139">
+      <c r="G110" s="140">
         <f>ROUND(F110*E110/D110,1)</f>
         <v/>
       </c>
-      <c r="H110" s="139">
+      <c r="H110" s="140">
         <f>F110+E110-G110</f>
         <v/>
       </c>
-      <c r="I110" s="139">
+      <c r="I110" s="140">
         <f>ROUND(MAX(H110,8),0)</f>
         <v/>
       </c>
-      <c r="J110" s="139">
+      <c r="J110" s="140">
         <f>D110-I110</f>
         <v/>
       </c>
-      <c r="K110" s="139">
+      <c r="K110" s="140">
         <f>K109+J109</f>
         <v/>
       </c>
-      <c r="L110" s="139">
+      <c r="L110" s="140">
         <f>L109+D109</f>
         <v/>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="139" t="n">
+      <c r="A111" s="140" t="n">
         <v>54</v>
       </c>
-      <c r="B111" s="139">
+      <c r="B111" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A111-1))</f>
         <v/>
       </c>
-      <c r="C111" s="139">
+      <c r="C111" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A111-1))</f>
         <v/>
       </c>
-      <c r="D111" s="139">
+      <c r="D111" s="140">
         <f>DAY(EOMONTH(DATE(B111,C111,1),0))</f>
         <v/>
       </c>
-      <c r="E111" s="139">
+      <c r="E111" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B111,법정공휴일!$A$4:$A$20,0),C111),0)</f>
         <v/>
       </c>
-      <c r="F111" s="139">
+      <c r="F111" s="140">
         <f>INDEX($D$25:$O$25,C111)</f>
         <v/>
       </c>
-      <c r="G111" s="139">
+      <c r="G111" s="140">
         <f>ROUND(F111*E111/D111,1)</f>
         <v/>
       </c>
-      <c r="H111" s="139">
+      <c r="H111" s="140">
         <f>F111+E111-G111</f>
         <v/>
       </c>
-      <c r="I111" s="139">
+      <c r="I111" s="140">
         <f>ROUND(MAX(H111,8),0)</f>
         <v/>
       </c>
-      <c r="J111" s="139">
+      <c r="J111" s="140">
         <f>D111-I111</f>
         <v/>
       </c>
-      <c r="K111" s="139">
+      <c r="K111" s="140">
         <f>K110+J110</f>
         <v/>
       </c>
-      <c r="L111" s="139">
+      <c r="L111" s="140">
         <f>L110+D110</f>
         <v/>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="139" t="n">
+      <c r="A112" s="140" t="n">
         <v>55</v>
       </c>
-      <c r="B112" s="139">
+      <c r="B112" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A112-1))</f>
         <v/>
       </c>
-      <c r="C112" s="139">
+      <c r="C112" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A112-1))</f>
         <v/>
       </c>
-      <c r="D112" s="139">
+      <c r="D112" s="140">
         <f>DAY(EOMONTH(DATE(B112,C112,1),0))</f>
         <v/>
       </c>
-      <c r="E112" s="139">
+      <c r="E112" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B112,법정공휴일!$A$4:$A$20,0),C112),0)</f>
         <v/>
       </c>
-      <c r="F112" s="139">
+      <c r="F112" s="140">
         <f>INDEX($D$25:$O$25,C112)</f>
         <v/>
       </c>
-      <c r="G112" s="139">
+      <c r="G112" s="140">
         <f>ROUND(F112*E112/D112,1)</f>
         <v/>
       </c>
-      <c r="H112" s="139">
+      <c r="H112" s="140">
         <f>F112+E112-G112</f>
         <v/>
       </c>
-      <c r="I112" s="139">
+      <c r="I112" s="140">
         <f>ROUND(MAX(H112,8),0)</f>
         <v/>
       </c>
-      <c r="J112" s="139">
+      <c r="J112" s="140">
         <f>D112-I112</f>
         <v/>
       </c>
-      <c r="K112" s="139">
+      <c r="K112" s="140">
         <f>K111+J111</f>
         <v/>
       </c>
-      <c r="L112" s="139">
+      <c r="L112" s="140">
         <f>L111+D111</f>
         <v/>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="139" t="n">
+      <c r="A113" s="140" t="n">
         <v>56</v>
       </c>
-      <c r="B113" s="139">
+      <c r="B113" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A113-1))</f>
         <v/>
       </c>
-      <c r="C113" s="139">
+      <c r="C113" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A113-1))</f>
         <v/>
       </c>
-      <c r="D113" s="139">
+      <c r="D113" s="140">
         <f>DAY(EOMONTH(DATE(B113,C113,1),0))</f>
         <v/>
       </c>
-      <c r="E113" s="139">
+      <c r="E113" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B113,법정공휴일!$A$4:$A$20,0),C113),0)</f>
         <v/>
       </c>
-      <c r="F113" s="139">
+      <c r="F113" s="140">
         <f>INDEX($D$25:$O$25,C113)</f>
         <v/>
       </c>
-      <c r="G113" s="139">
+      <c r="G113" s="140">
         <f>ROUND(F113*E113/D113,1)</f>
         <v/>
       </c>
-      <c r="H113" s="139">
+      <c r="H113" s="140">
         <f>F113+E113-G113</f>
         <v/>
       </c>
-      <c r="I113" s="139">
+      <c r="I113" s="140">
         <f>ROUND(MAX(H113,8),0)</f>
         <v/>
       </c>
-      <c r="J113" s="139">
+      <c r="J113" s="140">
         <f>D113-I113</f>
         <v/>
       </c>
-      <c r="K113" s="139">
+      <c r="K113" s="140">
         <f>K112+J112</f>
         <v/>
       </c>
-      <c r="L113" s="139">
+      <c r="L113" s="140">
         <f>L112+D112</f>
         <v/>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="139" t="n">
+      <c r="A114" s="140" t="n">
         <v>57</v>
       </c>
-      <c r="B114" s="139">
+      <c r="B114" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A114-1))</f>
         <v/>
       </c>
-      <c r="C114" s="139">
+      <c r="C114" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A114-1))</f>
         <v/>
       </c>
-      <c r="D114" s="139">
+      <c r="D114" s="140">
         <f>DAY(EOMONTH(DATE(B114,C114,1),0))</f>
         <v/>
       </c>
-      <c r="E114" s="139">
+      <c r="E114" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B114,법정공휴일!$A$4:$A$20,0),C114),0)</f>
         <v/>
       </c>
-      <c r="F114" s="139">
+      <c r="F114" s="140">
         <f>INDEX($D$25:$O$25,C114)</f>
         <v/>
       </c>
-      <c r="G114" s="139">
+      <c r="G114" s="140">
         <f>ROUND(F114*E114/D114,1)</f>
         <v/>
       </c>
-      <c r="H114" s="139">
+      <c r="H114" s="140">
         <f>F114+E114-G114</f>
         <v/>
       </c>
-      <c r="I114" s="139">
+      <c r="I114" s="140">
         <f>ROUND(MAX(H114,8),0)</f>
         <v/>
       </c>
-      <c r="J114" s="139">
+      <c r="J114" s="140">
         <f>D114-I114</f>
         <v/>
       </c>
-      <c r="K114" s="139">
+      <c r="K114" s="140">
         <f>K113+J113</f>
         <v/>
       </c>
-      <c r="L114" s="139">
+      <c r="L114" s="140">
         <f>L113+D113</f>
         <v/>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="139" t="n">
+      <c r="A115" s="140" t="n">
         <v>58</v>
       </c>
-      <c r="B115" s="139">
+      <c r="B115" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A115-1))</f>
         <v/>
       </c>
-      <c r="C115" s="139">
+      <c r="C115" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A115-1))</f>
         <v/>
       </c>
-      <c r="D115" s="139">
+      <c r="D115" s="140">
         <f>DAY(EOMONTH(DATE(B115,C115,1),0))</f>
         <v/>
       </c>
-      <c r="E115" s="139">
+      <c r="E115" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B115,법정공휴일!$A$4:$A$20,0),C115),0)</f>
         <v/>
       </c>
-      <c r="F115" s="139">
+      <c r="F115" s="140">
         <f>INDEX($D$25:$O$25,C115)</f>
         <v/>
       </c>
-      <c r="G115" s="139">
+      <c r="G115" s="140">
         <f>ROUND(F115*E115/D115,1)</f>
         <v/>
       </c>
-      <c r="H115" s="139">
+      <c r="H115" s="140">
         <f>F115+E115-G115</f>
         <v/>
       </c>
-      <c r="I115" s="139">
+      <c r="I115" s="140">
         <f>ROUND(MAX(H115,8),0)</f>
         <v/>
       </c>
-      <c r="J115" s="139">
+      <c r="J115" s="140">
         <f>D115-I115</f>
         <v/>
       </c>
-      <c r="K115" s="139">
+      <c r="K115" s="140">
         <f>K114+J114</f>
         <v/>
       </c>
-      <c r="L115" s="139">
+      <c r="L115" s="140">
         <f>L114+D114</f>
         <v/>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="139" t="n">
+      <c r="A116" s="140" t="n">
         <v>59</v>
       </c>
-      <c r="B116" s="139">
+      <c r="B116" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A116-1))</f>
         <v/>
       </c>
-      <c r="C116" s="139">
+      <c r="C116" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A116-1))</f>
         <v/>
       </c>
-      <c r="D116" s="139">
+      <c r="D116" s="140">
         <f>DAY(EOMONTH(DATE(B116,C116,1),0))</f>
         <v/>
       </c>
-      <c r="E116" s="139">
+      <c r="E116" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B116,법정공휴일!$A$4:$A$20,0),C116),0)</f>
         <v/>
       </c>
-      <c r="F116" s="139">
+      <c r="F116" s="140">
         <f>INDEX($D$25:$O$25,C116)</f>
         <v/>
       </c>
-      <c r="G116" s="139">
+      <c r="G116" s="140">
         <f>ROUND(F116*E116/D116,1)</f>
         <v/>
       </c>
-      <c r="H116" s="139">
+      <c r="H116" s="140">
         <f>F116+E116-G116</f>
         <v/>
       </c>
-      <c r="I116" s="139">
+      <c r="I116" s="140">
         <f>ROUND(MAX(H116,8),0)</f>
         <v/>
       </c>
-      <c r="J116" s="139">
+      <c r="J116" s="140">
         <f>D116-I116</f>
         <v/>
       </c>
-      <c r="K116" s="139">
+      <c r="K116" s="140">
         <f>K115+J115</f>
         <v/>
       </c>
-      <c r="L116" s="139">
+      <c r="L116" s="140">
         <f>L115+D115</f>
         <v/>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="139" t="n">
+      <c r="A117" s="140" t="n">
         <v>60</v>
       </c>
-      <c r="B117" s="139">
+      <c r="B117" s="140">
         <f>YEAR(EDATE(DATE($B$5,$B$6,1),A117-1))</f>
         <v/>
       </c>
-      <c r="C117" s="139">
+      <c r="C117" s="140">
         <f>MONTH(EDATE(DATE($B$5,$B$6,1),A117-1))</f>
         <v/>
       </c>
-      <c r="D117" s="139">
+      <c r="D117" s="140">
         <f>DAY(EOMONTH(DATE(B117,C117,1),0))</f>
         <v/>
       </c>
-      <c r="E117" s="139">
+      <c r="E117" s="140">
         <f>IFERROR(INDEX(법정공휴일!$B$4:$M$20,MATCH(B117,법정공휴일!$A$4:$A$20,0),C117),0)</f>
         <v/>
       </c>
-      <c r="F117" s="139">
+      <c r="F117" s="140">
         <f>INDEX($D$25:$O$25,C117)</f>
         <v/>
       </c>
-      <c r="G117" s="139">
+      <c r="G117" s="140">
         <f>ROUND(F117*E117/D117,1)</f>
         <v/>
       </c>
-      <c r="H117" s="139">
+      <c r="H117" s="140">
         <f>F117+E117-G117</f>
         <v/>
       </c>
-      <c r="I117" s="139">
+      <c r="I117" s="140">
         <f>ROUND(MAX(H117,8),0)</f>
         <v/>
       </c>
-      <c r="J117" s="139">
+      <c r="J117" s="140">
         <f>D117-I117</f>
         <v/>
       </c>
-      <c r="K117" s="139">
+      <c r="K117" s="140">
         <f>K116+J116</f>
         <v/>
       </c>
-      <c r="L117" s="139">
+      <c r="L117" s="140">
         <f>L116+D116</f>
         <v/>
       </c>
@@ -90139,7 +92543,7 @@
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=지점목록!$A$2:$A$96</formula1>
     </dataValidation>
@@ -90149,6 +92553,9 @@
     <dataValidation sqref="E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
+    <dataValidation sqref="A29 A30 A31 A32 A33 A34 A35 A36 A37 A38 A39 A40 A41 A42 A43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='1일작업량(토목)'!$A$2:$A$115</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/공기산정_2026기준.xlsx
+++ b/공기산정_2026기준.xlsx
@@ -90939,7 +90939,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>포장공사&gt;아스팔트포장 2단계-기층 (시공폭 3m 이상, 두께 5~7㎝)</t>
+          <t>포장공사&gt;아스팔트포장 2단계-기층 (시공폭 3m 이상, 두께 5-7㎝)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -90959,7 +90959,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>포장공사&gt;아스팔트포장 2단계-기층 (시공폭 3m 이상, 두께 8~10㎝)</t>
+          <t>포장공사&gt;아스팔트포장 2단계-기층 (시공폭 3m 이상, 두께 8-10㎝)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -90979,7 +90979,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>포장공사&gt;아스팔트포장 2단계-중간층/표층 (시공폭 3m 이상, 5~7㎝)</t>
+          <t>포장공사&gt;아스팔트포장 2단계-중간층/표층 (시공폭 3m 이상, 5-7㎝)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -92300,7 +92300,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>포장공사&gt;아스팔트포장 2단계-기층 (시공폭 3m 이상, 두께 5~7㎝)</t>
+          <t>포장공사&gt;아스팔트포장 2단계-기층 (시공폭 3m 이상, 두께 5-7㎝)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -92332,7 +92332,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>포장공사&gt;아스팔트포장 2단계-중간층/표층 (시공폭 3m 이상, 5~7㎝)</t>
+          <t>포장공사&gt;아스팔트포장 2단계-중간층/표층 (시공폭 3m 이상, 5-7㎝)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -92403,7 +92403,7 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>포장공사&gt;아스팔트포장 2단계-기층 (시공폭 3m 이상, 두께 5~7㎝)</t>
+          <t>포장공사&gt;아스팔트포장 2단계-기층 (시공폭 3m 이상, 두께 5-7㎝)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -92415,7 +92415,7 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>포장공사&gt;아스팔트포장 2단계-중간층/표층 (시공폭 3m 이상, 5~7㎝)</t>
+          <t>포장공사&gt;아스팔트포장 2단계-중간층/표층 (시공폭 3m 이상, 5-7㎝)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">

--- a/공기산정_2026기준.xlsx
+++ b/공기산정_2026기준.xlsx
@@ -4461,6 +4461,23 @@
         <v/>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="131" t="inlineStr">
+        <is>
+          <t>공종 목록 분류 (선택 범위 좁히기)</t>
+        </is>
+      </c>
+      <c r="B26" s="139" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>※ 분류를 고르면 아래 공종 칸의 목록이 그 분류의 공종만 보입니다.</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
       <c r="A27" s="131" t="inlineStr">
         <is>
@@ -8212,7 +8229,7 @@
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=공종프리셋!$A$1:$F$1</formula1>
     </dataValidation>
@@ -8225,8 +8242,11 @@
     <dataValidation sqref="E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
+    <dataValidation sqref="B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>='1일작업량(토목)'!$F$2:$F$9</formula1>
+    </dataValidation>
     <dataValidation sqref="A29 A30 A31 A32 A33 A34 A35 A36 A37 A38 A39 A40 A41 A42 A43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>='1일작업량(토목)'!$A$2:$A$115</formula1>
+      <formula1>=OFFSET('1일작업량(토목)'!$A$1,INDEX('1일작업량(토목)'!$G$2:$G$9,MATCH($B$26,'1일작업량(토목)'!$F$2:$F$9,0)),0,INDEX('1일작업량(토목)'!$H$2:$H$9,MATCH($B$26,'1일작업량(토목)'!$F$2:$F$9,0)),1)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -89766,12 +89786,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D117"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" style="92" min="1" max="1"/>
     <col width="20" customWidth="1" style="92" min="3" max="3"/>
     <col width="22" customWidth="1" style="92" min="4" max="4"/>
+    <col width="16" customWidth="1" style="92" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -89795,6 +89816,21 @@
           <t>원문 표기 (부록 4)</t>
         </is>
       </c>
+      <c r="F1" s="134" t="inlineStr">
+        <is>
+          <t>분류 필터</t>
+        </is>
+      </c>
+      <c r="G1" s="134" t="inlineStr">
+        <is>
+          <t>시작 위치</t>
+        </is>
+      </c>
+      <c r="H1" s="134" t="inlineStr">
+        <is>
+          <t>개수</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -89815,6 +89851,17 @@
           <t>77일/개소</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>114</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -89835,6 +89882,17 @@
           <t>30m/일</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>공통가설공사</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -89855,6 +89913,17 @@
           <t>30m/일</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>토공사</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>11</v>
+      </c>
+      <c r="H4" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -89875,6 +89944,17 @@
           <t>82㎥/일</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>배수공사</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>36</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -89895,6 +89975,17 @@
           <t>102㎡/일</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>포장공사</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>48</v>
+      </c>
+      <c r="H6" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -89915,6 +90006,17 @@
           <t>8본/일</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>교량공사</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>74</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -89935,6 +90037,17 @@
           <t>10본/일</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>터널공사</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>86</v>
+      </c>
+      <c r="H8" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -89954,6 +90067,17 @@
         <is>
           <t>6본/일</t>
         </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>부대공사</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>103</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="10">

--- a/공기산정_2026기준.xlsx
+++ b/공기산정_2026기준.xlsx
@@ -21,6 +21,14 @@
     <definedName name="내선전공">#REF!</definedName>
     <definedName name="보통인부">#REF!</definedName>
     <definedName name="프랜트전공">#REF!</definedName>
+    <definedName name="전체">'1일작업량(토목)'!$A$2:$A$115</definedName>
+    <definedName name="공통가설공사">'1일작업량(토목)'!$A$2:$A$11</definedName>
+    <definedName name="토공사">'1일작업량(토목)'!$A$12:$A$36</definedName>
+    <definedName name="배수공사">'1일작업량(토목)'!$A$37:$A$48</definedName>
+    <definedName name="포장공사">'1일작업량(토목)'!$A$49:$A$74</definedName>
+    <definedName name="교량공사">'1일작업량(토목)'!$A$75:$A$86</definedName>
+    <definedName name="터널공사">'1일작업량(토목)'!$A$87:$A$103</definedName>
+    <definedName name="부대공사">'1일작업량(토목)'!$A$104:$A$115</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'공기산정'!$A$1:$V$39</definedName>
   </definedNames>
   <calcPr calcId="152511" fullCalcOnLoad="1"/>
@@ -8246,7 +8254,7 @@
       <formula1>='1일작업량(토목)'!$F$2:$F$9</formula1>
     </dataValidation>
     <dataValidation sqref="A29 A30 A31 A32 A33 A34 A35 A36 A37 A38 A39 A40 A41 A42 A43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=OFFSET('1일작업량(토목)'!$A$1,INDEX('1일작업량(토목)'!$G$2:$G$9,MATCH($B$26,'1일작업량(토목)'!$F$2:$F$9,0)),0,INDEX('1일작업량(토목)'!$H$2:$H$9,MATCH($B$26,'1일작업량(토목)'!$F$2:$F$9,0)),1)</formula1>
+      <formula1>=INDIRECT($B$26)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/공기산정_2026기준.xlsx
+++ b/공기산정_2026기준.xlsx
@@ -21,14 +21,6 @@
     <definedName name="내선전공">#REF!</definedName>
     <definedName name="보통인부">#REF!</definedName>
     <definedName name="프랜트전공">#REF!</definedName>
-    <definedName name="전체">'1일작업량(토목)'!$A$2:$A$115</definedName>
-    <definedName name="공통가설공사">'1일작업량(토목)'!$A$2:$A$11</definedName>
-    <definedName name="토공사">'1일작업량(토목)'!$A$12:$A$36</definedName>
-    <definedName name="배수공사">'1일작업량(토목)'!$A$37:$A$48</definedName>
-    <definedName name="포장공사">'1일작업량(토목)'!$A$49:$A$74</definedName>
-    <definedName name="교량공사">'1일작업량(토목)'!$A$75:$A$86</definedName>
-    <definedName name="터널공사">'1일작업량(토목)'!$A$87:$A$103</definedName>
-    <definedName name="부대공사">'1일작업량(토목)'!$A$104:$A$115</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'공기산정'!$A$1:$V$39</definedName>
   </definedNames>
   <calcPr calcId="152511" fullCalcOnLoad="1"/>
@@ -8254,7 +8246,7 @@
       <formula1>='1일작업량(토목)'!$F$2:$F$9</formula1>
     </dataValidation>
     <dataValidation sqref="A29 A30 A31 A32 A33 A34 A35 A36 A37 A38 A39 A40 A41 A42 A43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=INDIRECT($B$26)</formula1>
+      <formula1>='1일작업량(토목)'!$J$2:$J$115</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -89794,13 +89786,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" style="92" min="1" max="1"/>
     <col width="20" customWidth="1" style="92" min="3" max="3"/>
     <col width="22" customWidth="1" style="92" min="4" max="4"/>
     <col width="16" customWidth="1" style="92" min="6" max="6"/>
+    <col width="70" customWidth="1" style="92" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -89839,6 +89832,11 @@
           <t>개수</t>
         </is>
       </c>
+      <c r="J1" s="134" t="inlineStr">
+        <is>
+          <t>필터된 공종 목록 (자동, 공종 칸 드롭다운의 원본)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -89870,6 +89868,10 @@
       <c r="H2" t="n">
         <v>114</v>
       </c>
+      <c r="J2">
+        <f>IF(ROWS($J$2:J2)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J2)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -89901,6 +89903,10 @@
       <c r="H3" t="n">
         <v>10</v>
       </c>
+      <c r="J3">
+        <f>IF(ROWS($J$2:J3)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J3)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -89932,6 +89938,10 @@
       <c r="H4" t="n">
         <v>25</v>
       </c>
+      <c r="J4">
+        <f>IF(ROWS($J$2:J4)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J4)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -89963,6 +89973,10 @@
       <c r="H5" t="n">
         <v>12</v>
       </c>
+      <c r="J5">
+        <f>IF(ROWS($J$2:J5)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J5)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -89994,6 +90008,10 @@
       <c r="H6" t="n">
         <v>26</v>
       </c>
+      <c r="J6">
+        <f>IF(ROWS($J$2:J6)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J6)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -90025,6 +90043,10 @@
       <c r="H7" t="n">
         <v>12</v>
       </c>
+      <c r="J7">
+        <f>IF(ROWS($J$2:J7)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J7)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -90056,6 +90078,10 @@
       <c r="H8" t="n">
         <v>17</v>
       </c>
+      <c r="J8">
+        <f>IF(ROWS($J$2:J8)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J8)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -90087,6 +90113,10 @@
       <c r="H9" t="n">
         <v>12</v>
       </c>
+      <c r="J9">
+        <f>IF(ROWS($J$2:J9)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J9)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -90107,6 +90137,10 @@
           <t>8본/일</t>
         </is>
       </c>
+      <c r="J10">
+        <f>IF(ROWS($J$2:J10)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J10)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -90127,6 +90161,10 @@
           <t>8본/일</t>
         </is>
       </c>
+      <c r="J11">
+        <f>IF(ROWS($J$2:J11)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J11)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -90147,6 +90185,10 @@
           <t>54㎥/일</t>
         </is>
       </c>
+      <c r="J12">
+        <f>IF(ROWS($J$2:J12)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J12)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -90167,6 +90209,10 @@
           <t>1,375㎡/일</t>
         </is>
       </c>
+      <c r="J13">
+        <f>IF(ROWS($J$2:J13)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J13)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -90187,6 +90233,10 @@
           <t>1,110㎡/일</t>
         </is>
       </c>
+      <c r="J14">
+        <f>IF(ROWS($J$2:J14)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J14)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -90207,6 +90257,10 @@
           <t>1,915㎡/일</t>
         </is>
       </c>
+      <c r="J15">
+        <f>IF(ROWS($J$2:J15)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J15)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -90227,6 +90281,10 @@
           <t>520㎥/일</t>
         </is>
       </c>
+      <c r="J16">
+        <f>IF(ROWS($J$2:J16)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J16)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -90247,6 +90305,10 @@
           <t>367㎥/일</t>
         </is>
       </c>
+      <c r="J17">
+        <f>IF(ROWS($J$2:J17)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J17)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -90267,6 +90329,10 @@
           <t>27㎥/일</t>
         </is>
       </c>
+      <c r="J18">
+        <f>IF(ROWS($J$2:J18)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J18)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -90287,6 +90353,10 @@
           <t>83㎥/일</t>
         </is>
       </c>
+      <c r="J19">
+        <f>IF(ROWS($J$2:J19)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J19)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -90307,6 +90377,10 @@
           <t>349㎥/일</t>
         </is>
       </c>
+      <c r="J20">
+        <f>IF(ROWS($J$2:J20)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J20)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -90327,6 +90401,10 @@
           <t>25㎥/일</t>
         </is>
       </c>
+      <c r="J21">
+        <f>IF(ROWS($J$2:J21)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J21)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -90347,6 +90425,10 @@
           <t>18㎥/일</t>
         </is>
       </c>
+      <c r="J22">
+        <f>IF(ROWS($J$2:J22)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J22)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -90367,6 +90449,10 @@
           <t>745㎥/일</t>
         </is>
       </c>
+      <c r="J23">
+        <f>IF(ROWS($J$2:J23)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J23)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -90387,6 +90473,10 @@
           <t>1,118㎥/일</t>
         </is>
       </c>
+      <c r="J24">
+        <f>IF(ROWS($J$2:J24)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J24)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -90407,6 +90497,10 @@
           <t>647㎥/일</t>
         </is>
       </c>
+      <c r="J25">
+        <f>IF(ROWS($J$2:J25)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J25)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -90427,6 +90521,10 @@
           <t>1,231㎥/일</t>
         </is>
       </c>
+      <c r="J26">
+        <f>IF(ROWS($J$2:J26)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J26)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -90447,6 +90545,10 @@
           <t>42㎥/일</t>
         </is>
       </c>
+      <c r="J27">
+        <f>IF(ROWS($J$2:J27)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J27)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -90467,6 +90569,10 @@
           <t>3,571㎡/일</t>
         </is>
       </c>
+      <c r="J28">
+        <f>IF(ROWS($J$2:J28)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J28)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -90487,6 +90593,10 @@
           <t>421㎥/일</t>
         </is>
       </c>
+      <c r="J29">
+        <f>IF(ROWS($J$2:J29)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J29)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -90507,6 +90617,10 @@
           <t>9,396m/일</t>
         </is>
       </c>
+      <c r="J30">
+        <f>IF(ROWS($J$2:J30)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J30)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -90527,6 +90641,10 @@
           <t>1,597㎥/일</t>
         </is>
       </c>
+      <c r="J31">
+        <f>IF(ROWS($J$2:J31)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J31)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -90547,6 +90665,10 @@
           <t>383㎥/일</t>
         </is>
       </c>
+      <c r="J32">
+        <f>IF(ROWS($J$2:J32)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J32)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -90567,6 +90689,10 @@
           <t>14본/일</t>
         </is>
       </c>
+      <c r="J33">
+        <f>IF(ROWS($J$2:J33)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J33)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -90587,6 +90713,10 @@
           <t>2.2본/일</t>
         </is>
       </c>
+      <c r="J34">
+        <f>IF(ROWS($J$2:J34)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J34)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -90607,6 +90737,10 @@
           <t>505㎡/일</t>
         </is>
       </c>
+      <c r="J35">
+        <f>IF(ROWS($J$2:J35)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J35)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -90627,6 +90761,10 @@
           <t>64m/일</t>
         </is>
       </c>
+      <c r="J36">
+        <f>IF(ROWS($J$2:J36)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J36)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -90647,6 +90785,10 @@
           <t>42일/15m/1span</t>
         </is>
       </c>
+      <c r="J37">
+        <f>IF(ROWS($J$2:J37)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J37)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -90667,6 +90809,10 @@
           <t>27일/15m/1span</t>
         </is>
       </c>
+      <c r="J38">
+        <f>IF(ROWS($J$2:J38)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J38)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -90687,6 +90833,10 @@
           <t>13일/개소</t>
         </is>
       </c>
+      <c r="J39">
+        <f>IF(ROWS($J$2:J39)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J39)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -90707,6 +90857,10 @@
           <t>43m/일</t>
         </is>
       </c>
+      <c r="J40">
+        <f>IF(ROWS($J$2:J40)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J40)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -90727,6 +90881,10 @@
           <t>38m/일</t>
         </is>
       </c>
+      <c r="J41">
+        <f>IF(ROWS($J$2:J41)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J41)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -90747,6 +90905,10 @@
           <t>3m/일</t>
         </is>
       </c>
+      <c r="J42">
+        <f>IF(ROWS($J$2:J42)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J42)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -90767,6 +90929,10 @@
           <t>25일/15m/1span</t>
         </is>
       </c>
+      <c r="J43">
+        <f>IF(ROWS($J$2:J43)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J43)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -90787,6 +90953,10 @@
           <t>14㎡/일</t>
         </is>
       </c>
+      <c r="J44">
+        <f>IF(ROWS($J$2:J44)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J44)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -90807,6 +90977,10 @@
           <t>8일/20m/1span</t>
         </is>
       </c>
+      <c r="J45">
+        <f>IF(ROWS($J$2:J45)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J45)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -90827,6 +91001,10 @@
           <t>9일/20m/1span</t>
         </is>
       </c>
+      <c r="J46">
+        <f>IF(ROWS($J$2:J46)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J46)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -90847,6 +91025,10 @@
           <t>8일/20m/1span</t>
         </is>
       </c>
+      <c r="J47">
+        <f>IF(ROWS($J$2:J47)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J47)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -90867,6 +91049,10 @@
           <t>8일/20m/1span</t>
         </is>
       </c>
+      <c r="J48">
+        <f>IF(ROWS($J$2:J48)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J48)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -90887,6 +91073,10 @@
           <t>1,900m/일</t>
         </is>
       </c>
+      <c r="J49">
+        <f>IF(ROWS($J$2:J49)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J49)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -90907,6 +91097,10 @@
           <t>1,600m/일</t>
         </is>
       </c>
+      <c r="J50">
+        <f>IF(ROWS($J$2:J50)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J50)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -90927,6 +91121,10 @@
           <t>5일</t>
         </is>
       </c>
+      <c r="J51">
+        <f>IF(ROWS($J$2:J51)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J51)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -90947,6 +91145,10 @@
           <t>600㎥/일</t>
         </is>
       </c>
+      <c r="J52">
+        <f>IF(ROWS($J$2:J52)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J52)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -90967,6 +91169,10 @@
           <t>550㎥/일</t>
         </is>
       </c>
+      <c r="J53">
+        <f>IF(ROWS($J$2:J53)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J53)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -90987,6 +91193,10 @@
           <t>1,900m/일</t>
         </is>
       </c>
+      <c r="J54">
+        <f>IF(ROWS($J$2:J54)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J54)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -91007,6 +91217,10 @@
           <t>1,600m/일</t>
         </is>
       </c>
+      <c r="J55">
+        <f>IF(ROWS($J$2:J55)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J55)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -91027,6 +91241,10 @@
           <t>3일</t>
         </is>
       </c>
+      <c r="J56">
+        <f>IF(ROWS($J$2:J56)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J56)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -91047,6 +91265,10 @@
           <t>20,000㎡/일</t>
         </is>
       </c>
+      <c r="J57">
+        <f>IF(ROWS($J$2:J57)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J57)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -91067,6 +91289,10 @@
           <t>20,000㎡/일</t>
         </is>
       </c>
+      <c r="J58">
+        <f>IF(ROWS($J$2:J58)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J58)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -91087,6 +91313,10 @@
           <t>4,900㎡/일</t>
         </is>
       </c>
+      <c r="J59">
+        <f>IF(ROWS($J$2:J59)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J59)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -91107,6 +91337,10 @@
           <t>4,500㎡/일</t>
         </is>
       </c>
+      <c r="J60">
+        <f>IF(ROWS($J$2:J60)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J60)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -91127,6 +91361,10 @@
           <t>4,800㎡/일</t>
         </is>
       </c>
+      <c r="J61">
+        <f>IF(ROWS($J$2:J61)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J61)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -91147,6 +91385,10 @@
           <t>3일/km</t>
         </is>
       </c>
+      <c r="J62">
+        <f>IF(ROWS($J$2:J62)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J62)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -91167,6 +91409,10 @@
           <t>1,900m/일</t>
         </is>
       </c>
+      <c r="J63">
+        <f>IF(ROWS($J$2:J63)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J63)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -91187,6 +91433,10 @@
           <t>1,600m/일</t>
         </is>
       </c>
+      <c r="J64">
+        <f>IF(ROWS($J$2:J64)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J64)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -91207,6 +91457,10 @@
           <t>5일</t>
         </is>
       </c>
+      <c r="J65">
+        <f>IF(ROWS($J$2:J65)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J65)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -91227,6 +91481,10 @@
           <t>600㎥/일</t>
         </is>
       </c>
+      <c r="J66">
+        <f>IF(ROWS($J$2:J66)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J66)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -91247,6 +91505,10 @@
           <t>550㎥/일</t>
         </is>
       </c>
+      <c r="J67">
+        <f>IF(ROWS($J$2:J67)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J67)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -91267,6 +91529,10 @@
           <t>1,900m/일</t>
         </is>
       </c>
+      <c r="J68">
+        <f>IF(ROWS($J$2:J68)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J68)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -91287,6 +91553,10 @@
           <t>1,600m/일</t>
         </is>
       </c>
+      <c r="J69">
+        <f>IF(ROWS($J$2:J69)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J69)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -91307,6 +91577,10 @@
           <t>3일</t>
         </is>
       </c>
+      <c r="J70">
+        <f>IF(ROWS($J$2:J70)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J70)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -91327,6 +91601,10 @@
           <t>300㎥/일</t>
         </is>
       </c>
+      <c r="J71">
+        <f>IF(ROWS($J$2:J71)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J71)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -91347,6 +91625,10 @@
           <t>700㎥/일</t>
         </is>
       </c>
+      <c r="J72">
+        <f>IF(ROWS($J$2:J72)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J72)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -91367,6 +91649,10 @@
           <t>3일</t>
         </is>
       </c>
+      <c r="J73">
+        <f>IF(ROWS($J$2:J73)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J73)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -91387,6 +91673,10 @@
           <t>3일/km</t>
         </is>
       </c>
+      <c r="J74">
+        <f>IF(ROWS($J$2:J74)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J74)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -91407,6 +91697,10 @@
           <t>18일/개소</t>
         </is>
       </c>
+      <c r="J75">
+        <f>IF(ROWS($J$2:J75)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J75)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -91427,6 +91721,10 @@
           <t>10본/일</t>
         </is>
       </c>
+      <c r="J76">
+        <f>IF(ROWS($J$2:J76)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J76)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -91447,6 +91745,10 @@
           <t>10일/1Lot</t>
         </is>
       </c>
+      <c r="J77">
+        <f>IF(ROWS($J$2:J77)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J77)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -91467,6 +91769,10 @@
           <t>7일/1Lot</t>
         </is>
       </c>
+      <c r="J78">
+        <f>IF(ROWS($J$2:J78)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J78)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -91487,6 +91793,10 @@
           <t>20일/개소</t>
         </is>
       </c>
+      <c r="J79">
+        <f>IF(ROWS($J$2:J79)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J79)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -91507,6 +91817,10 @@
           <t>10일</t>
         </is>
       </c>
+      <c r="J80">
+        <f>IF(ROWS($J$2:J80)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J80)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -91527,6 +91841,10 @@
           <t>18일/본</t>
         </is>
       </c>
+      <c r="J81">
+        <f>IF(ROWS($J$2:J81)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J81)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -91547,6 +91865,10 @@
           <t>2본/일</t>
         </is>
       </c>
+      <c r="J82">
+        <f>IF(ROWS($J$2:J82)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J82)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -91567,6 +91889,10 @@
           <t>25일/1경간</t>
         </is>
       </c>
+      <c r="J83">
+        <f>IF(ROWS($J$2:J83)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J83)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -91587,6 +91913,10 @@
           <t>200㎡/일</t>
         </is>
       </c>
+      <c r="J84">
+        <f>IF(ROWS($J$2:J84)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J84)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -91607,6 +91937,10 @@
           <t>8일/경간</t>
         </is>
       </c>
+      <c r="J85">
+        <f>IF(ROWS($J$2:J85)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J85)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -91627,6 +91961,10 @@
           <t>15일/교량</t>
         </is>
       </c>
+      <c r="J86">
+        <f>IF(ROWS($J$2:J86)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J86)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -91647,6 +91985,10 @@
           <t>25일/개소</t>
         </is>
       </c>
+      <c r="J87">
+        <f>IF(ROWS($J$2:J87)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J87)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -91667,6 +92009,10 @@
           <t>25일/개소</t>
         </is>
       </c>
+      <c r="J88">
+        <f>IF(ROWS($J$2:J88)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J88)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -91687,6 +92033,10 @@
           <t>4.3m/일</t>
         </is>
       </c>
+      <c r="J89">
+        <f>IF(ROWS($J$2:J89)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J89)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -91707,6 +92057,10 @@
           <t>4.1m/일</t>
         </is>
       </c>
+      <c r="J90">
+        <f>IF(ROWS($J$2:J90)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J90)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -91727,6 +92081,10 @@
           <t>2.9m/일</t>
         </is>
       </c>
+      <c r="J91">
+        <f>IF(ROWS($J$2:J91)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J91)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -91747,6 +92105,10 @@
           <t>2.6m/일</t>
         </is>
       </c>
+      <c r="J92">
+        <f>IF(ROWS($J$2:J92)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J92)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -91767,6 +92129,10 @@
           <t>7.1m/일</t>
         </is>
       </c>
+      <c r="J93">
+        <f>IF(ROWS($J$2:J93)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J93)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -91787,6 +92153,10 @@
           <t>2.2m/일</t>
         </is>
       </c>
+      <c r="J94">
+        <f>IF(ROWS($J$2:J94)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J94)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -91807,6 +92177,10 @@
           <t>3.6m/일</t>
         </is>
       </c>
+      <c r="J95">
+        <f>IF(ROWS($J$2:J95)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J95)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -91827,6 +92201,10 @@
           <t>2.2m/일</t>
         </is>
       </c>
+      <c r="J96">
+        <f>IF(ROWS($J$2:J96)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J96)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -91847,6 +92225,10 @@
           <t>2.9m/일</t>
         </is>
       </c>
+      <c r="J97">
+        <f>IF(ROWS($J$2:J97)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J97)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -91867,6 +92249,10 @@
           <t>3일/개소</t>
         </is>
       </c>
+      <c r="J98">
+        <f>IF(ROWS($J$2:J98)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J98)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -91887,6 +92273,10 @@
           <t>5일/개소</t>
         </is>
       </c>
+      <c r="J99">
+        <f>IF(ROWS($J$2:J99)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J99)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -91907,6 +92297,10 @@
           <t>50m/일</t>
         </is>
       </c>
+      <c r="J100">
+        <f>IF(ROWS($J$2:J100)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J100)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -91927,6 +92321,10 @@
           <t>25m/3일</t>
         </is>
       </c>
+      <c r="J101">
+        <f>IF(ROWS($J$2:J101)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J101)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -91947,6 +92345,10 @@
           <t>10m/3일</t>
         </is>
       </c>
+      <c r="J102">
+        <f>IF(ROWS($J$2:J102)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J102)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -91967,6 +92369,10 @@
           <t>25일/개소</t>
         </is>
       </c>
+      <c r="J103">
+        <f>IF(ROWS($J$2:J103)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J103)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -91987,6 +92393,10 @@
           <t>300m/일</t>
         </is>
       </c>
+      <c r="J104">
+        <f>IF(ROWS($J$2:J104)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J104)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -92007,6 +92417,10 @@
           <t>130개/일</t>
         </is>
       </c>
+      <c r="J105">
+        <f>IF(ROWS($J$2:J105)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J105)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -92027,6 +92441,10 @@
           <t>19m/일</t>
         </is>
       </c>
+      <c r="J106">
+        <f>IF(ROWS($J$2:J106)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J106)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -92047,6 +92465,10 @@
           <t>5개소/일</t>
         </is>
       </c>
+      <c r="J107">
+        <f>IF(ROWS($J$2:J107)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J107)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -92067,6 +92489,10 @@
           <t>1개소/일</t>
         </is>
       </c>
+      <c r="J108">
+        <f>IF(ROWS($J$2:J108)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J108)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -92087,6 +92513,10 @@
           <t>32m/일</t>
         </is>
       </c>
+      <c r="J109">
+        <f>IF(ROWS($J$2:J109)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J109)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -92107,6 +92537,10 @@
           <t>85㎡/일</t>
         </is>
       </c>
+      <c r="J110">
+        <f>IF(ROWS($J$2:J110)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J110)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -92127,6 +92561,10 @@
           <t>150개/일</t>
         </is>
       </c>
+      <c r="J111">
+        <f>IF(ROWS($J$2:J111)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J111)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -92147,6 +92585,10 @@
           <t>70개/일</t>
         </is>
       </c>
+      <c r="J112">
+        <f>IF(ROWS($J$2:J112)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J112)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -92167,6 +92609,10 @@
           <t>600m/일</t>
         </is>
       </c>
+      <c r="J113">
+        <f>IF(ROWS($J$2:J113)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J113)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -92187,6 +92633,10 @@
           <t>20일/개소</t>
         </is>
       </c>
+      <c r="J114">
+        <f>IF(ROWS($J$2:J114)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J114)-1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -92206,6 +92656,10 @@
         <is>
           <t>90㎡/일</t>
         </is>
+      </c>
+      <c r="J115">
+        <f>IF(ROWS($J$2:J115)&lt;=INDEX($H$2:$H$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0)),INDEX($A$2:$A$115,INDEX($G$2:$G$9,MATCH('공기산정(1일작업량)'!$B$26,$F$2:$F$9,0))+ROWS($J$2:J115)-1),"")</f>
+        <v/>
       </c>
     </row>
     <row r="117">

--- a/공기산정_2026기준.xlsx
+++ b/공기산정_2026기준.xlsx
@@ -3344,7 +3344,7 @@
     <col width="14" customWidth="1" style="92" min="8" max="8"/>
     <col width="14" customWidth="1" style="92" min="9" max="9"/>
     <col width="14" customWidth="1" style="92" min="10" max="10"/>
-    <col width="14" customWidth="1" style="92" min="11" max="11"/>
+    <col width="18" customWidth="1" style="92" min="11" max="11"/>
     <col width="14" customWidth="1" style="92" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -4541,6 +4541,11 @@
           <t>비작업일수</t>
         </is>
       </c>
+      <c r="K28" s="134" t="inlineStr">
+        <is>
+          <t>부록4 원문 표기</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="139">
@@ -4580,6 +4585,10 @@
         <f>IF(ISNUMBER(I29),ROUND(I29-F29,1),"")</f>
         <v/>
       </c>
+      <c r="K29" s="141">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$D$2:$D$115,MATCH($A29,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="139">
@@ -4619,6 +4628,10 @@
         <f>IF(ISNUMBER(I30),ROUND(I30-F30,1),"")</f>
         <v/>
       </c>
+      <c r="K30" s="141">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$D$2:$D$115,MATCH($A30,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="139">
@@ -4658,6 +4671,10 @@
         <f>IF(ISNUMBER(I31),ROUND(I31-F31,1),"")</f>
         <v/>
       </c>
+      <c r="K31" s="141">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$D$2:$D$115,MATCH($A31,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="139">
@@ -4697,6 +4714,10 @@
         <f>IF(ISNUMBER(I32),ROUND(I32-F32,1),"")</f>
         <v/>
       </c>
+      <c r="K32" s="141">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$D$2:$D$115,MATCH($A32,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="139">
@@ -4736,6 +4757,10 @@
         <f>IF(ISNUMBER(I33),ROUND(I33-F33,1),"")</f>
         <v/>
       </c>
+      <c r="K33" s="141">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$D$2:$D$115,MATCH($A33,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="139">
@@ -4775,6 +4800,10 @@
         <f>IF(ISNUMBER(I34),ROUND(I34-F34,1),"")</f>
         <v/>
       </c>
+      <c r="K34" s="141">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$D$2:$D$115,MATCH($A34,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="139">
@@ -4814,6 +4843,10 @@
         <f>IF(ISNUMBER(I35),ROUND(I35-F35,1),"")</f>
         <v/>
       </c>
+      <c r="K35" s="141">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$D$2:$D$115,MATCH($A35,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="139">
@@ -4853,6 +4886,10 @@
         <f>IF(ISNUMBER(I36),ROUND(I36-F36,1),"")</f>
         <v/>
       </c>
+      <c r="K36" s="141">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$D$2:$D$115,MATCH($A36,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="139">
@@ -4892,6 +4929,10 @@
         <f>IF(ISNUMBER(I37),ROUND(I37-F37,1),"")</f>
         <v/>
       </c>
+      <c r="K37" s="141">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$D$2:$D$115,MATCH($A37,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="139">
@@ -4931,6 +4972,10 @@
         <f>IF(ISNUMBER(I38),ROUND(I38-F38,1),"")</f>
         <v/>
       </c>
+      <c r="K38" s="141">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$D$2:$D$115,MATCH($A38,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="139">
@@ -4970,6 +5015,10 @@
         <f>IF(ISNUMBER(I39),ROUND(I39-F39,1),"")</f>
         <v/>
       </c>
+      <c r="K39" s="141">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$D$2:$D$115,MATCH($A39,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="139">
@@ -5009,6 +5058,10 @@
         <f>IF(ISNUMBER(I40),ROUND(I40-F40,1),"")</f>
         <v/>
       </c>
+      <c r="K40" s="141">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$D$2:$D$115,MATCH($A40,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="139">
@@ -5048,6 +5101,10 @@
         <f>IF(ISNUMBER(I41),ROUND(I41-F41,1),"")</f>
         <v/>
       </c>
+      <c r="K41" s="141">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$D$2:$D$115,MATCH($A41,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="139">
@@ -5087,6 +5144,10 @@
         <f>IF(ISNUMBER(I42),ROUND(I42-F42,1),"")</f>
         <v/>
       </c>
+      <c r="K42" s="141">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$D$2:$D$115,MATCH($A42,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="139">
@@ -5124,6 +5185,10 @@
       </c>
       <c r="J43" s="141">
         <f>IF(ISNUMBER(I43),ROUND(I43-F43,1),"")</f>
+        <v/>
+      </c>
+      <c r="K43" s="141">
+        <f>IFERROR(INDEX('1일작업량(토목)'!$D$2:$D$115,MATCH($A43,'1일작업량(토목)'!$A$2:$A$115,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -92886,7 +92951,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>포장공사&gt;아스팔트포장 2단계-기층 (시공폭 3m 이상, 두께 5-7㎝)</t>
+          <t>굴착부 아스팔트 복구포장 (폭 3m 미만) [1일 작업량 직접 입력]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -92916,11 +92981,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>포장공사&gt;아스팔트포장 2단계-중간층/표층 (시공폭 3m 이상, 5-7㎝)</t>
-        </is>
-      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>배수공사&gt;배수관-흄관, V.R관 (직경 600mm, 고무링접합)</t>
